--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos (carga)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos (carga)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -628,31 +628,31 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46116</v>
+        <v>46122</v>
       </c>
       <c r="B2" t="n">
-        <v>111.3</v>
+        <v>124.2</v>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>27.8</v>
       </c>
       <c r="D2" t="n">
-        <v>34.7</v>
+        <v>38.2</v>
       </c>
       <c r="E2" t="n">
-        <v>36.1</v>
+        <v>35.1</v>
       </c>
       <c r="F2" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="K2" t="n">
-        <v>65.3</v>
+        <v>71.3</v>
       </c>
       <c r="O2" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -661,40 +661,40 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V2" t="n">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="W2" t="n">
-        <v>28.5</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>23.8</v>
+        <v>19.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.2</v>
+        <v>21.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.699999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>220.23</v>
+        <v>229.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -703,7 +703,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>132.94</v>
+        <v>130.56</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -718,63 +721,48 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46116</v>
+        <v>46122</v>
       </c>
       <c r="BM2" t="n">
-        <v>42.33</v>
+        <v>54.51</v>
       </c>
       <c r="BN2" t="n">
-        <v>114.8</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>2960.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46117</v>
+        <v>46123</v>
       </c>
       <c r="B3" t="n">
-        <v>105.8</v>
+        <v>110</v>
       </c>
       <c r="C3" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>27.2</v>
       </c>
       <c r="F3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>34.6</v>
+        <v>11.5</v>
       </c>
       <c r="K3" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>31.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.2</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -783,40 +771,40 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>20.2</v>
+        <v>16</v>
       </c>
       <c r="V3" t="n">
-        <v>14.9</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X3" t="n">
-        <v>16.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.8</v>
+        <v>13.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>220.85</v>
+        <v>235.81</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.62</v>
+        <v>6.49</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -825,10 +813,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>134.45</v>
+        <v>134.07</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.51</v>
+        <v>3.52</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,63 +831,63 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46117</v>
+        <v>46123</v>
       </c>
       <c r="BM3" t="n">
-        <v>33.26</v>
+        <v>54.51</v>
       </c>
       <c r="BN3" t="n">
-        <v>67.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>3143.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46118</v>
+        <v>46124</v>
       </c>
       <c r="B4" t="n">
-        <v>120.3</v>
+        <v>108.2</v>
       </c>
       <c r="C4" t="n">
-        <v>28.2</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="n">
-        <v>37.2</v>
+        <v>37.7</v>
       </c>
       <c r="E4" t="n">
-        <v>37.3</v>
+        <v>27.2</v>
       </c>
       <c r="F4" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="H4" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="I4" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="J4" t="n">
-        <v>35.3</v>
+        <v>32.7</v>
       </c>
       <c r="K4" t="n">
-        <v>66.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="N4" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="O4" t="n">
-        <v>32</v>
+        <v>34.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.2</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -908,40 +896,40 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.2</v>
+        <v>13</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>12.6</v>
       </c>
       <c r="W4" t="n">
-        <v>17.8</v>
+        <v>26.4</v>
       </c>
       <c r="X4" t="n">
-        <v>16.3</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.3</v>
+        <v>12.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.7</v>
+        <v>7.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>225.25</v>
+        <v>235.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.4</v>
+        <v>-235.81</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -950,10 +938,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>130.12</v>
+        <v>134.07</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.33</v>
+        <v>-134.07</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -968,105 +956,105 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46118</v>
+        <v>46124</v>
       </c>
       <c r="BM4" t="n">
-        <v>41.06</v>
+        <v>54.51</v>
       </c>
       <c r="BN4" t="n">
-        <v>380.4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>2982.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B5" t="n">
-        <v>125.6</v>
+        <v>119.7</v>
       </c>
       <c r="C5" t="n">
-        <v>29.4</v>
+        <v>25.9</v>
       </c>
       <c r="D5" t="n">
-        <v>37.9</v>
+        <v>38.7</v>
       </c>
       <c r="E5" t="n">
-        <v>39.3</v>
+        <v>34.5</v>
       </c>
       <c r="F5" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16</v>
+      </c>
+      <c r="V5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W5" t="n">
         <v>24.8</v>
       </c>
-      <c r="I5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>70</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="V5" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>23.4</v>
-      </c>
       <c r="X5" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.4</v>
+        <v>15.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AF5" t="n">
-        <v>227.73</v>
+        <v>235.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.48</v>
+        <v>-4.98</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1075,10 +1063,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>127.75</v>
+        <v>136.17</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1093,63 +1081,63 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="BM5" t="n">
-        <v>44.13</v>
+        <v>54.51</v>
       </c>
       <c r="BN5" t="n">
-        <v>133.1</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>3144.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B6" t="n">
-        <v>126.8</v>
+        <v>116.54</v>
       </c>
       <c r="C6" t="n">
-        <v>28.3</v>
+        <v>23.39</v>
       </c>
       <c r="D6" t="n">
-        <v>39.2</v>
+        <v>36.98</v>
       </c>
       <c r="E6" t="n">
-        <v>39.4</v>
+        <v>35.59</v>
       </c>
       <c r="F6" t="n">
-        <v>11.3</v>
+        <v>10.58</v>
       </c>
       <c r="H6" t="n">
-        <v>25.4</v>
+        <v>20.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>34.5</v>
+        <v>27.7</v>
       </c>
       <c r="K6" t="n">
-        <v>69.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>32.8</v>
+        <v>29.2</v>
       </c>
       <c r="O6" t="n">
-        <v>34.9</v>
+        <v>31.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.8</v>
+        <v>17</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1158,40 +1146,40 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>20.8</v>
+        <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>14.2</v>
+        <v>19.5</v>
       </c>
       <c r="W6" t="n">
-        <v>23.5</v>
+        <v>26.2</v>
       </c>
       <c r="X6" t="n">
-        <v>18.9</v>
+        <v>22.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.3</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>228.5</v>
+        <v>230.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.77</v>
+        <v>-4.67</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1200,10 +1188,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>127.13</v>
+        <v>136.01</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.62</v>
+        <v>-0.16</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1218,63 +1206,63 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="BM6" t="n">
-        <v>43.41</v>
+        <v>37.84</v>
       </c>
       <c r="BN6" t="n">
-        <v>716.4</v>
+        <v>285.1</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>2003.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B7" t="n">
-        <v>125.3</v>
+        <v>117.05</v>
       </c>
       <c r="C7" t="n">
-        <v>27.9</v>
+        <v>23.91</v>
       </c>
       <c r="D7" t="n">
-        <v>37.7</v>
+        <v>36.97</v>
       </c>
       <c r="E7" t="n">
-        <v>37.2</v>
+        <v>35.6</v>
       </c>
       <c r="F7" t="n">
-        <v>11.2</v>
+        <v>10.56</v>
       </c>
       <c r="H7" t="n">
-        <v>25.5</v>
+        <v>22.3</v>
       </c>
       <c r="I7" t="n">
         <v>10.1</v>
       </c>
       <c r="J7" t="n">
-        <v>34.4</v>
+        <v>29.1</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>62.9</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="N7" t="n">
-        <v>34.2</v>
+        <v>30.5</v>
       </c>
       <c r="O7" t="n">
-        <v>35.9</v>
+        <v>31.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1283,40 +1271,40 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="V7" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="W7" t="n">
-        <v>20.6</v>
+        <v>25.8</v>
       </c>
       <c r="X7" t="n">
-        <v>18.6</v>
+        <v>22.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.5</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.3</v>
+        <v>7.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>226.87</v>
+        <v>225.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.63</v>
+        <v>-5.78</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1325,10 +1313,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>130.64</v>
+        <v>132.41</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1343,13 +1331,13 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="BM7" t="n">
-        <v>42.64</v>
+        <v>41.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>76.7</v>
+        <v>334.1</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1360,31 +1348,46 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B8" t="n">
-        <v>124.2</v>
+        <v>117.63</v>
       </c>
       <c r="C8" t="n">
-        <v>27.8</v>
+        <v>24.3</v>
       </c>
       <c r="D8" t="n">
-        <v>38.2</v>
+        <v>36.99</v>
       </c>
       <c r="E8" t="n">
-        <v>35.1</v>
+        <v>35.59</v>
       </c>
       <c r="F8" t="n">
-        <v>10.8</v>
+        <v>10.75</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.1</v>
       </c>
       <c r="K8" t="n">
-        <v>71.3</v>
+        <v>62.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31.8</v>
       </c>
       <c r="O8" t="n">
-        <v>33.3</v>
+        <v>31.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.3</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1393,40 +1396,40 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>20.3</v>
+        <v>17</v>
       </c>
       <c r="V8" t="n">
-        <v>16.8</v>
+        <v>19.1</v>
       </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>24.8</v>
       </c>
       <c r="X8" t="n">
-        <v>19.9</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.4</v>
+        <v>14.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>10.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>229.32</v>
+        <v>220</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.45</v>
+        <v>-2.67</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1435,10 +1438,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>130.56</v>
+        <v>131.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.08</v>
+        <v>-0.72</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1453,13 +1456,13 @@
         <v>0</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="BM8" t="n">
-        <v>54.51</v>
+        <v>42.83</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>106.5</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -1470,31 +1473,31 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46123</v>
+        <v>46129</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>22.3</v>
+        <v>24.75</v>
       </c>
       <c r="D9" t="n">
-        <v>37.7</v>
+        <v>37.02</v>
       </c>
       <c r="E9" t="n">
-        <v>27.2</v>
+        <v>35.31</v>
       </c>
       <c r="F9" t="n">
-        <v>11.5</v>
+        <v>10.92</v>
       </c>
       <c r="K9" t="n">
-        <v>71.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="O9" t="n">
-        <v>34.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1503,40 +1506,40 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V9" t="n">
-        <v>15.9</v>
+        <v>18.4</v>
       </c>
       <c r="W9" t="n">
-        <v>22</v>
+        <v>26.7</v>
       </c>
       <c r="X9" t="n">
-        <v>18.9</v>
+        <v>22.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.5</v>
+        <v>20.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.5</v>
+        <v>11.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.6</v>
+        <v>6.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>235.81</v>
+        <v>216.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.49</v>
+        <v>-0.66</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1544,12 +1547,6 @@
       <c r="AI9" t="n">
         <v>235</v>
       </c>
-      <c r="AK9" t="n">
-        <v>134.07</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3.52</v>
-      </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
@@ -1563,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46123</v>
+        <v>46129</v>
       </c>
       <c r="BM9" t="n">
-        <v>54.51</v>
+        <v>43.65</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -1580,46 +1577,31 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46124</v>
+        <v>46130</v>
       </c>
       <c r="B10" t="n">
-        <v>108.2</v>
+        <v>116.3</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6</v>
+        <v>25.23</v>
       </c>
       <c r="D10" t="n">
-        <v>37.7</v>
+        <v>37.18</v>
       </c>
       <c r="E10" t="n">
-        <v>27.2</v>
+        <v>32.98</v>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>32.7</v>
+        <v>10.92</v>
       </c>
       <c r="K10" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N10" t="n">
-        <v>31.5</v>
+        <v>62.9</v>
       </c>
       <c r="O10" t="n">
-        <v>34.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1628,40 +1610,40 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V10" t="n">
-        <v>12.6</v>
+        <v>18.6</v>
       </c>
       <c r="W10" t="n">
-        <v>26.4</v>
+        <v>30</v>
       </c>
       <c r="X10" t="n">
-        <v>19.5</v>
+        <v>24.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
         <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>235.83</v>
+        <v>216.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>-235.81</v>
+        <v>0.06</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1669,12 +1651,6 @@
       <c r="AI10" t="n">
         <v>235</v>
       </c>
-      <c r="AK10" t="n">
-        <v>134.07</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-134.07</v>
-      </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
@@ -1688,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46124</v>
+        <v>46130</v>
       </c>
       <c r="BM10" t="n">
-        <v>54.51</v>
+        <v>39.75</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -1705,31 +1681,31 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46125</v>
+        <v>46131</v>
       </c>
       <c r="B11" t="n">
-        <v>119.7</v>
+        <v>112.71</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9</v>
+        <v>25.48</v>
       </c>
       <c r="D11" t="n">
-        <v>38.7</v>
+        <v>37.35</v>
       </c>
       <c r="E11" t="n">
-        <v>34.5</v>
+        <v>28.98</v>
       </c>
       <c r="F11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.89</v>
       </c>
       <c r="H11" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J11" t="n">
-        <v>29</v>
+        <v>35.1</v>
       </c>
       <c r="K11" t="n">
         <v>62.9</v>
@@ -1738,55 +1714,55 @@
         <v>1.9</v>
       </c>
       <c r="N11" t="n">
-        <v>30.6</v>
+        <v>29.9</v>
       </c>
       <c r="O11" t="n">
         <v>31.8</v>
       </c>
       <c r="Q11" t="n">
+        <v>17</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>28</v>
+      </c>
+      <c r="X11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="Y11" t="n">
         <v>16</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>16</v>
-      </c>
-      <c r="V11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>17</v>
-      </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>15.7</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>235.47</v>
+        <v>216.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>-4.98</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1795,10 +1771,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>136.17</v>
+        <v>133.15</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1813,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46125</v>
+        <v>46131</v>
       </c>
       <c r="BM11" t="n">
-        <v>54.51</v>
+        <v>38.59</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -1830,46 +1806,46 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B12" t="n">
-        <v>116.54</v>
+        <v>143.9</v>
       </c>
       <c r="C12" t="n">
-        <v>23.39</v>
+        <v>32.1</v>
       </c>
       <c r="D12" t="n">
-        <v>36.98</v>
+        <v>39.5</v>
       </c>
       <c r="E12" t="n">
-        <v>35.59</v>
+        <v>40.5</v>
       </c>
       <c r="F12" t="n">
-        <v>10.58</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>20.5</v>
+        <v>24.6</v>
       </c>
       <c r="I12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>27.7</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N12" t="n">
-        <v>29.2</v>
+        <v>27</v>
       </c>
       <c r="O12" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1878,40 +1854,40 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="W12" t="n">
-        <v>26.2</v>
+        <v>20.8</v>
       </c>
       <c r="X12" t="n">
-        <v>22.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.7</v>
+        <v>-0.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>230.5</v>
+        <v>217.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>-4.67</v>
+        <v>-4.81</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1920,10 +1896,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>136.01</v>
+        <v>137.33</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.16</v>
+        <v>4.18</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1938,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="BM12" t="n">
-        <v>37.84</v>
+        <v>43.16</v>
       </c>
       <c r="BN12" t="n">
-        <v>285.1</v>
+        <v>212.4</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
@@ -1955,46 +1931,46 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B13" t="n">
-        <v>117.05</v>
+        <v>145.9</v>
       </c>
       <c r="C13" t="n">
-        <v>23.91</v>
+        <v>33.8</v>
       </c>
       <c r="D13" t="n">
-        <v>36.97</v>
+        <v>39.2</v>
       </c>
       <c r="E13" t="n">
-        <v>35.6</v>
+        <v>39.9</v>
       </c>
       <c r="F13" t="n">
-        <v>10.56</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>22.3</v>
+        <v>24.5</v>
       </c>
       <c r="I13" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="J13" t="n">
-        <v>29.1</v>
+        <v>37</v>
       </c>
       <c r="K13" t="n">
-        <v>62.9</v>
+        <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N13" t="n">
-        <v>30.5</v>
+        <v>27.7</v>
       </c>
       <c r="O13" t="n">
-        <v>31.8</v>
+        <v>29.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2003,40 +1979,40 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="W13" t="n">
-        <v>25.8</v>
+        <v>18</v>
       </c>
       <c r="X13" t="n">
-        <v>22.5</v>
+        <v>17.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>225.8</v>
+        <v>213</v>
       </c>
       <c r="AG13" t="n">
-        <v>-5.78</v>
+        <v>-2.75</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -2045,10 +2021,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>132.41</v>
+        <v>134.2</v>
       </c>
       <c r="AL13" t="n">
-        <v>-3.6</v>
+        <v>-3.13</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -2063,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="BM13" t="n">
-        <v>41.59</v>
+        <v>47.06</v>
       </c>
       <c r="BN13" t="n">
-        <v>334.1</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
@@ -2080,88 +2056,88 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B14" t="n">
-        <v>117.63</v>
+        <v>143.6</v>
       </c>
       <c r="C14" t="n">
-        <v>24.3</v>
+        <v>34.7</v>
       </c>
       <c r="D14" t="n">
-        <v>36.99</v>
+        <v>35.6</v>
       </c>
       <c r="E14" t="n">
-        <v>35.59</v>
+        <v>34.8</v>
       </c>
       <c r="F14" t="n">
-        <v>10.75</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="n">
-        <v>22.3</v>
+        <v>24.6</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>31.1</v>
+        <v>36.6</v>
       </c>
       <c r="K14" t="n">
-        <v>62.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="N14" t="n">
-        <v>31.8</v>
+        <v>34.1</v>
       </c>
       <c r="O14" t="n">
-        <v>31.8</v>
+        <v>36.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>21.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>17</v>
+        <v>21.5</v>
       </c>
       <c r="V14" t="n">
-        <v>19.1</v>
+        <v>15.9</v>
       </c>
       <c r="W14" t="n">
-        <v>24.8</v>
+        <v>20.5</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>18.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>22</v>
+        <v>16.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.8</v>
+        <v>10.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.9</v>
+        <v>6.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>220</v>
+        <v>210.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>-2.67</v>
+        <v>4.37</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -2170,10 +2146,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>131.69</v>
+        <v>128.79</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.72</v>
+        <v>-5.41</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -2182,19 +2158,19 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="BM14" t="n">
-        <v>42.83</v>
+        <v>42.7</v>
       </c>
       <c r="BN14" t="n">
-        <v>106.5</v>
+        <v>443.9</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
@@ -2205,73 +2181,88 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B15" t="n">
-        <v>118</v>
+        <v>139.1</v>
       </c>
       <c r="C15" t="n">
-        <v>24.75</v>
+        <v>34.3</v>
       </c>
       <c r="D15" t="n">
-        <v>37.02</v>
+        <v>35.7</v>
       </c>
       <c r="E15" t="n">
-        <v>35.31</v>
+        <v>34.3</v>
       </c>
       <c r="F15" t="n">
-        <v>10.92</v>
+        <v>9.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J15" t="n">
+        <v>36.9</v>
       </c>
       <c r="K15" t="n">
-        <v>62.9</v>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>32.4</v>
       </c>
       <c r="O15" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="V15" t="n">
-        <v>18.4</v>
+        <v>15.7</v>
       </c>
       <c r="W15" t="n">
-        <v>26.7</v>
+        <v>19.6</v>
       </c>
       <c r="X15" t="n">
-        <v>22.5</v>
+        <v>17.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.5</v>
+        <v>17.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.1</v>
+        <v>12.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.8</v>
+        <v>10.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>216.02</v>
+        <v>214.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.66</v>
+        <v>4.35</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2279,6 +2270,12 @@
       <c r="AI15" t="n">
         <v>235</v>
       </c>
+      <c r="AK15" t="n">
+        <v>126.33</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-2.46</v>
+      </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
@@ -2286,16 +2283,16 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="BM15" t="n">
-        <v>43.65</v>
+        <v>39.27</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -2309,73 +2306,61 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46130</v>
+        <v>46136</v>
       </c>
       <c r="B16" t="n">
-        <v>116.3</v>
+        <v>119.5</v>
       </c>
       <c r="C16" t="n">
-        <v>25.23</v>
+        <v>35.5</v>
       </c>
       <c r="D16" t="n">
-        <v>37.18</v>
+        <v>34.9</v>
       </c>
       <c r="E16" t="n">
-        <v>32.98</v>
+        <v>34.4</v>
       </c>
       <c r="F16" t="n">
-        <v>10.92</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>62.9</v>
+        <v>85.8</v>
       </c>
       <c r="O16" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>17</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>17</v>
+        <v>28.5</v>
       </c>
       <c r="V16" t="n">
-        <v>18.6</v>
+        <v>14.4</v>
       </c>
       <c r="W16" t="n">
-        <v>30</v>
+        <v>22.4</v>
       </c>
       <c r="X16" t="n">
-        <v>24.3</v>
+        <v>18.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB16" t="n">
         <v>4.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>216.08</v>
+        <v>213.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.06</v>
+        <v>-5.01</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2389,23 +2374,17 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46130</v>
+        <v>46136</v>
       </c>
       <c r="BM16" t="n">
-        <v>39.75</v>
+        <v>41.19</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP16" t="n">
         <v>0</v>
@@ -2413,88 +2392,61 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="B17" t="n">
-        <v>112.71</v>
+        <v>112.6</v>
       </c>
       <c r="C17" t="n">
-        <v>25.48</v>
+        <v>33.7</v>
       </c>
       <c r="D17" t="n">
-        <v>37.35</v>
+        <v>34.3</v>
       </c>
       <c r="E17" t="n">
-        <v>28.98</v>
+        <v>30.1</v>
       </c>
       <c r="F17" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="H17" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>35.1</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N17" t="n">
-        <v>29.9</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>17</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>17</v>
+        <v>36.4</v>
       </c>
       <c r="V17" t="n">
-        <v>19.9</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
-        <v>28</v>
+        <v>22.5</v>
       </c>
       <c r="X17" t="n">
-        <v>23.9</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>216.1</v>
+        <v>212.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.73</v>
+        <v>-1.88</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2502,29 +2454,17 @@
       <c r="AI17" t="n">
         <v>235</v>
       </c>
-      <c r="AK17" t="n">
-        <v>133.15</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="BM17" t="n">
-        <v>38.59</v>
+        <v>35.94</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2533,93 +2473,93 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46132</v>
+        <v>46138</v>
       </c>
       <c r="B18" t="n">
-        <v>143.9</v>
+        <v>137.4</v>
       </c>
       <c r="C18" t="n">
-        <v>32.1</v>
+        <v>40.3</v>
       </c>
       <c r="D18" t="n">
-        <v>39.5</v>
+        <v>32.8</v>
       </c>
       <c r="E18" t="n">
-        <v>40.5</v>
+        <v>27.7</v>
       </c>
       <c r="F18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N18" t="n">
+        <v>34</v>
+      </c>
+      <c r="O18" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="AC18" t="n">
         <v>5.9</v>
       </c>
-      <c r="H18" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>36</v>
-      </c>
-      <c r="K18" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27</v>
-      </c>
-      <c r="O18" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>11.1</v>
-      </c>
       <c r="AD18" t="n">
-        <v>5.2</v>
+        <v>0.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>217.8</v>
+        <v>212.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>-4.81</v>
+        <v>-0.12</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2628,10 +2568,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>137.33</v>
+        <v>128.64</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.18</v>
+        <v>2.31</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2640,111 +2580,111 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>75.88</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>12.45</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46132</v>
+        <v>46138</v>
       </c>
       <c r="BM18" t="n">
-        <v>43.16</v>
+        <v>29.44</v>
       </c>
       <c r="BN18" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B19" t="n">
-        <v>145.9</v>
+        <v>156.2</v>
       </c>
       <c r="C19" t="n">
-        <v>33.8</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>39.2</v>
+        <v>36.5</v>
       </c>
       <c r="E19" t="n">
-        <v>39.9</v>
+        <v>34.7</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H19" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="Q19" t="n">
         <v>24.5</v>
       </c>
-      <c r="I19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>37</v>
-      </c>
-      <c r="K19" t="n">
-        <v>71</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N19" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="V19" t="n">
-        <v>16.1</v>
+        <v>11.2</v>
       </c>
       <c r="W19" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="X19" t="n">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="n">
         <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>14</v>
+        <v>11.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>213</v>
+        <v>211.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>-2.75</v>
+        <v>-3.2</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2753,10 +2693,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>134.2</v>
+        <v>129.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>-3.13</v>
+        <v>1.31</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2765,16 +2705,16 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>74.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>12.33</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="BM19" t="n">
-        <v>47.06</v>
+        <v>38.57</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -2783,93 +2723,93 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B20" t="n">
-        <v>143.6</v>
+        <v>151.4</v>
       </c>
       <c r="C20" t="n">
-        <v>34.7</v>
+        <v>47.3</v>
       </c>
       <c r="D20" t="n">
-        <v>35.6</v>
+        <v>35.2</v>
       </c>
       <c r="E20" t="n">
-        <v>34.8</v>
+        <v>29.1</v>
       </c>
       <c r="F20" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="H20" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="I20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="K20" t="n">
-        <v>70.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="O20" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>15.9</v>
+        <v>8.4</v>
       </c>
       <c r="W20" t="n">
-        <v>20.5</v>
+        <v>16.9</v>
       </c>
       <c r="X20" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AF20" t="n">
-        <v>210.3</v>
+        <v>208.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.37</v>
+        <v>-0.6</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2878,10 +2818,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>128.79</v>
+        <v>122.63</v>
       </c>
       <c r="AL20" t="n">
-        <v>-5.41</v>
+        <v>-7.32</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2890,111 +2830,111 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>78.36</v>
+        <v>72.87</v>
       </c>
       <c r="AS20" t="n">
-        <v>13.07</v>
+        <v>14.41</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="BM20" t="n">
-        <v>42.7</v>
+        <v>35.38</v>
       </c>
       <c r="BN20" t="n">
-        <v>443.9</v>
+        <v>1290.5</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B21" t="n">
-        <v>139.1</v>
+        <v>143.4</v>
       </c>
       <c r="C21" t="n">
-        <v>34.3</v>
+        <v>42.8</v>
       </c>
       <c r="D21" t="n">
-        <v>35.7</v>
+        <v>33.9</v>
       </c>
       <c r="E21" t="n">
-        <v>34.3</v>
+        <v>29.3</v>
       </c>
       <c r="F21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>24.7</v>
+        <v>22.7</v>
       </c>
       <c r="I21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>36.9</v>
+        <v>34.6</v>
       </c>
       <c r="K21" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="N21" t="n">
-        <v>32.4</v>
+        <v>35.2</v>
       </c>
       <c r="O21" t="n">
-        <v>34.8</v>
+        <v>40.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="V21" t="n">
-        <v>15.7</v>
+        <v>8.9</v>
       </c>
       <c r="W21" t="n">
-        <v>19.6</v>
+        <v>20.6</v>
       </c>
       <c r="X21" t="n">
-        <v>17.6</v>
+        <v>14.8</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>17.7</v>
+        <v>16</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>214.63</v>
+        <v>208.07</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.35</v>
+        <v>-3.2</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -3003,10 +2943,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>126.33</v>
+        <v>120.64</v>
       </c>
       <c r="AL21" t="n">
-        <v>-2.46</v>
+        <v>-1.99</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -3015,84 +2955,78 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="BL21" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="BN21" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="AS21" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="BL21" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
       <c r="BO21" t="n">
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B22" t="n">
-        <v>119.5</v>
+        <v>126.5</v>
       </c>
       <c r="C22" t="n">
-        <v>35.5</v>
+        <v>42.3</v>
       </c>
       <c r="D22" t="n">
-        <v>34.9</v>
+        <v>35.4</v>
       </c>
       <c r="E22" t="n">
-        <v>34.4</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>28.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="W22" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="X22" t="n">
-        <v>18.4</v>
+        <v>16.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>213.96</v>
+        <v>205.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>-5.01</v>
+        <v>0.7</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -3100,6 +3034,12 @@
       <c r="AI22" t="n">
         <v>235</v>
       </c>
+      <c r="AK22" t="n">
+        <v>126.26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>5.62</v>
+      </c>
       <c r="AM22" t="n">
         <v>110</v>
       </c>
@@ -3107,78 +3047,72 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="BM22" t="n">
-        <v>41.19</v>
+        <v>34.74</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="B23" t="n">
-        <v>112.6</v>
+        <v>117</v>
       </c>
       <c r="C23" t="n">
-        <v>33.7</v>
+        <v>40.6</v>
       </c>
       <c r="D23" t="n">
-        <v>34.3</v>
+        <v>33.6</v>
       </c>
       <c r="E23" t="n">
-        <v>30.1</v>
+        <v>25.1</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="O23" t="n">
-        <v>36.4</v>
+        <v>9.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>11.2</v>
       </c>
       <c r="W23" t="n">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
       <c r="X23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>212.08</v>
+        <v>215.07</v>
       </c>
       <c r="AG23" t="n">
-        <v>-1.88</v>
+        <v>9.42</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -3186,6 +3120,12 @@
       <c r="AI23" t="n">
         <v>235</v>
       </c>
+      <c r="AK23" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>10.99</v>
+      </c>
       <c r="AM23" t="n">
         <v>110</v>
       </c>
@@ -3193,10 +3133,10 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="BM23" t="n">
-        <v>35.94</v>
+        <v>28.2</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
@@ -3205,93 +3145,60 @@
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>803</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="B24" t="n">
-        <v>137.4</v>
+        <v>123.4</v>
       </c>
       <c r="C24" t="n">
-        <v>40.3</v>
+        <v>41.7</v>
       </c>
       <c r="D24" t="n">
-        <v>32.8</v>
+        <v>34.4</v>
       </c>
       <c r="E24" t="n">
-        <v>27.7</v>
+        <v>29.8</v>
       </c>
       <c r="F24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I24" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N24" t="n">
-        <v>34</v>
-      </c>
-      <c r="O24" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
       </c>
       <c r="V24" t="n">
-        <v>13.4</v>
+        <v>15.9</v>
       </c>
       <c r="W24" t="n">
-        <v>24.6</v>
+        <v>18.1</v>
       </c>
       <c r="X24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>-5.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>212.1</v>
+        <v>218.94</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.12</v>
+        <v>1.37</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -3300,10 +3207,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>128.64</v>
+        <v>138.94</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.31</v>
+        <v>1.69</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -3311,17 +3218,11 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>75.88</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>12.45</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="BM24" t="n">
-        <v>29.44</v>
+        <v>34.9</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
@@ -3330,93 +3231,93 @@
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>2614.1</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="B25" t="n">
-        <v>156.2</v>
+        <v>139.9</v>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="D25" t="n">
-        <v>36.5</v>
+        <v>32.1</v>
       </c>
       <c r="E25" t="n">
-        <v>34.7</v>
+        <v>30.3</v>
       </c>
       <c r="F25" t="n">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="H25" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="I25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J25" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="K25" t="n">
-        <v>73.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N25" t="n">
-        <v>27.8</v>
+        <v>31.8</v>
       </c>
       <c r="O25" t="n">
-        <v>31.4</v>
+        <v>37.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>24.5</v>
+        <v>22.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>24.5</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="W25" t="n">
-        <v>17.8</v>
+        <v>21</v>
       </c>
       <c r="X25" t="n">
-        <v>14.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z25" t="n">
         <v>18</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>211.95</v>
+        <v>216.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.2</v>
+        <v>5.78</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3425,10 +3326,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>129.95</v>
+        <v>138.94</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3437,16 +3338,16 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>74.8</v>
+        <v>82.64</v>
       </c>
       <c r="AS25" t="n">
-        <v>12.33</v>
+        <v>17.47</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="BM25" t="n">
-        <v>38.57</v>
+        <v>35.06</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
@@ -3455,93 +3356,93 @@
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>3080.7</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B26" t="n">
-        <v>151.4</v>
+        <v>150.3</v>
       </c>
       <c r="C26" t="n">
-        <v>47.3</v>
+        <v>44.1</v>
       </c>
       <c r="D26" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E26" t="n">
         <v>35.2</v>
       </c>
-      <c r="E26" t="n">
-        <v>29.1</v>
-      </c>
       <c r="F26" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>24.2</v>
+        <v>25.2</v>
       </c>
       <c r="I26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="K26" t="n">
-        <v>72.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="N26" t="n">
-        <v>34.2</v>
+        <v>36</v>
       </c>
       <c r="O26" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="V26" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="W26" t="n">
-        <v>16.9</v>
+        <v>22.3</v>
       </c>
       <c r="X26" t="n">
-        <v>12.6</v>
+        <v>16.4</v>
       </c>
       <c r="Y26" t="n">
         <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>208.67</v>
+        <v>224.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.6</v>
+        <v>-1.69</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3550,10 +3451,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>122.63</v>
+        <v>137.96</v>
       </c>
       <c r="AL26" t="n">
-        <v>-7.32</v>
+        <v>-0.98</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3562,111 +3463,111 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>72.87</v>
+        <v>80.97</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.41</v>
+        <v>15.56</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="BM26" t="n">
-        <v>35.38</v>
+        <v>37.45</v>
       </c>
       <c r="BN26" t="n">
-        <v>1290.5</v>
+        <v>0</v>
       </c>
       <c r="BO26" t="n">
         <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>3224.5</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B27" t="n">
-        <v>143.4</v>
+        <v>147.9</v>
       </c>
       <c r="C27" t="n">
-        <v>42.8</v>
+        <v>39</v>
       </c>
       <c r="D27" t="n">
-        <v>33.9</v>
+        <v>35.7</v>
       </c>
       <c r="E27" t="n">
-        <v>29.3</v>
+        <v>34.7</v>
       </c>
       <c r="F27" t="n">
-        <v>9.199999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H27" t="n">
-        <v>22.7</v>
+        <v>25.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J27" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N27" t="n">
         <v>34.6</v>
       </c>
-      <c r="K27" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>35.2</v>
-      </c>
       <c r="O27" t="n">
-        <v>40.7</v>
+        <v>39.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="R27" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="V27" t="n">
-        <v>8.9</v>
+        <v>13.6</v>
       </c>
       <c r="W27" t="n">
-        <v>20.6</v>
+        <v>25.8</v>
       </c>
       <c r="X27" t="n">
-        <v>14.8</v>
+        <v>19.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA27" t="n">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>208.07</v>
+        <v>223.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3675,10 +3576,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>120.64</v>
+        <v>137.77</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.99</v>
+        <v>-0.19</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3687,78 +3588,111 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>72.25</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.19</v>
+        <v>15.85</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="BM27" t="n">
-        <v>33.67</v>
+        <v>38.99</v>
       </c>
       <c r="BN27" t="n">
-        <v>81.40000000000001</v>
+        <v>32.8</v>
       </c>
       <c r="BO27" t="n">
         <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>3077.5</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B28" t="n">
-        <v>126.5</v>
+        <v>140.8</v>
       </c>
       <c r="C28" t="n">
-        <v>42.3</v>
+        <v>36.9</v>
       </c>
       <c r="D28" t="n">
-        <v>35.4</v>
+        <v>33.8</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>34.3</v>
       </c>
       <c r="F28" t="n">
-        <v>9.800000000000001</v>
+        <v>11.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>19.7</v>
       </c>
       <c r="V28" t="n">
-        <v>10.6</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>23</v>
+        <v>27.2</v>
       </c>
       <c r="X28" t="n">
-        <v>16.8</v>
+        <v>20.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
         <v>23</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.5</v>
+        <v>22.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>205.66</v>
+        <v>225.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.7</v>
+        <v>6.89</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3767,10 +3701,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>126.26</v>
+        <v>137.06</v>
       </c>
       <c r="AL28" t="n">
-        <v>5.62</v>
+        <v>-0.71</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3778,73 +3712,112 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>17.56</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="BM28" t="n">
-        <v>34.74</v>
+        <v>38.26</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO28" t="n">
         <v>0</v>
       </c>
       <c r="BP28" t="n">
-        <v>3215.1</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B29" t="n">
-        <v>117</v>
+        <v>145.7</v>
       </c>
       <c r="C29" t="n">
-        <v>40.6</v>
+        <v>45.9</v>
       </c>
       <c r="D29" t="n">
-        <v>33.6</v>
+        <v>34.5</v>
       </c>
       <c r="E29" t="n">
-        <v>25.1</v>
+        <v>31.1</v>
       </c>
       <c r="F29" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>20.6</v>
       </c>
       <c r="V29" t="n">
-        <v>11.2</v>
+        <v>12.9</v>
       </c>
       <c r="W29" t="n">
-        <v>24.9</v>
+        <v>19.4</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>16.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>19</v>
+        <v>13.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>215.07</v>
+        <v>232.44</v>
       </c>
       <c r="AG29" t="n">
-        <v>9.42</v>
+        <v>0.32</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3853,10 +3826,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>137.25</v>
+        <v>136.23</v>
       </c>
       <c r="AL29" t="n">
-        <v>10.99</v>
+        <v>-0.83</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3864,11 +3837,17 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>17.5</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="BM29" t="n">
-        <v>28.2</v>
+        <v>36.16</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
@@ -3877,60 +3856,66 @@
         <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>2951.2</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="B30" t="n">
-        <v>123.4</v>
+        <v>136.5</v>
       </c>
       <c r="C30" t="n">
-        <v>41.7</v>
+        <v>52.8</v>
       </c>
       <c r="D30" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>29.8</v>
+        <v>30.6</v>
       </c>
       <c r="F30" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>36.5</v>
       </c>
       <c r="V30" t="n">
-        <v>15.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>13.7</v>
       </c>
       <c r="Y30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z30" t="n">
         <v>13</v>
       </c>
-      <c r="Z30" t="n">
-        <v>18</v>
-      </c>
       <c r="AA30" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.1</v>
+        <v>-1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>218.94</v>
+        <v>228.64</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.37</v>
+        <v>-4.15</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3939,10 +3924,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>138.94</v>
+        <v>134.67</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.69</v>
+        <v>-1.56</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3951,10 +3936,10 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="BM30" t="n">
-        <v>34.9</v>
+        <v>35.28</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
@@ -3963,93 +3948,66 @@
         <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>2928.3</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="B31" t="n">
-        <v>139.9</v>
+        <v>135.2</v>
       </c>
       <c r="C31" t="n">
-        <v>49.3</v>
+        <v>54.4</v>
       </c>
       <c r="D31" t="n">
-        <v>32.1</v>
+        <v>33.4</v>
       </c>
       <c r="E31" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="F31" t="n">
         <v>9.6</v>
       </c>
-      <c r="H31" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>38.3</v>
-      </c>
       <c r="K31" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>31.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>22.3</v>
+        <v>34.2</v>
       </c>
       <c r="V31" t="n">
-        <v>11.8</v>
+        <v>7.9</v>
       </c>
       <c r="W31" t="n">
-        <v>21</v>
+        <v>13.9</v>
       </c>
       <c r="X31" t="n">
-        <v>16.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AF31" t="n">
-        <v>216.4</v>
+        <v>225.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.78</v>
+        <v>-3.48</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -4058,10 +4016,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>138.94</v>
+        <v>128.27</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>-6.4</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -4069,112 +4027,106 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>82.64</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>17.47</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="BM31" t="n">
-        <v>35.06</v>
+        <v>34.73</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP31" t="n">
-        <v>2891.3</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46146</v>
+        <v>46152</v>
       </c>
       <c r="B32" t="n">
-        <v>150.3</v>
+        <v>154.3</v>
       </c>
       <c r="C32" t="n">
-        <v>44.1</v>
+        <v>62.4</v>
       </c>
       <c r="D32" t="n">
-        <v>34.5</v>
+        <v>32.3</v>
       </c>
       <c r="E32" t="n">
-        <v>35.2</v>
+        <v>27</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="H32" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="J32" t="n">
-        <v>35</v>
+        <v>38.7</v>
       </c>
       <c r="K32" t="n">
-        <v>70.2</v>
+        <v>74.3</v>
       </c>
       <c r="M32" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O32" t="n">
-        <v>41.2</v>
+        <v>36.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R32" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="V32" t="n">
-        <v>10.4</v>
+        <v>4.9</v>
       </c>
       <c r="W32" t="n">
-        <v>22.3</v>
+        <v>16.9</v>
       </c>
       <c r="X32" t="n">
-        <v>16.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>224.66</v>
+        <v>225.13</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.69</v>
+        <v>-1.28</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -4183,10 +4135,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>137.96</v>
+        <v>128.27</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -4195,111 +4147,111 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>80.97</v>
+        <v>79.12</v>
       </c>
       <c r="AS32" t="n">
-        <v>15.56</v>
+        <v>13.55</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46146</v>
+        <v>46152</v>
       </c>
       <c r="BM32" t="n">
-        <v>37.45</v>
+        <v>32.03</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="BP32" t="n">
-        <v>2948.4</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B33" t="n">
-        <v>147.9</v>
+        <v>152.8</v>
       </c>
       <c r="C33" t="n">
-        <v>39</v>
+        <v>60.4</v>
       </c>
       <c r="D33" t="n">
-        <v>35.7</v>
+        <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>34.7</v>
+        <v>25.1</v>
       </c>
       <c r="F33" t="n">
-        <v>10.6</v>
+        <v>7.5</v>
       </c>
       <c r="H33" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="I33" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K33" t="n">
-        <v>71.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O33" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V33" t="n">
-        <v>13.6</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>25.8</v>
+        <v>19.3</v>
       </c>
       <c r="X33" t="n">
-        <v>19.7</v>
+        <v>12.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>20.3</v>
+        <v>12.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>223.02</v>
+        <v>223.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.55</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -4308,10 +4260,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>137.77</v>
+        <v>125.44</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.19</v>
+        <v>-2.83</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -4320,111 +4272,111 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>85.15000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>15.85</v>
+        <v>13.16</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="BM33" t="n">
-        <v>38.99</v>
+        <v>29.94</v>
       </c>
       <c r="BN33" t="n">
-        <v>32.8</v>
+        <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="BP33" t="n">
-        <v>3132.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B34" t="n">
-        <v>140.8</v>
+        <v>152</v>
       </c>
       <c r="C34" t="n">
-        <v>36.9</v>
+        <v>57.9</v>
       </c>
       <c r="D34" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="E34" t="n">
-        <v>34.3</v>
+        <v>26.4</v>
       </c>
       <c r="F34" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="H34" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K34" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O34" t="n">
-        <v>36.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>19.7</v>
+        <v>23.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>19.7</v>
+        <v>23.1</v>
       </c>
       <c r="V34" t="n">
-        <v>14.7</v>
+        <v>8.6</v>
       </c>
       <c r="W34" t="n">
-        <v>27.2</v>
+        <v>22.9</v>
       </c>
       <c r="X34" t="n">
-        <v>20.9</v>
+        <v>15.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Z34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="n">
-        <v>22.1</v>
+        <v>15.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>225.57</v>
+        <v>222.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>6.89</v>
+        <v>0.06</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -4433,10 +4385,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>137.06</v>
+        <v>124.13</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.71</v>
+        <v>-1.31</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -4445,111 +4397,111 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>88.22</v>
+        <v>79.44</v>
       </c>
       <c r="AS34" t="n">
-        <v>17.56</v>
+        <v>13.94</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="BM34" t="n">
-        <v>38.26</v>
+        <v>30.3</v>
       </c>
       <c r="BN34" t="n">
-        <v>90.09999999999999</v>
+        <v>6604.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>946</v>
       </c>
       <c r="BP34" t="n">
-        <v>3220.9</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B35" t="n">
-        <v>145.7</v>
+        <v>156.1</v>
       </c>
       <c r="C35" t="n">
-        <v>45.9</v>
+        <v>60.7</v>
       </c>
       <c r="D35" t="n">
         <v>34.5</v>
       </c>
       <c r="E35" t="n">
-        <v>31.1</v>
+        <v>26.6</v>
       </c>
       <c r="F35" t="n">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I35" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
-        <v>38.7</v>
+        <v>39.5</v>
       </c>
       <c r="K35" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="N35" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="O35" t="n">
-        <v>38.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.6</v>
+        <v>22.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>20.6</v>
+        <v>22.7</v>
       </c>
       <c r="V35" t="n">
-        <v>12.9</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>19.4</v>
+        <v>23</v>
       </c>
       <c r="X35" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AC35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD35" t="n">
         <v>5.9</v>
       </c>
-      <c r="AD35" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF35" t="n">
-        <v>232.44</v>
+        <v>222.98</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.32</v>
+        <v>-1.71</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -4558,10 +4510,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>136.23</v>
+        <v>125.24</v>
       </c>
       <c r="AL35" t="n">
-        <v>-0.83</v>
+        <v>1.11</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -4570,84 +4522,111 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>85.48999999999999</v>
+        <v>79.06</v>
       </c>
       <c r="AS35" t="n">
-        <v>17.5</v>
+        <v>14.03</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="BM35" t="n">
-        <v>36.16</v>
+        <v>30.8</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1027.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>3053.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B36" t="n">
-        <v>136.5</v>
+        <v>156.3</v>
       </c>
       <c r="C36" t="n">
-        <v>52.8</v>
+        <v>60.3</v>
       </c>
       <c r="D36" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E36" t="n">
-        <v>30.6</v>
+        <v>27.8</v>
       </c>
       <c r="F36" t="n">
-        <v>9.6</v>
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>39.6</v>
       </c>
       <c r="K36" t="n">
-        <v>97.2</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>36.8</v>
       </c>
       <c r="O36" t="n">
-        <v>36.5</v>
+        <v>39.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.5</v>
       </c>
       <c r="V36" t="n">
-        <v>9.699999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="W36" t="n">
-        <v>17.7</v>
+        <v>20.8</v>
       </c>
       <c r="X36" t="n">
-        <v>13.7</v>
+        <v>15.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.2</v>
+        <v>11.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="AF36" t="n">
-        <v>228.64</v>
+        <v>221.26</v>
       </c>
       <c r="AG36" t="n">
-        <v>-4.15</v>
+        <v>-0.2</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4656,10 +4635,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>134.67</v>
+        <v>125.58</v>
       </c>
       <c r="AL36" t="n">
-        <v>-1.56</v>
+        <v>0.34</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4667,79 +4646,85 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>79.02</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>13.34</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="BM36" t="n">
-        <v>35.28</v>
+        <v>32.04</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1410.7</v>
       </c>
       <c r="BP36" t="n">
-        <v>2989.1</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="B37" t="n">
-        <v>135.2</v>
+        <v>132.9</v>
       </c>
       <c r="C37" t="n">
-        <v>54.4</v>
+        <v>56.5</v>
       </c>
       <c r="D37" t="n">
-        <v>33.4</v>
+        <v>34.6</v>
       </c>
       <c r="E37" t="n">
-        <v>29</v>
+        <v>24.6</v>
       </c>
       <c r="F37" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="K37" t="n">
-        <v>97.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="O37" t="n">
-        <v>34.2</v>
+        <v>39.1</v>
       </c>
       <c r="V37" t="n">
-        <v>7.9</v>
+        <v>11.6</v>
       </c>
       <c r="W37" t="n">
-        <v>13.9</v>
+        <v>21.3</v>
       </c>
       <c r="X37" t="n">
-        <v>10.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>-1.6</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>225.16</v>
+        <v>221.88</v>
       </c>
       <c r="AG37" t="n">
-        <v>-3.48</v>
+        <v>0.79</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4748,10 +4733,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>128.27</v>
+        <v>123.06</v>
       </c>
       <c r="AL37" t="n">
-        <v>-6.4</v>
+        <v>-2.52</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4760,105 +4745,78 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="BM37" t="n">
-        <v>34.73</v>
+        <v>30.26</v>
       </c>
       <c r="BN37" t="n">
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>530.9</v>
+        <v>677.9</v>
       </c>
       <c r="BP37" t="n">
-        <v>2772.3</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="B38" t="n">
-        <v>154.3</v>
+        <v>133.2</v>
       </c>
       <c r="C38" t="n">
-        <v>62.4</v>
+        <v>58.4</v>
       </c>
       <c r="D38" t="n">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="E38" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
         <v>6.7</v>
       </c>
-      <c r="H38" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="O38" t="n">
         <v>38.7</v>
       </c>
-      <c r="K38" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>33</v>
-      </c>
-      <c r="O38" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>23.3</v>
-      </c>
       <c r="V38" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="W38" t="n">
-        <v>16.9</v>
+        <v>17.9</v>
       </c>
       <c r="X38" t="n">
-        <v>10.9</v>
+        <v>14.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.3</v>
+        <v>14.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>2</v>
+        <v>-1.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>11.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AF38" t="n">
-        <v>225.13</v>
+        <v>223.58</v>
       </c>
       <c r="AG38" t="n">
-        <v>-1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4867,10 +4825,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.27</v>
+        <v>125.11</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4878,112 +4836,106 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
-      <c r="AP38" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>13.55</v>
-      </c>
       <c r="BL38" s="1" t="n">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="BM38" t="n">
-        <v>32.03</v>
+        <v>30.36</v>
       </c>
       <c r="BN38" t="n">
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>164</v>
+        <v>1209</v>
       </c>
       <c r="BP38" t="n">
-        <v>2906.5</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46153</v>
+        <v>46159</v>
       </c>
       <c r="B39" t="n">
-        <v>152.8</v>
+        <v>156.7</v>
       </c>
       <c r="C39" t="n">
-        <v>60.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>31.8</v>
       </c>
       <c r="E39" t="n">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
       <c r="F39" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H39" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="I39" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>38.4</v>
+        <v>40</v>
       </c>
       <c r="K39" t="n">
-        <v>72.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>34.5</v>
+        <v>36.7</v>
       </c>
       <c r="O39" t="n">
-        <v>39.5</v>
+        <v>40.3</v>
       </c>
       <c r="Q39" t="n">
         <v>23.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="T39" t="n">
         <v>23.1</v>
       </c>
       <c r="V39" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>19.3</v>
+        <v>13.1</v>
       </c>
       <c r="X39" t="n">
-        <v>12.4</v>
+        <v>10.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="AF39" t="n">
-        <v>223.85</v>
+        <v>223.6</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4992,10 +4944,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>125.44</v>
+        <v>125.11</v>
       </c>
       <c r="AL39" t="n">
-        <v>-2.83</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -5004,111 +4956,111 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>77.90000000000001</v>
+        <v>83.37</v>
       </c>
       <c r="AS39" t="n">
-        <v>13.16</v>
+        <v>14</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46153</v>
+        <v>46159</v>
       </c>
       <c r="BM39" t="n">
-        <v>29.94</v>
+        <v>30.74</v>
       </c>
       <c r="BN39" t="n">
         <v>0</v>
       </c>
       <c r="BO39" t="n">
-        <v>455</v>
+        <v>1207.3</v>
       </c>
       <c r="BP39" t="n">
-        <v>3341</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B40" t="n">
-        <v>152</v>
+        <v>169.4</v>
       </c>
       <c r="C40" t="n">
-        <v>57.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="E40" t="n">
-        <v>26.4</v>
+        <v>29.9</v>
       </c>
       <c r="F40" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="H40" t="n">
         <v>25.3</v>
       </c>
       <c r="I40" t="n">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="K40" t="n">
-        <v>72.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>37.1</v>
+        <v>33.2</v>
       </c>
       <c r="O40" t="n">
-        <v>41.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R40" t="n">
         <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="T40" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V40" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="W40" t="n">
-        <v>22.9</v>
+        <v>16.2</v>
       </c>
       <c r="X40" t="n">
-        <v>15.8</v>
+        <v>10.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA40" t="n">
-        <v>15.5</v>
+        <v>10.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC40" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="AF40" t="n">
-        <v>222.91</v>
+        <v>223.66</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.06</v>
+        <v>-3.09</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -5117,10 +5069,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>124.13</v>
+        <v>129.53</v>
       </c>
       <c r="AL40" t="n">
-        <v>-1.31</v>
+        <v>4.42</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -5129,111 +5081,111 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>79.44</v>
+        <v>81.22</v>
       </c>
       <c r="AS40" t="n">
-        <v>13.94</v>
+        <v>13.69</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="BM40" t="n">
-        <v>30.3</v>
+        <v>33.76</v>
       </c>
       <c r="BN40" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>946</v>
+        <v>1003.3</v>
       </c>
       <c r="BP40" t="n">
-        <v>3260.9</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B41" t="n">
-        <v>156.1</v>
+        <v>163.7</v>
       </c>
       <c r="C41" t="n">
-        <v>60.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="E41" t="n">
-        <v>26.6</v>
+        <v>30.1</v>
       </c>
       <c r="F41" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="H41" t="n">
-        <v>25.7</v>
+        <v>23.7</v>
       </c>
       <c r="I41" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="K41" t="n">
-        <v>74.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
+        <v>34</v>
+      </c>
+      <c r="O41" t="n">
         <v>37.2</v>
       </c>
-      <c r="O41" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q41" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="T41" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V41" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="W41" t="n">
-        <v>23</v>
+        <v>17.2</v>
       </c>
       <c r="X41" t="n">
-        <v>16.2</v>
+        <v>10.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>222.98</v>
+        <v>220.58</v>
       </c>
       <c r="AG41" t="n">
-        <v>-1.71</v>
+        <v>-2.41</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -5242,10 +5194,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>125.24</v>
+        <v>125</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.11</v>
+        <v>-4.53</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -5254,111 +5206,111 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>79.06</v>
+        <v>81.27</v>
       </c>
       <c r="AS41" t="n">
-        <v>14.03</v>
+        <v>14.01</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="BM41" t="n">
-        <v>30.8</v>
+        <v>34.44</v>
       </c>
       <c r="BN41" t="n">
         <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>1027.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP41" t="n">
-        <v>3503</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B42" t="n">
-        <v>156.3</v>
+        <v>167.7</v>
       </c>
       <c r="C42" t="n">
-        <v>60.3</v>
+        <v>68.2</v>
       </c>
       <c r="D42" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="E42" t="n">
-        <v>27.8</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K42" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N42" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T42" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W42" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Y42" t="n">
         <v>8</v>
       </c>
-      <c r="H42" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J42" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K42" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N42" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O42" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X42" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>10</v>
-      </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AF42" t="n">
-        <v>221.26</v>
+        <v>218.18</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.2</v>
+        <v>-5.83</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -5367,10 +5319,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>125.58</v>
+        <v>123.1</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.34</v>
+        <v>-1.9</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -5379,84 +5331,111 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>79.02</v>
+        <v>78.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.34</v>
+        <v>13.16</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="BM42" t="n">
-        <v>32.04</v>
+        <v>35.14</v>
       </c>
       <c r="BN42" t="n">
-        <v>6212.1</v>
+        <v>668.9</v>
       </c>
       <c r="BO42" t="n">
-        <v>1410.7</v>
+        <v>2177.3</v>
       </c>
       <c r="BP42" t="n">
-        <v>3322</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B43" t="n">
-        <v>132.9</v>
+        <v>167.8</v>
       </c>
       <c r="C43" t="n">
-        <v>56.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>34.6</v>
+        <v>32.8</v>
       </c>
       <c r="E43" t="n">
-        <v>24.6</v>
+        <v>30.7</v>
       </c>
       <c r="F43" t="n">
-        <v>8.1</v>
+        <v>4.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>40.8</v>
       </c>
       <c r="K43" t="n">
-        <v>98.3</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>38.1</v>
       </c>
       <c r="O43" t="n">
-        <v>39.1</v>
+        <v>42.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23.9</v>
       </c>
       <c r="V43" t="n">
-        <v>11.6</v>
+        <v>9.9</v>
       </c>
       <c r="W43" t="n">
-        <v>21.3</v>
+        <v>15.5</v>
       </c>
       <c r="X43" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="Y43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.300000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>221.88</v>
+        <v>212.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.79</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -5465,10 +5444,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>123.06</v>
+        <v>121.78</v>
       </c>
       <c r="AL43" t="n">
-        <v>-2.52</v>
+        <v>-1.32</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -5476,79 +5455,85 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>12.62</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="BM43" t="n">
-        <v>30.26</v>
+        <v>35.64</v>
       </c>
       <c r="BN43" t="n">
-        <v>0</v>
+        <v>10274.1</v>
       </c>
       <c r="BO43" t="n">
-        <v>677.9</v>
+        <v>2925.4</v>
       </c>
       <c r="BP43" t="n">
-        <v>676.6</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="B44" t="n">
-        <v>133.2</v>
+        <v>146.5</v>
       </c>
       <c r="C44" t="n">
-        <v>58.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>34.2</v>
+        <v>32.9</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>29.8</v>
       </c>
       <c r="F44" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="K44" t="n">
-        <v>96.7</v>
+        <v>100.9</v>
       </c>
       <c r="O44" t="n">
-        <v>38.7</v>
+        <v>34.4</v>
       </c>
       <c r="V44" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="X44" t="n">
-        <v>14.2</v>
+        <v>12.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AB44" t="n">
-        <v>-1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>223.58</v>
+        <v>214.64</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.7</v>
+        <v>3.23</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -5557,10 +5542,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>125.11</v>
+        <v>121</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.05</v>
+        <v>-0.78</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -5569,105 +5554,78 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="BM44" t="n">
-        <v>30.36</v>
+        <v>34.42</v>
       </c>
       <c r="BN44" t="n">
-        <v>0</v>
+        <v>10401.8</v>
       </c>
       <c r="BO44" t="n">
-        <v>1209</v>
+        <v>2042.8</v>
       </c>
       <c r="BP44" t="n">
-        <v>357.9</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46159</v>
+        <v>46165</v>
       </c>
       <c r="B45" t="n">
-        <v>156.7</v>
+        <v>142.1</v>
       </c>
       <c r="C45" t="n">
-        <v>65.40000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D45" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="E45" t="n">
-        <v>26.2</v>
+        <v>29.8</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J45" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="K45" t="n">
-        <v>75</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>36.7</v>
+        <v>101.4</v>
       </c>
       <c r="O45" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>23.1</v>
+        <v>35.2</v>
       </c>
       <c r="V45" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>13.1</v>
+        <v>16.5</v>
       </c>
       <c r="X45" t="n">
-        <v>10.6</v>
+        <v>12.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
         <v>15</v>
       </c>
       <c r="AA45" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>11.4</v>
+        <v>10.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AF45" t="n">
-        <v>223.6</v>
+        <v>218.66</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.11</v>
+        <v>4.02</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5676,10 +5634,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>125.11</v>
+        <v>124.39</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5687,112 +5645,79 @@
       <c r="AN45" t="n">
         <v>142</v>
       </c>
-      <c r="AP45" t="n">
-        <v>83.37</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>14</v>
-      </c>
       <c r="BL45" s="1" t="n">
-        <v>46159</v>
+        <v>46165</v>
       </c>
       <c r="BM45" t="n">
-        <v>30.74</v>
+        <v>34.27</v>
       </c>
       <c r="BN45" t="n">
-        <v>0</v>
+        <v>2566.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>1207.3</v>
+        <v>1843.4</v>
       </c>
       <c r="BP45" t="n">
-        <v>1838.3</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46160</v>
+        <v>46166</v>
       </c>
       <c r="B46" t="n">
-        <v>169.4</v>
+        <v>138</v>
       </c>
       <c r="C46" t="n">
-        <v>69.09999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="D46" t="n">
-        <v>34.8</v>
+        <v>31.8</v>
       </c>
       <c r="E46" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="F46" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H46" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J46" t="n">
-        <v>40.5</v>
+        <v>6.6</v>
       </c>
       <c r="K46" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N46" t="n">
-        <v>33.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>23.3</v>
+        <v>39.6</v>
       </c>
       <c r="V46" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W46" t="n">
-        <v>16.2</v>
+        <v>17.6</v>
       </c>
       <c r="X46" t="n">
-        <v>10.6</v>
+        <v>13.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA46" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>14.2</v>
+        <v>9.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>9.1</v>
+        <v>5.6</v>
       </c>
       <c r="AF46" t="n">
-        <v>223.66</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="n">
-        <v>-3.09</v>
+        <v>1.34</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5801,10 +5726,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>129.53</v>
+        <v>126.54</v>
       </c>
       <c r="AL46" t="n">
-        <v>4.42</v>
+        <v>2.15</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5812,112 +5737,106 @@
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>81.22</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>13.69</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46160</v>
+        <v>46166</v>
       </c>
       <c r="BM46" t="n">
-        <v>33.76</v>
+        <v>35.63</v>
       </c>
       <c r="BN46" t="n">
-        <v>0</v>
+        <v>422.9</v>
       </c>
       <c r="BO46" t="n">
-        <v>1003.3</v>
+        <v>926.5</v>
       </c>
       <c r="BP46" t="n">
-        <v>3599.2</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="B47" t="n">
-        <v>163.7</v>
+        <v>160.7</v>
       </c>
       <c r="C47" t="n">
-        <v>65.90000000000001</v>
+        <v>62</v>
       </c>
       <c r="D47" t="n">
-        <v>33.9</v>
+        <v>30.8</v>
       </c>
       <c r="E47" t="n">
-        <v>30.1</v>
+        <v>32.6</v>
       </c>
       <c r="F47" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="H47" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="I47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J47" t="n">
-        <v>39.6</v>
+        <v>41.1</v>
       </c>
       <c r="K47" t="n">
-        <v>73</v>
+        <v>73.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>34</v>
+        <v>37.4</v>
       </c>
       <c r="O47" t="n">
-        <v>37.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>22.8</v>
+        <v>24.4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>10.6</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>22.8</v>
+        <v>24.4</v>
       </c>
       <c r="V47" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="W47" t="n">
-        <v>17.2</v>
+        <v>19.4</v>
       </c>
       <c r="X47" t="n">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z47" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA47" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="AB47" t="n">
         <v>3.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>220.58</v>
+        <v>220</v>
       </c>
       <c r="AG47" t="n">
-        <v>-2.41</v>
+        <v>-0.75</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5926,10 +5845,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>125</v>
+        <v>126.54</v>
       </c>
       <c r="AL47" t="n">
-        <v>-4.53</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5938,111 +5857,111 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>81.27</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="AS47" t="n">
-        <v>14.01</v>
+        <v>13.37</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="BM47" t="n">
-        <v>34.44</v>
+        <v>36.56</v>
       </c>
       <c r="BN47" t="n">
-        <v>0</v>
+        <v>554.1</v>
       </c>
       <c r="BO47" t="n">
-        <v>1174.9</v>
+        <v>569.9</v>
       </c>
       <c r="BP47" t="n">
-        <v>3385.6</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="B48" t="n">
-        <v>167.7</v>
+        <v>164.5</v>
       </c>
       <c r="C48" t="n">
-        <v>68.2</v>
+        <v>66.5</v>
       </c>
       <c r="D48" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="E48" t="n">
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="F48" t="n">
-        <v>7.7</v>
+        <v>4.4</v>
       </c>
       <c r="H48" t="n">
-        <v>22.7</v>
+        <v>26</v>
       </c>
       <c r="I48" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>40.8</v>
+        <v>41.2</v>
       </c>
       <c r="K48" t="n">
-        <v>73.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M48" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N48" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="R48" t="n">
         <v>3.8</v>
       </c>
-      <c r="N48" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O48" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.8</v>
-      </c>
       <c r="S48" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="V48" t="n">
-        <v>4.4</v>
+        <v>9.1</v>
       </c>
       <c r="W48" t="n">
-        <v>18.3</v>
+        <v>21.2</v>
       </c>
       <c r="X48" t="n">
-        <v>11.4</v>
+        <v>15.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC48" t="n">
-        <v>13.7</v>
+        <v>11.7</v>
       </c>
       <c r="AD48" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="AF48" t="n">
-        <v>218.18</v>
+        <v>219.23</v>
       </c>
       <c r="AG48" t="n">
-        <v>-5.83</v>
+        <v>-2.93</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -6051,10 +5970,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>123.1</v>
+        <v>126.55</v>
       </c>
       <c r="AL48" t="n">
-        <v>-1.9</v>
+        <v>0.01</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -6063,111 +5982,111 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>78.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.16</v>
+        <v>13.77</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="BM48" t="n">
-        <v>35.14</v>
+        <v>37.15</v>
       </c>
       <c r="BN48" t="n">
-        <v>668.9</v>
+        <v>6026.3</v>
       </c>
       <c r="BO48" t="n">
-        <v>2177.3</v>
+        <v>593.2</v>
       </c>
       <c r="BP48" t="n">
-        <v>3522.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="B49" t="n">
-        <v>167.8</v>
+        <v>162.4</v>
       </c>
       <c r="C49" t="n">
-        <v>71.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="E49" t="n">
-        <v>30.7</v>
+        <v>27.1</v>
       </c>
       <c r="F49" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="H49" t="n">
         <v>26.1</v>
       </c>
       <c r="I49" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>40.8</v>
+        <v>41.1</v>
       </c>
       <c r="K49" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="N49" t="n">
-        <v>38.1</v>
+        <v>37</v>
       </c>
       <c r="O49" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="S49" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="V49" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W49" t="n">
-        <v>15.5</v>
+        <v>20.5</v>
       </c>
       <c r="X49" t="n">
-        <v>12.7</v>
+        <v>15.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>8.4</v>
+        <v>13.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AC49" t="n">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="AD49" t="n">
         <v>7.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>212.3</v>
+        <v>216.29</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -6176,10 +6095,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>121.78</v>
+        <v>126.45</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.32</v>
+        <v>-0.1</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -6188,84 +6107,111 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>71.68000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS49" t="n">
-        <v>12.62</v>
+        <v>12.96</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="BM49" t="n">
-        <v>35.64</v>
+        <v>32.3</v>
       </c>
       <c r="BN49" t="n">
-        <v>10274.1</v>
+        <v>12649</v>
       </c>
       <c r="BO49" t="n">
-        <v>2925.4</v>
+        <v>1123.4</v>
       </c>
       <c r="BP49" t="n">
-        <v>3588</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="B50" t="n">
-        <v>146.5</v>
+        <v>157.5</v>
       </c>
       <c r="C50" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="D50" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="E50" t="n">
-        <v>29.8</v>
+        <v>25.8</v>
       </c>
       <c r="F50" t="n">
-        <v>7.1</v>
+        <v>4.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>41.3</v>
       </c>
       <c r="K50" t="n">
-        <v>100.9</v>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="M50" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>34.7</v>
       </c>
       <c r="O50" t="n">
-        <v>34.4</v>
+        <v>40.8</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>24.2</v>
       </c>
       <c r="V50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>15.9</v>
+        <v>21.1</v>
       </c>
       <c r="X50" t="n">
-        <v>12.6</v>
+        <v>15.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>9</v>
+        <v>13.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AF50" t="n">
-        <v>214.64</v>
+        <v>216.91</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -6274,10 +6220,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>121</v>
+        <v>124.66</v>
       </c>
       <c r="AL50" t="n">
-        <v>-0.78</v>
+        <v>-1.79</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -6285,79 +6231,85 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>13.33</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="BM50" t="n">
-        <v>34.42</v>
+        <v>30.61</v>
       </c>
       <c r="BN50" t="n">
-        <v>10401.8</v>
+        <v>15239.7</v>
       </c>
       <c r="BO50" t="n">
-        <v>2042.8</v>
+        <v>1447.3</v>
       </c>
       <c r="BP50" t="n">
-        <v>3553.1</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46165</v>
+        <v>46171</v>
       </c>
       <c r="B51" t="n">
-        <v>142.1</v>
+        <v>135.7</v>
       </c>
       <c r="C51" t="n">
-        <v>63.8</v>
+        <v>62.2</v>
       </c>
       <c r="D51" t="n">
-        <v>32.1</v>
+        <v>32.7</v>
       </c>
       <c r="E51" t="n">
-        <v>29.8</v>
+        <v>25.3</v>
       </c>
       <c r="F51" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="K51" t="n">
-        <v>101.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>35.2</v>
+        <v>37.8</v>
       </c>
       <c r="V51" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="W51" t="n">
-        <v>16.5</v>
+        <v>20.4</v>
       </c>
       <c r="X51" t="n">
-        <v>12.2</v>
+        <v>16</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA51" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC51" t="n">
-        <v>10.1</v>
+        <v>12</v>
       </c>
       <c r="AD51" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>218.66</v>
+        <v>217.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>4.02</v>
+        <v>-0.72</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -6366,10 +6318,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>124.39</v>
+        <v>133</v>
       </c>
       <c r="AL51" t="n">
-        <v>3.39</v>
+        <v>8.34</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -6378,78 +6330,78 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46165</v>
+        <v>46171</v>
       </c>
       <c r="BM51" t="n">
-        <v>34.27</v>
+        <v>30.47</v>
       </c>
       <c r="BN51" t="n">
-        <v>2566.2</v>
+        <v>12907.2</v>
       </c>
       <c r="BO51" t="n">
-        <v>1843.4</v>
+        <v>1441.3</v>
       </c>
       <c r="BP51" t="n">
-        <v>3518.4</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46166</v>
+        <v>46172</v>
       </c>
       <c r="B52" t="n">
-        <v>138</v>
+        <v>130.4</v>
       </c>
       <c r="C52" t="n">
-        <v>60.6</v>
+        <v>58.6</v>
       </c>
       <c r="D52" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="E52" t="n">
-        <v>29.8</v>
+        <v>22.5</v>
       </c>
       <c r="F52" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="K52" t="n">
-        <v>98.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>39.6</v>
+        <v>37.7</v>
       </c>
       <c r="V52" t="n">
-        <v>8.800000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="W52" t="n">
-        <v>17.6</v>
+        <v>19.6</v>
       </c>
       <c r="X52" t="n">
-        <v>13.2</v>
+        <v>16.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
         <v>16</v>
       </c>
       <c r="AA52" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>9.4</v>
+        <v>12.3</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>220</v>
+        <v>217.82</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.34</v>
+        <v>0.32</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -6458,10 +6410,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>126.54</v>
+        <v>133</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -6470,105 +6422,105 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46166</v>
+        <v>46172</v>
       </c>
       <c r="BM52" t="n">
-        <v>35.63</v>
+        <v>29.35</v>
       </c>
       <c r="BN52" t="n">
-        <v>422.9</v>
+        <v>7367.2</v>
       </c>
       <c r="BO52" t="n">
-        <v>926.5</v>
+        <v>1684.4</v>
       </c>
       <c r="BP52" t="n">
-        <v>3432.2</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46167</v>
+        <v>46173</v>
       </c>
       <c r="B53" t="n">
-        <v>160.7</v>
+        <v>151</v>
       </c>
       <c r="C53" t="n">
-        <v>62</v>
+        <v>59.9</v>
       </c>
       <c r="D53" t="n">
-        <v>30.8</v>
+        <v>30.3</v>
       </c>
       <c r="E53" t="n">
-        <v>32.6</v>
+        <v>25.1</v>
       </c>
       <c r="F53" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>23.1</v>
+        <v>21.4</v>
       </c>
       <c r="I53" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K53" t="n">
-        <v>73.7</v>
+        <v>72.5</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="N53" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="O53" t="n">
-        <v>41.4</v>
+        <v>39.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="V53" t="n">
-        <v>8.9</v>
+        <v>12.6</v>
       </c>
       <c r="W53" t="n">
-        <v>19.4</v>
+        <v>22.1</v>
       </c>
       <c r="X53" t="n">
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>13.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>220</v>
+        <v>217.8</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.75</v>
+        <v>1.75</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -6577,10 +6529,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>126.54</v>
+        <v>125.03</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>-7.97</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -6589,111 +6541,111 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>80.18000000000001</v>
+        <v>81.81</v>
       </c>
       <c r="AS53" t="n">
-        <v>13.37</v>
+        <v>15.04</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46167</v>
+        <v>46173</v>
       </c>
       <c r="BM53" t="n">
-        <v>36.56</v>
+        <v>29.43</v>
       </c>
       <c r="BN53" t="n">
-        <v>554.1</v>
+        <v>5971.2</v>
       </c>
       <c r="BO53" t="n">
-        <v>569.9</v>
+        <v>1199.2</v>
       </c>
       <c r="BP53" t="n">
-        <v>3436.9</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B54" t="n">
-        <v>164.5</v>
+        <v>169</v>
       </c>
       <c r="C54" t="n">
-        <v>66.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="E54" t="n">
-        <v>31.6</v>
+        <v>35.9</v>
       </c>
       <c r="F54" t="n">
-        <v>4.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>26</v>
+        <v>21.3</v>
       </c>
       <c r="I54" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>41.2</v>
+        <v>42.2</v>
       </c>
       <c r="K54" t="n">
-        <v>76.5</v>
+        <v>73.2</v>
       </c>
       <c r="M54" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="N54" t="n">
-        <v>34.7</v>
+        <v>39.4</v>
       </c>
       <c r="O54" t="n">
-        <v>40.5</v>
+        <v>42.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="R54" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T54" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="V54" t="n">
-        <v>9.1</v>
+        <v>11.9</v>
       </c>
       <c r="W54" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="X54" t="n">
-        <v>15.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="AA54" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="AB54" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>7.3</v>
+        <v>9.9</v>
       </c>
       <c r="AF54" t="n">
-        <v>219.23</v>
+        <v>219.54</v>
       </c>
       <c r="AG54" t="n">
-        <v>-2.93</v>
+        <v>1.11</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6702,10 +6654,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>126.55</v>
+        <v>129.57</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.01</v>
+        <v>4.54</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -6714,111 +6666,111 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>75.90000000000001</v>
+        <v>83.89</v>
       </c>
       <c r="AS54" t="n">
-        <v>13.77</v>
+        <v>15.89</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="BM54" t="n">
-        <v>37.15</v>
+        <v>39.73</v>
       </c>
       <c r="BN54" t="n">
-        <v>6026.3</v>
+        <v>2846.5</v>
       </c>
       <c r="BO54" t="n">
-        <v>593.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP54" t="n">
-        <v>3525.8</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B55" t="n">
-        <v>162.4</v>
+        <v>174.1</v>
       </c>
       <c r="C55" t="n">
-        <v>67.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>32.7</v>
+        <v>33.9</v>
       </c>
       <c r="E55" t="n">
-        <v>27.1</v>
+        <v>37.8</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>26.1</v>
+        <v>20.9</v>
       </c>
       <c r="I55" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K55" t="n">
-        <v>76.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="O55" t="n">
-        <v>42.5</v>
+        <v>40.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="R55" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T55" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="V55" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="W55" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X55" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y55" t="n">
         <v>10</v>
       </c>
-      <c r="W55" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X55" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>9</v>
-      </c>
       <c r="Z55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA55" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AC55" t="n">
-        <v>12.2</v>
+        <v>14.3</v>
       </c>
       <c r="AD55" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AF55" t="n">
-        <v>216.29</v>
+        <v>220.65</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.62</v>
+        <v>-0.7</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6827,10 +6779,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>126.45</v>
+        <v>132.59</v>
       </c>
       <c r="AL55" t="n">
-        <v>-0.1</v>
+        <v>3.02</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -6839,111 +6791,93 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>75.38</v>
+        <v>83.73</v>
       </c>
       <c r="AS55" t="n">
-        <v>12.96</v>
+        <v>15.63</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="BM55" t="n">
-        <v>32.3</v>
+        <v>43.63</v>
       </c>
       <c r="BN55" t="n">
-        <v>12649</v>
+        <v>423.4</v>
       </c>
       <c r="BO55" t="n">
-        <v>1123.4</v>
+        <v>559.8</v>
       </c>
       <c r="BP55" t="n">
-        <v>3281.4</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B56" t="n">
-        <v>157.5</v>
+        <v>169.5</v>
       </c>
       <c r="C56" t="n">
-        <v>66.7</v>
+        <v>59.3</v>
       </c>
       <c r="D56" t="n">
-        <v>32.5</v>
+        <v>34.4</v>
       </c>
       <c r="E56" t="n">
-        <v>25.8</v>
+        <v>38.6</v>
       </c>
       <c r="F56" t="n">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="H56" t="n">
-        <v>26.1</v>
+        <v>24</v>
       </c>
       <c r="I56" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>41.3</v>
+        <v>40.9</v>
       </c>
       <c r="K56" t="n">
-        <v>76.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="N56" t="n">
-        <v>34.7</v>
+        <v>35.9</v>
       </c>
       <c r="O56" t="n">
-        <v>40.8</v>
+        <v>38.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="R56" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T56" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V56" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W56" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X56" t="n">
-        <v>15.4</v>
+        <v>23.7</v>
       </c>
       <c r="Y56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AF56" t="n">
-        <v>216.91</v>
+        <v>219.97</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.28</v>
+        <v>-0.68</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6952,10 +6886,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>124.66</v>
+        <v>130.34</v>
       </c>
       <c r="AL56" t="n">
-        <v>-1.79</v>
+        <v>-2.25</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -6964,66 +6898,93 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>76.8</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS56" t="n">
-        <v>13.33</v>
+        <v>13.98</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="BM56" t="n">
-        <v>30.61</v>
+        <v>42.19</v>
       </c>
       <c r="BN56" t="n">
-        <v>15239.7</v>
+        <v>56.3</v>
       </c>
       <c r="BO56" t="n">
-        <v>1447.3</v>
+        <v>612.6</v>
       </c>
       <c r="BP56" t="n">
-        <v>3587.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B57" t="n">
-        <v>135.7</v>
+        <v>171.5</v>
       </c>
       <c r="C57" t="n">
-        <v>62.2</v>
+        <v>57.9</v>
       </c>
       <c r="D57" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="E57" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H57" t="n">
         <v>25.3</v>
       </c>
-      <c r="F57" t="n">
-        <v>5.4</v>
+      <c r="I57" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>41.6</v>
       </c>
       <c r="K57" t="n">
-        <v>96.40000000000001</v>
+        <v>76.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>38</v>
       </c>
       <c r="O57" t="n">
-        <v>37.8</v>
+        <v>42.2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S57" t="n">
+        <v>12</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z57" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF57" t="n">
-        <v>217.5</v>
+        <v>223.97</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.72</v>
+        <v>0.96</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -7032,10 +6993,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>133</v>
+        <v>124.73</v>
       </c>
       <c r="AL57" t="n">
-        <v>8.34</v>
+        <v>-5.61</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -7043,61 +7004,67 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>14.85</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="BM57" t="n">
-        <v>30.47</v>
+        <v>47.76</v>
       </c>
       <c r="BN57" t="n">
-        <v>12907.2</v>
+        <v>33.2</v>
       </c>
       <c r="BO57" t="n">
-        <v>1441.3</v>
+        <v>1106.6</v>
       </c>
       <c r="BP57" t="n">
-        <v>3544.9</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46172</v>
+        <v>46178</v>
       </c>
       <c r="B58" t="n">
-        <v>130.4</v>
+        <v>152.8</v>
       </c>
       <c r="C58" t="n">
-        <v>58.6</v>
+        <v>57.9</v>
       </c>
       <c r="D58" t="n">
-        <v>32.2</v>
+        <v>36.9</v>
       </c>
       <c r="E58" t="n">
-        <v>22.5</v>
+        <v>40</v>
       </c>
       <c r="F58" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="K58" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>37.7</v>
+        <v>39</v>
       </c>
       <c r="Y58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>217.82</v>
+        <v>226.45</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.32</v>
+        <v>1.52</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -7109,7 +7076,7 @@
         <v>133</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>8.27</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -7118,87 +7085,60 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46172</v>
+        <v>46178</v>
       </c>
       <c r="BM58" t="n">
-        <v>29.35</v>
+        <v>47.09</v>
       </c>
       <c r="BN58" t="n">
-        <v>7367.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO58" t="n">
-        <v>1684.4</v>
+        <v>1116</v>
       </c>
       <c r="BP58" t="n">
-        <v>3545.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46173</v>
+        <v>46179</v>
       </c>
       <c r="B59" t="n">
-        <v>151</v>
+        <v>143.6</v>
       </c>
       <c r="C59" t="n">
-        <v>59.9</v>
+        <v>54.1</v>
       </c>
       <c r="D59" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="E59" t="n">
-        <v>25.1</v>
+        <v>37.7</v>
       </c>
       <c r="F59" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H59" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J59" t="n">
-        <v>41.3</v>
+        <v>7.9</v>
       </c>
       <c r="K59" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N59" t="n">
-        <v>37.1</v>
+        <v>93.5</v>
       </c>
       <c r="O59" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>23.9</v>
+        <v>40.1</v>
       </c>
       <c r="Y59" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Z59" t="n">
         <v>18</v>
       </c>
       <c r="AA59" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF59" t="n">
-        <v>217.8</v>
+        <v>228.57</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -7207,10 +7147,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>125.03</v>
+        <v>133</v>
       </c>
       <c r="AL59" t="n">
-        <v>-7.97</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -7218,94 +7158,88 @@
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>81.81</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>15.04</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46173</v>
+        <v>46179</v>
       </c>
       <c r="BM59" t="n">
-        <v>29.43</v>
+        <v>45.96</v>
       </c>
       <c r="BN59" t="n">
-        <v>5971.2</v>
+        <v>30.9</v>
       </c>
       <c r="BO59" t="n">
-        <v>1199.2</v>
+        <v>582.3</v>
       </c>
       <c r="BP59" t="n">
-        <v>3351.7</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46174</v>
+        <v>46180</v>
       </c>
       <c r="B60" t="n">
-        <v>169</v>
+        <v>161.8</v>
       </c>
       <c r="C60" t="n">
-        <v>66.59999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="D60" t="n">
-        <v>33.1</v>
+        <v>31.9</v>
       </c>
       <c r="E60" t="n">
-        <v>35.9</v>
+        <v>38.1</v>
       </c>
       <c r="F60" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>21.3</v>
+        <v>24.9</v>
       </c>
       <c r="I60" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>42.2</v>
+        <v>40.6</v>
       </c>
       <c r="K60" t="n">
-        <v>73.2</v>
+        <v>75.3</v>
       </c>
       <c r="M60" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
+        <v>36</v>
+      </c>
+      <c r="O60" t="n">
         <v>39.4</v>
       </c>
-      <c r="O60" t="n">
-        <v>42.1</v>
-      </c>
       <c r="Q60" t="n">
-        <v>24</v>
+        <v>19.4</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
+        <v>11</v>
+      </c>
+      <c r="T60" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z60" t="n">
         <v>16</v>
       </c>
-      <c r="T60" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>15</v>
-      </c>
       <c r="AA60" t="n">
-        <v>11.9</v>
+        <v>15.7</v>
       </c>
       <c r="AF60" t="n">
-        <v>219.54</v>
+        <v>228.53</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -7314,10 +7248,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.57</v>
+        <v>128.43</v>
       </c>
       <c r="AL60" t="n">
-        <v>4.54</v>
+        <v>-4.57</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -7326,60 +7260,54 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>83.89</v>
+        <v>85.77</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.89</v>
+        <v>15.64</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46174</v>
+        <v>46180</v>
       </c>
       <c r="BM60" t="n">
-        <v>39.73</v>
+        <v>42.04</v>
       </c>
       <c r="BN60" t="n">
-        <v>2846.5</v>
+        <v>39.6</v>
       </c>
       <c r="BO60" t="n">
-        <v>800.7</v>
+        <v>369.2</v>
       </c>
       <c r="BP60" t="n">
-        <v>3191.9</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B61" t="n">
-        <v>146.5</v>
+        <v>155.1</v>
       </c>
       <c r="C61" t="n">
-        <v>57.7</v>
+        <v>61.8</v>
       </c>
       <c r="D61" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="E61" t="n">
-        <v>39.1</v>
+        <v>41.7</v>
       </c>
       <c r="F61" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="Y61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA61" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>219.98</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>-0.7</v>
+        <v>13</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -7391,7 +7319,7 @@
         <v>133</v>
       </c>
       <c r="AL61" t="n">
-        <v>3.43</v>
+        <v>4.57</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -7400,48 +7328,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>43.63</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>423.4</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>559.8</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>3084.2</v>
+        <v>46181</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B62" t="n">
-        <v>151.9</v>
+        <v>155.3</v>
       </c>
       <c r="C62" t="n">
-        <v>60.7</v>
+        <v>62.6</v>
       </c>
       <c r="D62" t="n">
-        <v>33.8</v>
+        <v>34.2</v>
       </c>
       <c r="E62" t="n">
-        <v>39.6</v>
+        <v>42.1</v>
       </c>
       <c r="F62" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y62" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Z62" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -7462,7 +7378,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -663,15 +663,6 @@
       <c r="T2" t="n">
         <v>20.3</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>23</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y2" t="n">
         <v>11</v>
       </c>
@@ -680,15 +671,6 @@
       </c>
       <c r="AA2" t="n">
         <v>16</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14.5</v>
       </c>
       <c r="AF2" t="n">
         <v>229.32</v>
@@ -773,15 +755,6 @@
       <c r="T3" t="n">
         <v>16</v>
       </c>
-      <c r="V3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X3" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
@@ -790,15 +763,6 @@
       </c>
       <c r="AA3" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13.6</v>
       </c>
       <c r="AF3" t="n">
         <v>235.81</v>
@@ -898,15 +862,6 @@
       <c r="T4" t="n">
         <v>13</v>
       </c>
-      <c r="V4" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y4" t="n">
         <v>13</v>
       </c>
@@ -915,15 +870,6 @@
       </c>
       <c r="AA4" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>7.2</v>
       </c>
       <c r="AF4" t="n">
         <v>235.83</v>
@@ -1023,15 +969,6 @@
       <c r="T5" t="n">
         <v>16</v>
       </c>
-      <c r="V5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y5" t="n">
         <v>17</v>
       </c>
@@ -1040,15 +977,6 @@
       </c>
       <c r="AA5" t="n">
         <v>19</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AF5" t="n">
         <v>235.47</v>
@@ -1148,15 +1076,6 @@
       <c r="T6" t="n">
         <v>17</v>
       </c>
-      <c r="V6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>22.9</v>
-      </c>
       <c r="Y6" t="n">
         <v>18</v>
       </c>
@@ -1165,15 +1084,6 @@
       </c>
       <c r="AA6" t="n">
         <v>21</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>7.1</v>
       </c>
       <c r="AF6" t="n">
         <v>230.5</v>
@@ -1273,15 +1183,6 @@
       <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="V7" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X7" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Y7" t="n">
         <v>20</v>
       </c>
@@ -1290,15 +1191,6 @@
       </c>
       <c r="AA7" t="n">
         <v>21</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>7.9</v>
       </c>
       <c r="AF7" t="n">
         <v>225.8</v>
@@ -1398,15 +1290,6 @@
       <c r="T8" t="n">
         <v>17</v>
       </c>
-      <c r="V8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>22</v>
-      </c>
       <c r="Y8" t="n">
         <v>19</v>
       </c>
@@ -1415,15 +1298,6 @@
       </c>
       <c r="AA8" t="n">
         <v>22</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>10.9</v>
       </c>
       <c r="AF8" t="n">
         <v>220</v>
@@ -1508,15 +1382,6 @@
       <c r="T9" t="n">
         <v>17</v>
       </c>
-      <c r="V9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Y9" t="n">
         <v>17</v>
       </c>
@@ -1525,15 +1390,6 @@
       </c>
       <c r="AA9" t="n">
         <v>20.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6.8</v>
       </c>
       <c r="AF9" t="n">
         <v>216.02</v>
@@ -1612,15 +1468,6 @@
       <c r="T10" t="n">
         <v>17</v>
       </c>
-      <c r="V10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>30</v>
-      </c>
-      <c r="X10" t="n">
-        <v>24.3</v>
-      </c>
       <c r="Y10" t="n">
         <v>15</v>
       </c>
@@ -1629,15 +1476,6 @@
       </c>
       <c r="AA10" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.9</v>
       </c>
       <c r="AF10" t="n">
         <v>216.08</v>
@@ -1731,15 +1569,6 @@
       <c r="T11" t="n">
         <v>17</v>
       </c>
-      <c r="V11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>28</v>
-      </c>
-      <c r="X11" t="n">
-        <v>23.9</v>
-      </c>
       <c r="Y11" t="n">
         <v>16</v>
       </c>
@@ -1748,15 +1577,6 @@
       </c>
       <c r="AA11" t="n">
         <v>19</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.4</v>
       </c>
       <c r="AF11" t="n">
         <v>216.1</v>
@@ -1856,15 +1676,6 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1873,15 +1684,6 @@
       </c>
       <c r="AA12" t="n">
         <v>16</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.2</v>
       </c>
       <c r="AF12" t="n">
         <v>217.8</v>
@@ -1981,15 +1783,6 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>18</v>
-      </c>
-      <c r="X13" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y13" t="n">
         <v>10</v>
       </c>
@@ -1998,15 +1791,6 @@
       </c>
       <c r="AA13" t="n">
         <v>14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>6.2</v>
       </c>
       <c r="AF13" t="n">
         <v>213</v>
@@ -2106,15 +1890,6 @@
       <c r="T14" t="n">
         <v>21.5</v>
       </c>
-      <c r="V14" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>18.2</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -2123,15 +1898,6 @@
       </c>
       <c r="AA14" t="n">
         <v>16.2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6.6</v>
       </c>
       <c r="AF14" t="n">
         <v>210.3</v>
@@ -2231,15 +1997,6 @@
       <c r="T15" t="n">
         <v>19.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X15" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
@@ -2248,15 +2005,6 @@
       </c>
       <c r="AA15" t="n">
         <v>17.7</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>10.3</v>
       </c>
       <c r="AF15" t="n">
         <v>214.63</v>
@@ -2329,15 +2077,6 @@
       <c r="O16" t="n">
         <v>28.5</v>
       </c>
-      <c r="V16" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>18.4</v>
-      </c>
       <c r="Y16" t="n">
         <v>12</v>
       </c>
@@ -2346,15 +2085,6 @@
       </c>
       <c r="AA16" t="n">
         <v>18</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.5</v>
       </c>
       <c r="AF16" t="n">
         <v>213.96</v>
@@ -2415,15 +2145,6 @@
       <c r="O17" t="n">
         <v>36.4</v>
       </c>
-      <c r="V17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>18.5</v>
-      </c>
       <c r="Y17" t="n">
         <v>14</v>
       </c>
@@ -2432,15 +2153,6 @@
       </c>
       <c r="AA17" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.7</v>
       </c>
       <c r="AF17" t="n">
         <v>212.08</v>
@@ -2528,15 +2240,6 @@
       <c r="T18" t="n">
         <v>16.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19</v>
-      </c>
       <c r="Y18" t="n">
         <v>12</v>
       </c>
@@ -2545,15 +2248,6 @@
       </c>
       <c r="AA18" t="n">
         <v>13.4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.1</v>
       </c>
       <c r="AF18" t="n">
         <v>212.1</v>
@@ -2653,15 +2347,6 @@
       <c r="T19" t="n">
         <v>24.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.5</v>
-      </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
@@ -2670,15 +2355,6 @@
       </c>
       <c r="AA19" t="n">
         <v>11.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>6.1</v>
       </c>
       <c r="AF19" t="n">
         <v>211.95</v>
@@ -2778,15 +2454,6 @@
       <c r="T20" t="n">
         <v>21.8</v>
       </c>
-      <c r="V20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y20" t="n">
         <v>10</v>
       </c>
@@ -2795,15 +2462,6 @@
       </c>
       <c r="AA20" t="n">
         <v>15.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>8.300000000000001</v>
       </c>
       <c r="AF20" t="n">
         <v>208.67</v>
@@ -2903,15 +2561,6 @@
       <c r="T21" t="n">
         <v>21</v>
       </c>
-      <c r="V21" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X21" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2920,15 +2569,6 @@
       </c>
       <c r="AA21" t="n">
         <v>16</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>7.3</v>
       </c>
       <c r="AF21" t="n">
         <v>208.07</v>
@@ -2995,15 +2635,6 @@
       <c r="F22" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V22" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.8</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -3012,15 +2643,6 @@
       </c>
       <c r="AA22" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>7.2</v>
       </c>
       <c r="AF22" t="n">
         <v>205.66</v>
@@ -3081,15 +2703,6 @@
       <c r="F23" t="n">
         <v>9.1</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X23" t="n">
-        <v>18</v>
-      </c>
       <c r="Y23" t="n">
         <v>13</v>
       </c>
@@ -3098,15 +2711,6 @@
       </c>
       <c r="AA23" t="n">
         <v>19</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.4</v>
       </c>
       <c r="AF23" t="n">
         <v>215.07</v>
@@ -3167,15 +2771,6 @@
       <c r="F24" t="n">
         <v>8.6</v>
       </c>
-      <c r="V24" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>17</v>
-      </c>
       <c r="Y24" t="n">
         <v>13</v>
       </c>
@@ -3184,15 +2779,6 @@
       </c>
       <c r="AA24" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
         <v>218.94</v>
@@ -3286,15 +2872,6 @@
       <c r="T25" t="n">
         <v>22.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W25" t="n">
-        <v>21</v>
-      </c>
-      <c r="X25" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>5</v>
       </c>
@@ -3303,15 +2880,6 @@
       </c>
       <c r="AA25" t="n">
         <v>11.1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>6.8</v>
       </c>
       <c r="AF25" t="n">
         <v>216.4</v>
@@ -3411,15 +2979,6 @@
       <c r="T26" t="n">
         <v>22.2</v>
       </c>
-      <c r="V26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>10</v>
       </c>
@@ -3428,15 +2987,6 @@
       </c>
       <c r="AA26" t="n">
         <v>16.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>224.66</v>
@@ -3536,15 +3086,6 @@
       <c r="T27" t="n">
         <v>22.9</v>
       </c>
-      <c r="V27" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Y27" t="n">
         <v>13</v>
       </c>
@@ -3553,15 +3094,6 @@
       </c>
       <c r="AA27" t="n">
         <v>20.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>7.5</v>
       </c>
       <c r="AF27" t="n">
         <v>223.02</v>
@@ -3661,15 +3193,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="X28" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>19</v>
       </c>
@@ -3678,15 +3201,6 @@
       </c>
       <c r="AA28" t="n">
         <v>22.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>6.9</v>
       </c>
       <c r="AF28" t="n">
         <v>225.57</v>
@@ -3786,15 +3300,6 @@
       <c r="T29" t="n">
         <v>20.6</v>
       </c>
-      <c r="V29" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X29" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y29" t="n">
         <v>15</v>
       </c>
@@ -3803,15 +3308,6 @@
       </c>
       <c r="AA29" t="n">
         <v>13.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.6</v>
       </c>
       <c r="AF29" t="n">
         <v>232.44</v>
@@ -3884,15 +3380,6 @@
       <c r="O30" t="n">
         <v>36.5</v>
       </c>
-      <c r="V30" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W30" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X30" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Y30" t="n">
         <v>7</v>
       </c>
@@ -3901,15 +3388,6 @@
       </c>
       <c r="AA30" t="n">
         <v>10</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
         <v>228.64</v>
@@ -3976,15 +3454,6 @@
       <c r="O31" t="n">
         <v>34.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W31" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y31" t="n">
         <v>6</v>
       </c>
@@ -3993,15 +3462,6 @@
       </c>
       <c r="AA31" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4</v>
       </c>
       <c r="AF31" t="n">
         <v>225.16</v>
@@ -4095,15 +3555,6 @@
       <c r="T32" t="n">
         <v>23.3</v>
       </c>
-      <c r="V32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W32" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X32" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y32" t="n">
         <v>3</v>
       </c>
@@ -4112,15 +3563,6 @@
       </c>
       <c r="AA32" t="n">
         <v>10.3</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>6.8</v>
       </c>
       <c r="AF32" t="n">
         <v>225.13</v>
@@ -4220,15 +3662,6 @@
       <c r="T33" t="n">
         <v>23.1</v>
       </c>
-      <c r="V33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y33" t="n">
         <v>4</v>
       </c>
@@ -4237,15 +3670,6 @@
       </c>
       <c r="AA33" t="n">
         <v>12.9</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>7.7</v>
       </c>
       <c r="AF33" t="n">
         <v>223.85</v>
@@ -4345,15 +3769,6 @@
       <c r="T34" t="n">
         <v>23.1</v>
       </c>
-      <c r="V34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X34" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>9</v>
       </c>
@@ -4362,15 +3777,6 @@
       </c>
       <c r="AA34" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>8.6</v>
       </c>
       <c r="AF34" t="n">
         <v>222.91</v>
@@ -4470,15 +3876,6 @@
       <c r="T35" t="n">
         <v>22.7</v>
       </c>
-      <c r="V35" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>23</v>
-      </c>
-      <c r="X35" t="n">
-        <v>16.2</v>
-      </c>
       <c r="Y35" t="n">
         <v>9</v>
       </c>
@@ -4487,15 +3884,6 @@
       </c>
       <c r="AA35" t="n">
         <v>12.6</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>5.9</v>
       </c>
       <c r="AF35" t="n">
         <v>222.98</v>
@@ -4595,15 +3983,6 @@
       <c r="T36" t="n">
         <v>23.5</v>
       </c>
-      <c r="V36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X36" t="n">
-        <v>15.9</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -4612,15 +3991,6 @@
       </c>
       <c r="AA36" t="n">
         <v>12.2</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>6.6</v>
       </c>
       <c r="AF36" t="n">
         <v>221.26</v>
@@ -4693,15 +4063,6 @@
       <c r="O37" t="n">
         <v>39.1</v>
       </c>
-      <c r="V37" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W37" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y37" t="n">
         <v>8</v>
       </c>
@@ -4710,15 +4071,6 @@
       </c>
       <c r="AA37" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>5.2</v>
       </c>
       <c r="AF37" t="n">
         <v>221.88</v>
@@ -4785,15 +4137,6 @@
       <c r="O38" t="n">
         <v>38.7</v>
       </c>
-      <c r="V38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -4802,15 +4145,6 @@
       </c>
       <c r="AA38" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4</v>
       </c>
       <c r="AF38" t="n">
         <v>223.58</v>
@@ -4904,15 +4238,6 @@
       <c r="T39" t="n">
         <v>23.1</v>
       </c>
-      <c r="V39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W39" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y39" t="n">
         <v>9</v>
       </c>
@@ -4921,15 +4246,6 @@
       </c>
       <c r="AA39" t="n">
         <v>11.1</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>5.7</v>
       </c>
       <c r="AF39" t="n">
         <v>223.6</v>
@@ -5029,15 +4345,6 @@
       <c r="T40" t="n">
         <v>23.3</v>
       </c>
-      <c r="V40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y40" t="n">
         <v>3</v>
       </c>
@@ -5046,15 +4353,6 @@
       </c>
       <c r="AA40" t="n">
         <v>10.7</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>9.1</v>
       </c>
       <c r="AF40" t="n">
         <v>223.66</v>
@@ -5154,15 +4452,6 @@
       <c r="T41" t="n">
         <v>22.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W41" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X41" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>6</v>
       </c>
@@ -5171,15 +4460,6 @@
       </c>
       <c r="AA41" t="n">
         <v>12.3</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>8.5</v>
       </c>
       <c r="AF41" t="n">
         <v>220.58</v>
@@ -5279,15 +4559,6 @@
       <c r="T42" t="n">
         <v>23.7</v>
       </c>
-      <c r="V42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W42" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X42" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y42" t="n">
         <v>8</v>
       </c>
@@ -5296,15 +4567,6 @@
       </c>
       <c r="AA42" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>8.4</v>
       </c>
       <c r="AF42" t="n">
         <v>218.18</v>
@@ -5404,15 +4666,6 @@
       <c r="T43" t="n">
         <v>23.9</v>
       </c>
-      <c r="V43" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W43" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X43" t="n">
-        <v>12.7</v>
-      </c>
       <c r="Y43" t="n">
         <v>6</v>
       </c>
@@ -5421,15 +4674,6 @@
       </c>
       <c r="AA43" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>7.8</v>
       </c>
       <c r="AF43" t="n">
         <v>212.3</v>
@@ -5502,15 +4746,6 @@
       <c r="O44" t="n">
         <v>34.4</v>
       </c>
-      <c r="V44" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X44" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>5</v>
       </c>
@@ -5519,15 +4754,6 @@
       </c>
       <c r="AA44" t="n">
         <v>9</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>5.8</v>
       </c>
       <c r="AF44" t="n">
         <v>214.64</v>
@@ -5594,15 +4820,6 @@
       <c r="O45" t="n">
         <v>35.2</v>
       </c>
-      <c r="V45" t="n">
-        <v>8</v>
-      </c>
-      <c r="W45" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X45" t="n">
-        <v>12.2</v>
-      </c>
       <c r="Y45" t="n">
         <v>10</v>
       </c>
@@ -5611,15 +4828,6 @@
       </c>
       <c r="AA45" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>6</v>
       </c>
       <c r="AF45" t="n">
         <v>218.66</v>
@@ -5686,15 +4894,6 @@
       <c r="O46" t="n">
         <v>39.6</v>
       </c>
-      <c r="V46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W46" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y46" t="n">
         <v>9</v>
       </c>
@@ -5703,15 +4902,6 @@
       </c>
       <c r="AA46" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>5.6</v>
       </c>
       <c r="AF46" t="n">
         <v>220</v>
@@ -5805,15 +4995,6 @@
       <c r="T47" t="n">
         <v>24.4</v>
       </c>
-      <c r="V47" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X47" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y47" t="n">
         <v>9</v>
       </c>
@@ -5822,15 +5003,6 @@
       </c>
       <c r="AA47" t="n">
         <v>12.7</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>8.6</v>
       </c>
       <c r="AF47" t="n">
         <v>220</v>
@@ -5930,15 +5102,6 @@
       <c r="T48" t="n">
         <v>24.1</v>
       </c>
-      <c r="V48" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="X48" t="n">
-        <v>15.1</v>
-      </c>
       <c r="Y48" t="n">
         <v>7.2</v>
       </c>
@@ -5947,15 +5110,6 @@
       </c>
       <c r="AA48" t="n">
         <v>12.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>7.3</v>
       </c>
       <c r="AF48" t="n">
         <v>219.23</v>
@@ -6055,15 +5209,6 @@
       <c r="T49" t="n">
         <v>24.2</v>
       </c>
-      <c r="V49" t="n">
-        <v>10</v>
-      </c>
-      <c r="W49" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y49" t="n">
         <v>9</v>
       </c>
@@ -6072,15 +5217,6 @@
       </c>
       <c r="AA49" t="n">
         <v>13.3</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>7.8</v>
       </c>
       <c r="AF49" t="n">
         <v>216.29</v>
@@ -6180,15 +5316,6 @@
       <c r="T50" t="n">
         <v>24.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W50" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X50" t="n">
-        <v>15.4</v>
-      </c>
       <c r="Y50" t="n">
         <v>11</v>
       </c>
@@ -6197,15 +5324,6 @@
       </c>
       <c r="AA50" t="n">
         <v>13.8</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>7.6</v>
       </c>
       <c r="AF50" t="n">
         <v>216.91</v>
@@ -6278,15 +5396,6 @@
       <c r="O51" t="n">
         <v>37.8</v>
       </c>
-      <c r="V51" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="X51" t="n">
-        <v>16</v>
-      </c>
       <c r="Y51" t="n">
         <v>12</v>
       </c>
@@ -6295,15 +5404,6 @@
       </c>
       <c r="AA51" t="n">
         <v>14</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.4</v>
       </c>
       <c r="AF51" t="n">
         <v>217.5</v>
@@ -6370,15 +5470,6 @@
       <c r="O52" t="n">
         <v>37.7</v>
       </c>
-      <c r="V52" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W52" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y52" t="n">
         <v>10</v>
       </c>
@@ -6387,15 +5478,6 @@
       </c>
       <c r="AA52" t="n">
         <v>13</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>7.9</v>
       </c>
       <c r="AF52" t="n">
         <v>217.82</v>
@@ -6489,15 +5571,6 @@
       <c r="T53" t="n">
         <v>23.9</v>
       </c>
-      <c r="V53" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y53" t="n">
         <v>3</v>
       </c>
@@ -6506,15 +5579,6 @@
       </c>
       <c r="AA53" t="n">
         <v>12</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>6.2</v>
       </c>
       <c r="AF53" t="n">
         <v>217.8</v>
@@ -6614,15 +5678,6 @@
       <c r="T54" t="n">
         <v>24</v>
       </c>
-      <c r="V54" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W54" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X54" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y54" t="n">
         <v>10</v>
       </c>
@@ -6631,15 +5686,6 @@
       </c>
       <c r="AA54" t="n">
         <v>11.9</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.9</v>
       </c>
       <c r="AF54" t="n">
         <v>219.54</v>
@@ -6739,15 +5785,6 @@
       <c r="T55" t="n">
         <v>23.9</v>
       </c>
-      <c r="V55" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W55" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X55" t="n">
-        <v>17.9</v>
-      </c>
       <c r="Y55" t="n">
         <v>10</v>
       </c>
@@ -6756,15 +5793,6 @@
       </c>
       <c r="AA55" t="n">
         <v>14.1</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>9.4</v>
       </c>
       <c r="AF55" t="n">
         <v>220.65</v>
@@ -7329,6 +6357,18 @@
       </c>
       <c r="BL61" s="1" t="n">
         <v>46181</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>1136.8</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>3331.2</v>
       </c>
     </row>
     <row r="62">

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,31 +628,31 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="B2" t="n">
-        <v>124.2</v>
+        <v>110</v>
       </c>
       <c r="C2" t="n">
-        <v>27.8</v>
+        <v>22.3</v>
       </c>
       <c r="D2" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="E2" t="n">
-        <v>35.1</v>
+        <v>27.2</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="K2" t="n">
-        <v>71.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.3</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -661,22 +661,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>20.3</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>229.32</v>
+        <v>235.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>6.49</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -685,10 +685,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>130.56</v>
+        <v>134.07</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.08</v>
+        <v>3.52</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="BM2" t="n">
         <v>54.51</v>
@@ -720,13 +720,13 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B3" t="n">
-        <v>110</v>
+        <v>108.2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="n">
         <v>37.7</v>
@@ -737,14 +737,29 @@
       <c r="F3" t="n">
         <v>11.5</v>
       </c>
+      <c r="H3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32.7</v>
+      </c>
       <c r="K3" t="n">
         <v>71.59999999999999</v>
       </c>
+      <c r="M3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>31.5</v>
+      </c>
       <c r="O3" t="n">
         <v>34.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -753,22 +768,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>235.81</v>
+        <v>235.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.49</v>
+        <v>-235.81</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -780,7 +795,7 @@
         <v>134.07</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.52</v>
+        <v>-134.07</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -795,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="BM3" t="n">
         <v>54.51</v>
@@ -812,46 +827,46 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B4" t="n">
-        <v>108.2</v>
+        <v>119.7</v>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>25.9</v>
       </c>
       <c r="D4" t="n">
-        <v>37.7</v>
+        <v>38.7</v>
       </c>
       <c r="E4" t="n">
-        <v>27.2</v>
+        <v>34.5</v>
       </c>
       <c r="F4" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>22.1</v>
+        <v>20.5</v>
       </c>
       <c r="I4" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>32.7</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>71.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="M4" t="n">
         <v>1.9</v>
       </c>
       <c r="N4" t="n">
-        <v>31.5</v>
+        <v>30.6</v>
       </c>
       <c r="O4" t="n">
-        <v>34.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -860,22 +875,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>235.83</v>
+        <v>235.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>-235.81</v>
+        <v>-4.98</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -884,10 +899,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>134.07</v>
+        <v>136.17</v>
       </c>
       <c r="AL4" t="n">
-        <v>-134.07</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -902,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="BM4" t="n">
         <v>54.51</v>
@@ -919,46 +934,46 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B5" t="n">
-        <v>119.7</v>
+        <v>116.54</v>
       </c>
       <c r="C5" t="n">
-        <v>25.9</v>
+        <v>23.39</v>
       </c>
       <c r="D5" t="n">
-        <v>38.7</v>
+        <v>36.98</v>
       </c>
       <c r="E5" t="n">
-        <v>34.5</v>
+        <v>35.59</v>
       </c>
       <c r="F5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="H5" t="n">
         <v>20.5</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
       <c r="K5" t="n">
         <v>62.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>30.6</v>
+        <v>29.2</v>
       </c>
       <c r="O5" t="n">
         <v>31.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -967,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" t="n">
         <v>21</v>
       </c>
-      <c r="AA5" t="n">
-        <v>19</v>
-      </c>
       <c r="AF5" t="n">
-        <v>235.47</v>
+        <v>230.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.98</v>
+        <v>-4.67</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -991,10 +1006,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>136.17</v>
+        <v>136.01</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.1</v>
+        <v>-0.16</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1009,13 +1024,13 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="BM5" t="n">
-        <v>54.51</v>
+        <v>37.84</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>285.1</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1026,40 +1041,40 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B6" t="n">
-        <v>116.54</v>
+        <v>117.05</v>
       </c>
       <c r="C6" t="n">
-        <v>23.39</v>
+        <v>23.91</v>
       </c>
       <c r="D6" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
       <c r="E6" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="F6" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="H6" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J6" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="K6" t="n">
         <v>62.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N6" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="O6" t="n">
         <v>31.8</v>
@@ -1077,19 +1092,19 @@
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>230.5</v>
+        <v>225.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>-4.67</v>
+        <v>-5.78</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1098,10 +1113,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>136.01</v>
+        <v>132.41</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.16</v>
+        <v>-3.6</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1116,13 +1131,13 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="BM6" t="n">
-        <v>37.84</v>
+        <v>41.59</v>
       </c>
       <c r="BN6" t="n">
-        <v>285.1</v>
+        <v>334.1</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1133,40 +1148,40 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B7" t="n">
-        <v>117.05</v>
+        <v>117.63</v>
       </c>
       <c r="C7" t="n">
-        <v>23.91</v>
+        <v>24.3</v>
       </c>
       <c r="D7" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="E7" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="F7" t="n">
-        <v>10.56</v>
+        <v>10.75</v>
       </c>
       <c r="H7" t="n">
         <v>22.3</v>
       </c>
       <c r="I7" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K7" t="n">
         <v>62.9</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N7" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="O7" t="n">
         <v>31.8</v>
@@ -1184,19 +1199,19 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA7" t="n">
         <v>22</v>
       </c>
-      <c r="AA7" t="n">
-        <v>21</v>
-      </c>
       <c r="AF7" t="n">
-        <v>225.8</v>
+        <v>220</v>
       </c>
       <c r="AG7" t="n">
-        <v>-5.78</v>
+        <v>-2.67</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1205,10 +1220,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>132.41</v>
+        <v>131.69</v>
       </c>
       <c r="AL7" t="n">
-        <v>-3.6</v>
+        <v>-0.72</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1223,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BM7" t="n">
-        <v>41.59</v>
+        <v>42.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>334.1</v>
+        <v>106.5</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1240,41 +1255,26 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B8" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D8" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E8" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F8" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K8" t="n">
         <v>62.9</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O8" t="n">
         <v>31.8</v>
       </c>
@@ -1291,19 +1291,19 @@
         <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1311,12 +1311,6 @@
       <c r="AI8" t="n">
         <v>235</v>
       </c>
-      <c r="AK8" t="n">
-        <v>131.69</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
@@ -1330,13 +1324,13 @@
         <v>0</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM8" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -1347,19 +1341,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C9" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D9" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E9" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F9" t="n">
         <v>10.92</v>
@@ -1383,19 +1377,19 @@
         <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1416,10 +1410,10 @@
         <v>0</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM9" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -1433,26 +1427,41 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B10" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C10" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D10" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E10" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F10" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35.1</v>
       </c>
       <c r="K10" t="n">
         <v>62.9</v>
       </c>
+      <c r="M10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O10" t="n">
         <v>31.8</v>
       </c>
@@ -1469,19 +1478,19 @@
         <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1489,6 +1498,12 @@
       <c r="AI10" t="n">
         <v>235</v>
       </c>
+      <c r="AK10" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.46</v>
+      </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
@@ -1502,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM10" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -1519,46 +1534,46 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B11" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C11" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D11" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E11" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F11" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H11" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I11" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M11" t="n">
         <v>1.9</v>
       </c>
       <c r="N11" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O11" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1567,22 +1582,22 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA11" t="n">
         <v>16</v>
       </c>
-      <c r="Z11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>19</v>
-      </c>
       <c r="AF11" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1591,10 +1606,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1609,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM11" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
@@ -1626,43 +1641,43 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B12" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C12" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D12" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E12" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M12" t="n">
         <v>1.9</v>
       </c>
       <c r="N12" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O12" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1677,19 +1692,19 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG12" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1698,10 +1713,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1716,13 +1731,13 @@
         <v>0</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM12" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN12" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
@@ -1733,70 +1748,70 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B13" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C13" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D13" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E13" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H13" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K13" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N13" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O13" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1805,10 +1820,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL13" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1817,19 +1832,19 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM13" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
@@ -1840,46 +1855,46 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B14" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C14" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D14" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E14" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H14" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K14" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O14" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R14" t="n">
         <v>0.6</v>
@@ -1888,22 +1903,22 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1912,10 +1927,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1924,19 +1939,19 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS14" t="n">
         <v>13.07</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM14" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN14" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
@@ -1947,70 +1962,43 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B15" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C15" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D15" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E15" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O15" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA15" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF15" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2018,35 +2006,23 @@
       <c r="AI15" t="n">
         <v>235</v>
       </c>
-      <c r="AK15" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM15" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP15" t="n">
         <v>0</v>
@@ -2054,43 +2030,43 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B16" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C16" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D16" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E16" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,60 +2081,87 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM16" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B17" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C17" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D17" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E17" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.6</v>
       </c>
       <c r="K17" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34</v>
       </c>
       <c r="O17" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2166,17 +2169,29 @@
       <c r="AI17" t="n">
         <v>235</v>
       </c>
+      <c r="AK17" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM17" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2185,75 +2200,75 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B18" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C18" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E18" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F18" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H18" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I18" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K18" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O18" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2262,10 +2277,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2274,16 +2289,16 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM18" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -2292,30 +2307,30 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B19" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D19" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E19" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F19" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H19" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I19" t="n">
         <v>9.800000000000001</v>
@@ -2324,43 +2339,43 @@
         <v>38.6</v>
       </c>
       <c r="K19" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O19" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2369,10 +2384,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2381,93 +2396,93 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS19" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM19" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B20" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C20" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D20" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N20" t="n">
         <v>35.2</v>
       </c>
-      <c r="E20" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J20" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O20" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF20" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2476,10 +2491,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL20" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2488,93 +2503,60 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS20" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM20" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN20" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B21" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C21" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D21" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E21" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>21</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z21" t="n">
         <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2583,10 +2565,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL21" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2594,61 +2576,55 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM21" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN21" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO21" t="n">
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B22" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C22" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D22" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA22" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF22" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2657,10 +2633,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2669,10 +2645,10 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM22" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
@@ -2681,42 +2657,42 @@
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B23" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C23" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D23" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E23" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F23" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y23" t="n">
         <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2725,10 +2701,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL23" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2737,10 +2713,10 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM23" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
@@ -2749,42 +2725,75 @@
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B24" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C24" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D24" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E24" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F24" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z24" t="n">
         <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2796,7 +2805,7 @@
         <v>138.94</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2804,11 +2813,17 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM24" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
@@ -2817,51 +2832,51 @@
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B25" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C25" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D25" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I25" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K25" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M25" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N25" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O25" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R25" t="n">
         <v>3.5</v>
@@ -2870,22 +2885,22 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2894,10 +2909,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2906,16 +2921,16 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS25" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM25" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
@@ -2924,75 +2939,75 @@
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B26" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C26" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E26" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H26" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J26" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K26" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N26" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O26" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R26" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA26" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3001,10 +3016,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3013,93 +3028,93 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM26" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO26" t="n">
         <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B27" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D27" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E27" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F27" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H27" t="n">
         <v>25.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J27" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K27" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N27" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O27" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3108,10 +3123,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3120,93 +3135,93 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM27" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN27" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO27" t="n">
         <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B28" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C28" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D28" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E28" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F28" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H28" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I28" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J28" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O28" t="n">
         <v>38.4</v>
       </c>
-      <c r="K28" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q28" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG28" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3215,10 +3230,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3227,93 +3242,66 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM28" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN28" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO28" t="n">
         <v>0</v>
       </c>
       <c r="BP28" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B29" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C29" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D29" t="n">
         <v>34.5</v>
       </c>
       <c r="E29" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F29" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K29" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N29" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O29" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3322,10 +3310,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3333,17 +3321,11 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM29" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
@@ -3352,48 +3334,48 @@
         <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B30" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C30" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D30" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E30" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>9.6</v>
       </c>
       <c r="K30" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG30" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3402,10 +3384,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL30" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3414,60 +3396,87 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM30" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP30" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B31" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C31" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D31" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F31" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>38.7</v>
       </c>
       <c r="K31" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>33</v>
       </c>
       <c r="O31" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG31" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3479,7 +3488,7 @@
         <v>128.27</v>
       </c>
       <c r="AL31" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3487,88 +3496,94 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM31" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP31" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B32" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C32" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D32" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F32" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H32" t="n">
         <v>25.1</v>
       </c>
       <c r="I32" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J32" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K32" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O32" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA32" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3577,10 +3592,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3589,72 +3604,72 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM32" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP32" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B33" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C33" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D33" t="n">
         <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F33" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H33" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I33" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K33" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O33" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q33" t="n">
         <v>23.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3663,19 +3678,19 @@
         <v>23.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3684,10 +3699,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL33" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3696,69 +3711,69 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM33" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP33" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B34" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C34" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D34" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E34" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F34" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I34" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J34" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K34" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O34" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R34" t="n">
         <v>1.3</v>
@@ -3767,22 +3782,22 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y34" t="n">
         <v>9</v>
       </c>
       <c r="Z34" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA34" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3791,10 +3806,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3803,93 +3818,93 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS34" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM34" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN34" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP34" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B35" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C35" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D35" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E35" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I35" t="n">
         <v>9.4</v>
       </c>
       <c r="J35" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O35" t="n">
         <v>39.5</v>
       </c>
-      <c r="K35" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N35" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q35" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA35" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG35" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3898,10 +3913,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3910,93 +3925,66 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM35" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO35" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP35" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B36" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C36" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D36" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E36" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F36" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y36" t="n">
         <v>8</v>
       </c>
-      <c r="H36" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K36" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N36" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>10</v>
-      </c>
       <c r="Z36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4005,10 +3993,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4016,67 +4004,61 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM36" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN36" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP36" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B37" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C37" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D37" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E37" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F37" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K37" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O37" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4085,10 +4067,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL37" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4097,60 +4079,87 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM37" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN37" t="n">
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP37" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B38" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C38" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F38" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40</v>
       </c>
       <c r="K38" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>36.7</v>
       </c>
       <c r="O38" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4162,7 +4171,7 @@
         <v>125.11</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4170,88 +4179,94 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>14</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM38" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN38" t="n">
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP38" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B39" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C39" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E39" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F39" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H39" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I39" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K39" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O39" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T39" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA39" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF39" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4260,10 +4275,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4272,93 +4287,93 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS39" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM39" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN39" t="n">
         <v>0</v>
       </c>
       <c r="BO39" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP39" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B40" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C40" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E40" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F40" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H40" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K40" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O40" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T40" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG40" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4367,10 +4382,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4379,93 +4394,93 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS40" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM40" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN40" t="n">
         <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP40" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B41" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C41" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D41" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E41" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F41" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H41" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K41" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N41" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q41" t="n">
         <v>23.7</v>
       </c>
-      <c r="I41" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J41" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>73</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>34</v>
-      </c>
-      <c r="O41" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S41" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T41" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG41" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4474,10 +4489,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL41" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4486,93 +4501,93 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM41" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN41" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO41" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP41" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B42" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C42" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E42" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F42" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H42" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I42" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>40.8</v>
       </c>
       <c r="K42" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O42" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T42" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA42" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF42" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG42" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4581,10 +4596,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL42" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4593,93 +4608,66 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM42" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN42" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP42" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B43" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C43" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E43" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F43" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H43" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J43" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K43" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M43" t="n">
-        <v>4</v>
-      </c>
-      <c r="N43" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O43" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2</v>
-      </c>
-      <c r="S43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T43" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z43" t="n">
         <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF43" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4688,10 +4676,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL43" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4699,67 +4687,61 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM43" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN43" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO43" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP43" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B44" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C44" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D44" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E44" t="n">
         <v>29.8</v>
       </c>
       <c r="F44" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K44" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O44" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4768,10 +4750,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4780,33 +4762,33 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM44" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN44" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO44" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP44" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B45" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C45" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E45" t="n">
         <v>29.8</v>
@@ -4815,25 +4797,25 @@
         <v>6.6</v>
       </c>
       <c r="K45" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA45" t="n">
         <v>12.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4842,10 +4824,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL45" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4854,60 +4836,87 @@
         <v>142</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM45" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN45" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO45" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP45" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B46" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C46" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D46" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E46" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F46" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>41.1</v>
       </c>
       <c r="K46" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" t="n">
+        <v>37.4</v>
       </c>
       <c r="O46" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y46" t="n">
         <v>9</v>
       </c>
       <c r="Z46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF46" t="n">
         <v>220</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4919,7 +4928,7 @@
         <v>126.54</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4927,88 +4936,94 @@
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM46" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN46" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO46" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP46" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B47" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C47" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D47" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E47" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F47" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H47" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I47" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K47" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N47" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O47" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5017,10 +5032,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5029,93 +5044,93 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM47" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN47" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO47" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP47" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B48" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C48" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E48" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F48" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I48" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K48" t="n">
         <v>76.5</v>
       </c>
       <c r="M48" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N48" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O48" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R48" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA48" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF48" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG48" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5124,10 +5139,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5136,72 +5151,72 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM48" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN48" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO48" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP48" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B49" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C49" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D49" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E49" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F49" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H49" t="n">
         <v>26.1</v>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K49" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N49" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O49" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q49" t="n">
         <v>24.2</v>
       </c>
       <c r="R49" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -5210,19 +5225,19 @@
         <v>24.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z49" t="n">
         <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5231,10 +5246,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL49" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5243,93 +5258,66 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS49" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM49" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN49" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO49" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP49" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B50" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C50" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D50" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E50" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K50" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M50" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="n">
         <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF50" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5338,10 +5326,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>124.66</v>
+        <v>133</v>
       </c>
       <c r="AL50" t="n">
-        <v>-1.79</v>
+        <v>8.34</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5349,67 +5337,61 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM50" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN50" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO50" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP50" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B51" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C51" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D51" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E51" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F51" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K51" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="Y51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
         <v>16</v>
       </c>
       <c r="AA51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF51" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5421,7 +5403,7 @@
         <v>133</v>
       </c>
       <c r="AL51" t="n">
-        <v>8.34</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5430,60 +5412,87 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM51" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN51" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO51" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP51" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B52" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C52" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D52" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E52" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F52" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J52" t="n">
+        <v>41.3</v>
       </c>
       <c r="K52" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N52" t="n">
+        <v>37.1</v>
       </c>
       <c r="O52" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z52" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF52" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5492,10 +5501,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>133</v>
+        <v>125.03</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>-7.97</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5503,88 +5512,94 @@
       <c r="AN52" t="n">
         <v>142</v>
       </c>
+      <c r="AP52" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL52" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM52" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN52" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO52" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP52" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B53" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C53" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E53" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F53" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I53" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K53" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M53" t="n">
         <v>2.7</v>
       </c>
       <c r="N53" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O53" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R53" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T53" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Y53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA53" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF53" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5593,10 +5608,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL53" t="n">
-        <v>-7.97</v>
+        <v>4.54</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5605,78 +5620,78 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM53" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN53" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO53" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP53" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B54" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C54" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D54" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E54" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F54" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I54" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K54" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N54" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O54" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
         <v>16</v>
       </c>
       <c r="T54" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y54" t="n">
         <v>10</v>
@@ -5685,13 +5700,13 @@
         <v>15</v>
       </c>
       <c r="AA54" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF54" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5700,10 +5715,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL54" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5712,93 +5727,93 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM54" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN54" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO54" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP54" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B55" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C55" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D55" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E55" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F55" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H55" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I55" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K55" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N55" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O55" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S55" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y55" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA55" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF55" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5807,10 +5822,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL55" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5819,78 +5834,78 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM55" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN55" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO55" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP55" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B56" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C56" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D56" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E56" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F56" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H56" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I56" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J56" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K56" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M56" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N56" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O56" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R56" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S56" t="n">
         <v>12</v>
       </c>
       <c r="T56" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y56" t="n">
         <v>13</v>
@@ -5899,13 +5914,13 @@
         <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF56" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5914,10 +5929,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL56" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5926,93 +5941,66 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS56" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM56" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN56" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO56" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP56" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B57" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C57" t="n">
         <v>57.9</v>
       </c>
       <c r="D57" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E57" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F57" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H57" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J57" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N57" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S57" t="n">
-        <v>12</v>
-      </c>
-      <c r="T57" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="Y57" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z57" t="n">
         <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6021,10 +6009,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>124.73</v>
+        <v>133</v>
       </c>
       <c r="AL57" t="n">
-        <v>-5.61</v>
+        <v>8.27</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6032,67 +6020,61 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM57" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN57" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO57" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP57" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B58" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C58" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D58" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E58" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K58" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O58" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Y58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z58" t="n">
         <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF58" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6104,7 +6086,7 @@
         <v>133</v>
       </c>
       <c r="AL58" t="n">
-        <v>8.27</v>
+        <v>0</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6113,60 +6095,87 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM58" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN58" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO58" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP58" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B59" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C59" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D59" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E59" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F59" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J59" t="n">
+        <v>40.6</v>
       </c>
       <c r="K59" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N59" t="n">
+        <v>36</v>
       </c>
       <c r="O59" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>11</v>
+      </c>
+      <c r="T59" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z59" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA59" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF59" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6175,10 +6184,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>133</v>
+        <v>128.43</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>-4.57</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6186,88 +6195,94 @@
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM59" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN59" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO59" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP59" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B60" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C60" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D60" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E60" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F60" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H60" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I60" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K60" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N60" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O60" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T60" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z60" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF60" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6276,10 +6291,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL60" t="n">
-        <v>-4.57</v>
+        <v>2.39</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6288,54 +6303,60 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM60" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN60" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO60" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP60" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B61" t="n">
-        <v>155.1</v>
+        <v>155.3</v>
       </c>
       <c r="C61" t="n">
-        <v>61.8</v>
+        <v>62.6</v>
       </c>
       <c r="D61" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E61" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="F61" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="Y61" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA61" t="n">
-        <v>13</v>
+        <v>11.5</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>221.34</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0.06</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6347,7 +6368,7 @@
         <v>133</v>
       </c>
       <c r="AL61" t="n">
-        <v>4.57</v>
+        <v>2.18</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6356,48 +6377,48 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM61" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN61" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO61" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP61" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B62" t="n">
-        <v>155.3</v>
+        <v>152.3</v>
       </c>
       <c r="C62" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="D62" t="n">
-        <v>34.2</v>
+        <v>33.6</v>
       </c>
       <c r="E62" t="n">
-        <v>42.1</v>
+        <v>37</v>
       </c>
       <c r="F62" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Y62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z62" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA62" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6418,7 +6439,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,13 +628,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B2" t="n">
-        <v>110</v>
+        <v>108.2</v>
       </c>
       <c r="C2" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="D2" t="n">
         <v>37.7</v>
@@ -645,14 +645,29 @@
       <c r="F2" t="n">
         <v>11.5</v>
       </c>
+      <c r="H2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32.7</v>
+      </c>
       <c r="K2" t="n">
         <v>71.59999999999999</v>
       </c>
+      <c r="M2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>31.5</v>
+      </c>
       <c r="O2" t="n">
         <v>34.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -661,22 +676,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>235.81</v>
+        <v>235.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.49</v>
+        <v>-235.81</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -688,7 +703,7 @@
         <v>134.07</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.52</v>
+        <v>-134.07</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="BM2" t="n">
         <v>54.51</v>
@@ -720,46 +735,46 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B3" t="n">
-        <v>108.2</v>
+        <v>119.7</v>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>25.9</v>
       </c>
       <c r="D3" t="n">
-        <v>37.7</v>
+        <v>38.7</v>
       </c>
       <c r="E3" t="n">
-        <v>27.2</v>
+        <v>34.5</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>22.1</v>
+        <v>20.5</v>
       </c>
       <c r="I3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>32.7</v>
+        <v>29</v>
       </c>
       <c r="K3" t="n">
-        <v>71.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="M3" t="n">
         <v>1.9</v>
       </c>
       <c r="N3" t="n">
-        <v>31.5</v>
+        <v>30.6</v>
       </c>
       <c r="O3" t="n">
-        <v>34.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -768,22 +783,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>235.83</v>
+        <v>235.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>-235.81</v>
+        <v>-4.98</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -792,10 +807,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>134.07</v>
+        <v>136.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>-134.07</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -810,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="BM3" t="n">
         <v>54.51</v>
@@ -827,46 +842,46 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B4" t="n">
-        <v>119.7</v>
+        <v>116.54</v>
       </c>
       <c r="C4" t="n">
-        <v>25.9</v>
+        <v>23.39</v>
       </c>
       <c r="D4" t="n">
-        <v>38.7</v>
+        <v>36.98</v>
       </c>
       <c r="E4" t="n">
-        <v>34.5</v>
+        <v>35.59</v>
       </c>
       <c r="F4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="H4" t="n">
         <v>20.5</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
       <c r="K4" t="n">
         <v>62.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>30.6</v>
+        <v>29.2</v>
       </c>
       <c r="O4" t="n">
         <v>31.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -875,22 +890,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" t="n">
         <v>21</v>
       </c>
-      <c r="AA4" t="n">
-        <v>19</v>
-      </c>
       <c r="AF4" t="n">
-        <v>235.47</v>
+        <v>230.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4.98</v>
+        <v>-4.67</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -899,10 +914,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>136.17</v>
+        <v>136.01</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>-0.16</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -917,13 +932,13 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="BM4" t="n">
-        <v>54.51</v>
+        <v>37.84</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>285.1</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -934,40 +949,40 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B5" t="n">
-        <v>116.54</v>
+        <v>117.05</v>
       </c>
       <c r="C5" t="n">
-        <v>23.39</v>
+        <v>23.91</v>
       </c>
       <c r="D5" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
       <c r="E5" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="F5" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="H5" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="I5" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J5" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="K5" t="n">
         <v>62.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N5" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="O5" t="n">
         <v>31.8</v>
@@ -985,19 +1000,19 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>230.5</v>
+        <v>225.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.67</v>
+        <v>-5.78</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1006,10 +1021,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>136.01</v>
+        <v>132.41</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.16</v>
+        <v>-3.6</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1024,13 +1039,13 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="BM5" t="n">
-        <v>37.84</v>
+        <v>41.59</v>
       </c>
       <c r="BN5" t="n">
-        <v>285.1</v>
+        <v>334.1</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1041,40 +1056,40 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B6" t="n">
-        <v>117.05</v>
+        <v>117.63</v>
       </c>
       <c r="C6" t="n">
-        <v>23.91</v>
+        <v>24.3</v>
       </c>
       <c r="D6" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="E6" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="F6" t="n">
-        <v>10.56</v>
+        <v>10.75</v>
       </c>
       <c r="H6" t="n">
         <v>22.3</v>
       </c>
       <c r="I6" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K6" t="n">
         <v>62.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N6" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="O6" t="n">
         <v>31.8</v>
@@ -1092,19 +1107,19 @@
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA6" t="n">
         <v>22</v>
       </c>
-      <c r="AA6" t="n">
-        <v>21</v>
-      </c>
       <c r="AF6" t="n">
-        <v>225.8</v>
+        <v>220</v>
       </c>
       <c r="AG6" t="n">
-        <v>-5.78</v>
+        <v>-2.67</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1113,10 +1128,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>132.41</v>
+        <v>131.69</v>
       </c>
       <c r="AL6" t="n">
-        <v>-3.6</v>
+        <v>-0.72</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1131,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BM6" t="n">
-        <v>41.59</v>
+        <v>42.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>334.1</v>
+        <v>106.5</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1148,41 +1163,26 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B7" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D7" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E7" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F7" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K7" t="n">
         <v>62.9</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O7" t="n">
         <v>31.8</v>
       </c>
@@ -1199,19 +1199,19 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1219,12 +1219,6 @@
       <c r="AI7" t="n">
         <v>235</v>
       </c>
-      <c r="AK7" t="n">
-        <v>131.69</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="AM7" t="n">
         <v>110</v>
       </c>
@@ -1238,13 +1232,13 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM7" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1255,19 +1249,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C8" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D8" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E8" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F8" t="n">
         <v>10.92</v>
@@ -1291,19 +1285,19 @@
         <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1324,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM8" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
@@ -1341,26 +1335,41 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B9" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C9" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D9" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E9" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F9" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.1</v>
       </c>
       <c r="K9" t="n">
         <v>62.9</v>
       </c>
+      <c r="M9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O9" t="n">
         <v>31.8</v>
       </c>
@@ -1377,19 +1386,19 @@
         <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
         <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1397,6 +1406,12 @@
       <c r="AI9" t="n">
         <v>235</v>
       </c>
+      <c r="AK9" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.46</v>
+      </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
@@ -1410,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM9" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -1427,46 +1442,46 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B10" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D10" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E10" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F10" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K10" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.9</v>
       </c>
       <c r="N10" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O10" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1475,22 +1490,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA10" t="n">
         <v>16</v>
       </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>19</v>
-      </c>
       <c r="AF10" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1499,10 +1514,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1517,13 +1532,13 @@
         <v>0</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM10" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
@@ -1534,43 +1549,43 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B11" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C11" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D11" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E11" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M11" t="n">
         <v>1.9</v>
       </c>
       <c r="N11" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O11" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1585,19 +1600,19 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG11" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1606,10 +1621,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1624,13 +1639,13 @@
         <v>0</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM11" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN11" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
@@ -1641,70 +1656,70 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B12" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C12" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D12" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E12" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H12" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K12" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N12" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O12" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1713,10 +1728,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL12" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1725,19 +1740,19 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM12" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
@@ -1748,46 +1763,46 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B13" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C13" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D13" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E13" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H13" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K13" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O13" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R13" t="n">
         <v>0.6</v>
@@ -1796,22 +1811,22 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1820,10 +1835,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL13" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1832,19 +1847,19 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS13" t="n">
         <v>13.07</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM13" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN13" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
@@ -1855,70 +1870,43 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B14" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C14" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D14" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E14" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J14" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O14" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF14" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1926,35 +1914,23 @@
       <c r="AI14" t="n">
         <v>235</v>
       </c>
-      <c r="AK14" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM14" t="n">
         <v>110</v>
       </c>
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM14" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP14" t="n">
         <v>0</v>
@@ -1962,43 +1938,43 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B15" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C15" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D15" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E15" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2013,60 +1989,87 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM15" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B16" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C16" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D16" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E16" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>35.6</v>
       </c>
       <c r="K16" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>34</v>
       </c>
       <c r="O16" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2074,17 +2077,29 @@
       <c r="AI16" t="n">
         <v>235</v>
       </c>
+      <c r="AK16" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM16" t="n">
         <v>110</v>
       </c>
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM16" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -2093,75 +2108,75 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B17" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C17" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E17" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F17" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I17" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K17" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O17" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2170,10 +2185,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2182,16 +2197,16 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM17" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2200,30 +2215,30 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B18" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D18" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E18" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F18" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H18" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I18" t="n">
         <v>9.800000000000001</v>
@@ -2232,43 +2247,43 @@
         <v>38.6</v>
       </c>
       <c r="K18" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O18" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2277,10 +2292,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2289,93 +2304,93 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS18" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM18" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B19" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C19" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D19" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N19" t="n">
         <v>35.2</v>
       </c>
-      <c r="E19" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J19" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O19" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2384,10 +2399,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL19" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2396,93 +2411,60 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM19" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B20" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C20" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D20" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E20" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>21</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
         <v>23</v>
       </c>
       <c r="AA20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2491,10 +2473,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2502,61 +2484,55 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM20" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN20" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B21" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C21" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D21" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2565,10 +2541,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2577,10 +2553,10 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM21" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
@@ -2589,42 +2565,42 @@
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B22" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C22" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D22" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E22" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F22" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y22" t="n">
         <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA22" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2633,10 +2609,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL22" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2645,10 +2621,10 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM22" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
@@ -2657,42 +2633,75 @@
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B23" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C23" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D23" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E23" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F23" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="n">
         <v>18</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2704,7 +2713,7 @@
         <v>138.94</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2712,11 +2721,17 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM23" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
@@ -2725,51 +2740,51 @@
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B24" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C24" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D24" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E24" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I24" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O24" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R24" t="n">
         <v>3.5</v>
@@ -2778,22 +2793,22 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2802,10 +2817,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2814,16 +2829,16 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS24" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM24" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
@@ -2832,75 +2847,75 @@
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B25" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C25" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D25" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E25" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H25" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J25" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K25" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O25" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R25" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2909,10 +2924,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2921,93 +2936,93 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM25" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO25" t="n">
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B26" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C26" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D26" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E26" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F26" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H26" t="n">
         <v>25.4</v>
       </c>
       <c r="I26" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J26" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K26" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N26" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O26" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3016,10 +3031,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3028,93 +3043,93 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM26" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN26" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO26" t="n">
         <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B27" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C27" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D27" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E27" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F27" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H27" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I27" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J27" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O27" t="n">
         <v>38.4</v>
       </c>
-      <c r="K27" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q27" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3123,10 +3138,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3135,93 +3150,66 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM27" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN27" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO27" t="n">
         <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B28" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C28" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D28" t="n">
         <v>34.5</v>
       </c>
       <c r="E28" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F28" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I28" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K28" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O28" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF28" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3230,10 +3218,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3241,17 +3229,11 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM28" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
@@ -3260,48 +3242,48 @@
         <v>0</v>
       </c>
       <c r="BP28" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B29" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C29" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D29" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E29" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
         <v>9.6</v>
       </c>
       <c r="K29" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z29" t="n">
         <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG29" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3310,10 +3292,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3322,60 +3304,87 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM29" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP29" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B30" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C30" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D30" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>38.7</v>
       </c>
       <c r="K30" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33</v>
       </c>
       <c r="O30" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG30" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3387,7 +3396,7 @@
         <v>128.27</v>
       </c>
       <c r="AL30" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3395,88 +3404,94 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM30" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP30" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B31" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C31" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D31" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F31" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H31" t="n">
         <v>25.1</v>
       </c>
       <c r="I31" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K31" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O31" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3485,10 +3500,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3497,72 +3512,72 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM31" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP31" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B32" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C32" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D32" t="n">
         <v>34</v>
       </c>
       <c r="E32" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H32" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I32" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K32" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N32" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O32" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q32" t="n">
         <v>23.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -3571,19 +3586,19 @@
         <v>23.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3592,10 +3607,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL32" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3604,69 +3619,69 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM32" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO32" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP32" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B33" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C33" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E33" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F33" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I33" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J33" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K33" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O33" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R33" t="n">
         <v>1.3</v>
@@ -3675,22 +3690,22 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y33" t="n">
         <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3699,10 +3714,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3711,93 +3726,93 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM33" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN33" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP33" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B34" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C34" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D34" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E34" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H34" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I34" t="n">
         <v>9.4</v>
       </c>
       <c r="J34" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O34" t="n">
         <v>39.5</v>
       </c>
-      <c r="K34" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O34" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q34" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF34" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG34" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3806,10 +3821,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3818,93 +3833,66 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS34" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM34" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO34" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP34" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B35" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C35" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D35" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E35" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F35" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y35" t="n">
         <v>8</v>
       </c>
-      <c r="H35" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K35" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N35" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O35" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>10</v>
-      </c>
       <c r="Z35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3913,10 +3901,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3924,67 +3912,61 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM35" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN35" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP35" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B36" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C36" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D36" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E36" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K36" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O36" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3993,10 +3975,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL36" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4005,60 +3987,87 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM36" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN36" t="n">
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP36" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B37" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C37" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F37" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>40</v>
       </c>
       <c r="K37" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>36.7</v>
       </c>
       <c r="O37" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF37" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4070,7 +4079,7 @@
         <v>125.11</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4078,88 +4087,94 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>14</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM37" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN37" t="n">
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP37" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B38" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C38" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E38" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F38" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H38" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I38" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K38" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O38" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T38" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA38" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4168,10 +4183,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4180,93 +4195,93 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS38" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM38" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN38" t="n">
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP38" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B39" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C39" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E39" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F39" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H39" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K39" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O39" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T39" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG39" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4275,10 +4290,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4287,93 +4302,93 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS39" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM39" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN39" t="n">
         <v>0</v>
       </c>
       <c r="BO39" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP39" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B40" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C40" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D40" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E40" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F40" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H40" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K40" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q40" t="n">
         <v>23.7</v>
       </c>
-      <c r="I40" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J40" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K40" t="n">
-        <v>73</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N40" t="n">
-        <v>34</v>
-      </c>
-      <c r="O40" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S40" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T40" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z40" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG40" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4382,10 +4397,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4394,93 +4409,93 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM40" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO40" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP40" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B41" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C41" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E41" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F41" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H41" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I41" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>40.8</v>
       </c>
       <c r="K41" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O41" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T41" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA41" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF41" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG41" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4489,10 +4504,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL41" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4501,93 +4516,66 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS41" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM41" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN41" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B42" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C42" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E42" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J42" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K42" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4</v>
-      </c>
-      <c r="N42" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O42" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z42" t="n">
         <v>13</v>
       </c>
       <c r="AA42" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF42" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4596,10 +4584,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL42" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4607,67 +4595,61 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM42" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN42" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO42" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP42" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B43" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C43" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D43" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E43" t="n">
         <v>29.8</v>
       </c>
       <c r="F43" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K43" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O43" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA43" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4676,10 +4658,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4688,33 +4670,33 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM43" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN43" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO43" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP43" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B44" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C44" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D44" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E44" t="n">
         <v>29.8</v>
@@ -4723,25 +4705,25 @@
         <v>6.6</v>
       </c>
       <c r="K44" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA44" t="n">
         <v>12.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG44" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4750,10 +4732,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL44" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4762,60 +4744,87 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM44" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN44" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO44" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP44" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B45" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C45" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D45" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E45" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F45" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>41.1</v>
       </c>
       <c r="K45" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" t="n">
+        <v>37.4</v>
       </c>
       <c r="O45" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y45" t="n">
         <v>9</v>
       </c>
       <c r="Z45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA45" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF45" t="n">
         <v>220</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4827,7 +4836,7 @@
         <v>126.54</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4835,88 +4844,94 @@
       <c r="AN45" t="n">
         <v>142</v>
       </c>
+      <c r="AP45" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL45" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM45" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN45" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO45" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP45" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B46" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C46" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D46" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E46" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F46" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H46" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I46" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K46" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N46" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O46" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4925,10 +4940,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4937,93 +4952,93 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS46" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM46" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN46" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO46" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP46" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B47" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C47" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E47" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F47" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H47" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I47" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K47" t="n">
         <v>76.5</v>
       </c>
       <c r="M47" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N47" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O47" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z47" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA47" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF47" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG47" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5032,10 +5047,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5044,72 +5059,72 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM47" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN47" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO47" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP47" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B48" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C48" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D48" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E48" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H48" t="n">
         <v>26.1</v>
       </c>
       <c r="I48" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J48" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K48" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N48" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O48" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q48" t="n">
         <v>24.2</v>
       </c>
       <c r="R48" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -5118,19 +5133,19 @@
         <v>24.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
         <v>16</v>
       </c>
       <c r="AA48" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5139,10 +5154,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5151,93 +5166,66 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM48" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN48" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO48" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP48" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B49" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C49" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D49" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E49" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F49" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H49" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J49" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K49" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M49" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="Y49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z49" t="n">
         <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF49" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5246,10 +5234,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>124.66</v>
+        <v>133</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.79</v>
+        <v>8.34</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5257,67 +5245,61 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM49" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN49" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP49" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B50" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C50" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D50" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E50" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F50" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K50" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
         <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF50" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5329,7 +5311,7 @@
         <v>133</v>
       </c>
       <c r="AL50" t="n">
-        <v>8.34</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5338,60 +5320,87 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM50" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN50" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO50" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP50" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B51" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C51" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D51" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E51" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F51" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J51" t="n">
+        <v>41.3</v>
       </c>
       <c r="K51" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N51" t="n">
+        <v>37.1</v>
       </c>
       <c r="O51" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF51" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5400,10 +5409,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>133</v>
+        <v>125.03</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>-7.97</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5411,88 +5420,94 @@
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM51" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN51" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO51" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP51" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B52" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C52" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E52" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F52" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I52" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K52" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M52" t="n">
         <v>2.7</v>
       </c>
       <c r="N52" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O52" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R52" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T52" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Y52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5501,10 +5516,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL52" t="n">
-        <v>-7.97</v>
+        <v>4.54</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5513,78 +5528,78 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM52" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN52" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO52" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP52" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B53" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C53" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D53" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E53" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F53" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I53" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K53" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O53" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R53" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>16</v>
       </c>
       <c r="T53" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y53" t="n">
         <v>10</v>
@@ -5593,13 +5608,13 @@
         <v>15</v>
       </c>
       <c r="AA53" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF53" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5608,10 +5623,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL53" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5620,93 +5635,93 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM53" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN53" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO53" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP53" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B54" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C54" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D54" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E54" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F54" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H54" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I54" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K54" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N54" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O54" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S54" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z54" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA54" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF54" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5715,10 +5730,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL54" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5727,78 +5742,78 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM54" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN54" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO54" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP54" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B55" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C55" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D55" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E55" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F55" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I55" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J55" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K55" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M55" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N55" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O55" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S55" t="n">
         <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y55" t="n">
         <v>13</v>
@@ -5807,13 +5822,13 @@
         <v>18</v>
       </c>
       <c r="AA55" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF55" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5822,10 +5837,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL55" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5834,93 +5849,66 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS55" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM55" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN55" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO55" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP55" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B56" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C56" t="n">
         <v>57.9</v>
       </c>
       <c r="D56" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E56" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F56" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H56" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K56" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N56" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S56" t="n">
-        <v>12</v>
-      </c>
-      <c r="T56" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="Y56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z56" t="n">
         <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5929,10 +5917,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>124.73</v>
+        <v>133</v>
       </c>
       <c r="AL56" t="n">
-        <v>-5.61</v>
+        <v>8.27</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5940,67 +5928,61 @@
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM56" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN56" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP56" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B57" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C57" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D57" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E57" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K57" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O57" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Y57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z57" t="n">
         <v>18</v>
       </c>
       <c r="AA57" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF57" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6012,7 +5994,7 @@
         <v>133</v>
       </c>
       <c r="AL57" t="n">
-        <v>8.27</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6021,60 +6003,87 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM57" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN57" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO57" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP57" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B58" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C58" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D58" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E58" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F58" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>40.6</v>
       </c>
       <c r="K58" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>36</v>
       </c>
       <c r="O58" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>11</v>
+      </c>
+      <c r="T58" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA58" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF58" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6083,10 +6092,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>133</v>
+        <v>128.43</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>-4.57</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6094,88 +6103,94 @@
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM58" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN58" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO58" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP58" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B59" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C59" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D59" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E59" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F59" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H59" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I59" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K59" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N59" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O59" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T59" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z59" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6184,10 +6199,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL59" t="n">
-        <v>-4.57</v>
+        <v>2.39</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6196,93 +6211,93 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS59" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM59" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN59" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO59" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP59" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B60" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C60" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D60" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E60" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F60" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H60" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I60" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K60" t="n">
         <v>75.7</v>
       </c>
       <c r="M60" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O60" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R60" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T60" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA60" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF60" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6291,10 +6306,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6303,60 +6318,54 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS60" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM60" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN60" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO60" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP60" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B61" t="n">
-        <v>155.3</v>
+        <v>152.3</v>
       </c>
       <c r="C61" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="D61" t="n">
-        <v>34.2</v>
+        <v>33.6</v>
       </c>
       <c r="E61" t="n">
-        <v>42.1</v>
+        <v>37</v>
       </c>
       <c r="F61" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z61" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA61" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>221.34</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0.06</v>
+        <v>12</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6368,7 +6377,7 @@
         <v>133</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6377,48 +6386,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>1228.7</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>3169.7</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B62" t="n">
-        <v>152.3</v>
+        <v>150.7</v>
       </c>
       <c r="C62" t="n">
-        <v>65.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>33.6</v>
+        <v>32.9</v>
       </c>
       <c r="E62" t="n">
-        <v>37</v>
+        <v>35.3</v>
       </c>
       <c r="F62" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z62" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA62" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6439,7 +6436,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,46 +628,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B2" t="n">
-        <v>108.2</v>
+        <v>119.7</v>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>25.9</v>
       </c>
       <c r="D2" t="n">
-        <v>37.7</v>
+        <v>38.7</v>
       </c>
       <c r="E2" t="n">
-        <v>27.2</v>
+        <v>34.5</v>
       </c>
       <c r="F2" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>22.1</v>
+        <v>20.5</v>
       </c>
       <c r="I2" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>32.7</v>
+        <v>29</v>
       </c>
       <c r="K2" t="n">
-        <v>71.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="n">
         <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>31.5</v>
+        <v>30.6</v>
       </c>
       <c r="O2" t="n">
-        <v>34.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -676,22 +676,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>235.83</v>
+        <v>235.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>-235.81</v>
+        <v>-4.98</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -700,10 +700,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>134.07</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-134.07</v>
+        <v>136.17</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -718,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="BM2" t="n">
         <v>54.51</v>
@@ -735,46 +732,46 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B3" t="n">
-        <v>119.7</v>
+        <v>116.54</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9</v>
+        <v>23.39</v>
       </c>
       <c r="D3" t="n">
-        <v>38.7</v>
+        <v>36.98</v>
       </c>
       <c r="E3" t="n">
-        <v>34.5</v>
+        <v>35.59</v>
       </c>
       <c r="F3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="H3" t="n">
         <v>20.5</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
       <c r="K3" t="n">
         <v>62.9</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>30.6</v>
+        <v>29.2</v>
       </c>
       <c r="O3" t="n">
         <v>31.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -783,22 +780,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" t="n">
         <v>21</v>
       </c>
-      <c r="AA3" t="n">
-        <v>19</v>
-      </c>
       <c r="AF3" t="n">
-        <v>235.47</v>
+        <v>230.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4.98</v>
+        <v>-4.67</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -807,10 +804,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>136.17</v>
+        <v>136.01</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>-0.16</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -825,13 +822,13 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="BM3" t="n">
-        <v>54.51</v>
+        <v>37.84</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>285.1</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -842,40 +839,40 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B4" t="n">
-        <v>116.54</v>
+        <v>117.05</v>
       </c>
       <c r="C4" t="n">
-        <v>23.39</v>
+        <v>23.91</v>
       </c>
       <c r="D4" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
       <c r="E4" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="F4" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="H4" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J4" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="K4" t="n">
         <v>62.9</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N4" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="O4" t="n">
         <v>31.8</v>
@@ -893,19 +890,19 @@
         <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>230.5</v>
+        <v>225.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4.67</v>
+        <v>-5.78</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -914,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>136.01</v>
+        <v>132.41</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.16</v>
+        <v>-3.6</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -932,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="BM4" t="n">
-        <v>37.84</v>
+        <v>41.59</v>
       </c>
       <c r="BN4" t="n">
-        <v>285.1</v>
+        <v>334.1</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -949,40 +946,40 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B5" t="n">
-        <v>117.05</v>
+        <v>117.63</v>
       </c>
       <c r="C5" t="n">
-        <v>23.91</v>
+        <v>24.3</v>
       </c>
       <c r="D5" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="E5" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="F5" t="n">
-        <v>10.56</v>
+        <v>10.75</v>
       </c>
       <c r="H5" t="n">
         <v>22.3</v>
       </c>
       <c r="I5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K5" t="n">
         <v>62.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N5" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="O5" t="n">
         <v>31.8</v>
@@ -1000,19 +997,19 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" t="n">
         <v>22</v>
       </c>
-      <c r="AA5" t="n">
-        <v>21</v>
-      </c>
       <c r="AF5" t="n">
-        <v>225.8</v>
+        <v>220</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5.78</v>
+        <v>-2.67</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1021,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>132.41</v>
+        <v>131.69</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.6</v>
+        <v>-0.72</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1039,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BM5" t="n">
-        <v>41.59</v>
+        <v>42.83</v>
       </c>
       <c r="BN5" t="n">
-        <v>334.1</v>
+        <v>106.5</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1056,41 +1053,26 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B6" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C6" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D6" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E6" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F6" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K6" t="n">
         <v>62.9</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O6" t="n">
         <v>31.8</v>
       </c>
@@ -1107,19 +1089,19 @@
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1127,12 +1109,6 @@
       <c r="AI6" t="n">
         <v>235</v>
       </c>
-      <c r="AK6" t="n">
-        <v>131.69</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
@@ -1146,13 +1122,13 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM6" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1163,19 +1139,19 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C7" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D7" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E7" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F7" t="n">
         <v>10.92</v>
@@ -1199,19 +1175,19 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1232,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM7" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
@@ -1249,26 +1225,41 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B8" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C8" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D8" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E8" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F8" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.1</v>
       </c>
       <c r="K8" t="n">
         <v>62.9</v>
       </c>
+      <c r="M8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O8" t="n">
         <v>31.8</v>
       </c>
@@ -1285,19 +1276,19 @@
         <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1305,6 +1296,12 @@
       <c r="AI8" t="n">
         <v>235</v>
       </c>
+      <c r="AK8" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.46</v>
+      </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
@@ -1318,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM8" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
@@ -1335,46 +1332,46 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B9" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C9" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D9" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E9" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F9" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.9</v>
       </c>
       <c r="N9" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O9" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1383,22 +1380,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA9" t="n">
         <v>16</v>
       </c>
-      <c r="Z9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>19</v>
-      </c>
       <c r="AF9" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1407,10 +1404,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1425,13 +1422,13 @@
         <v>0</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM9" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
@@ -1442,43 +1439,43 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B10" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D10" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E10" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M10" t="n">
         <v>1.9</v>
       </c>
       <c r="N10" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O10" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1493,19 +1490,19 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG10" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1514,10 +1511,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1532,13 +1529,13 @@
         <v>0</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM10" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN10" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
@@ -1549,70 +1546,70 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B11" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C11" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D11" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E11" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H11" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K11" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N11" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O11" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1621,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL11" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1633,19 +1630,19 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM11" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
@@ -1656,46 +1653,46 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B12" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C12" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D12" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E12" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F12" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H12" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K12" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N12" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O12" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R12" t="n">
         <v>0.6</v>
@@ -1704,22 +1701,22 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y12" t="n">
         <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1728,10 +1725,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL12" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1740,19 +1737,19 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS12" t="n">
         <v>13.07</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM12" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN12" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
@@ -1763,70 +1760,43 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B13" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C13" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D13" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O13" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF13" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1834,35 +1804,23 @@
       <c r="AI13" t="n">
         <v>235</v>
       </c>
-      <c r="AK13" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM13" t="n">
         <v>110</v>
       </c>
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM13" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP13" t="n">
         <v>0</v>
@@ -1870,43 +1828,43 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B14" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C14" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D14" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E14" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1921,60 +1879,87 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM14" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B15" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C15" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D15" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E15" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.6</v>
       </c>
       <c r="K15" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>34</v>
       </c>
       <c r="O15" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1982,17 +1967,29 @@
       <c r="AI15" t="n">
         <v>235</v>
       </c>
+      <c r="AK15" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM15" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -2001,75 +1998,75 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B16" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C16" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E16" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F16" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H16" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I16" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K16" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O16" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2078,10 +2075,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2090,16 +2087,16 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM16" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -2108,30 +2105,30 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B17" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D17" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E17" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F17" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H17" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I17" t="n">
         <v>9.800000000000001</v>
@@ -2140,43 +2137,43 @@
         <v>38.6</v>
       </c>
       <c r="K17" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O17" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2185,10 +2182,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2197,93 +2194,93 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS17" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM17" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO17" t="n">
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B18" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C18" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D18" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N18" t="n">
         <v>35.2</v>
       </c>
-      <c r="E18" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O18" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2292,10 +2289,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL18" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2304,93 +2301,60 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS18" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM18" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B19" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C19" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D19" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E19" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H19" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>21</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
         <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2399,10 +2363,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2410,61 +2374,55 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM19" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN19" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B20" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C20" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D20" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2473,10 +2431,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2485,10 +2443,10 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM20" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -2497,42 +2455,42 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B21" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C21" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D21" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E21" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F21" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y21" t="n">
         <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG21" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2541,10 +2499,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL21" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2553,10 +2511,10 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM21" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
@@ -2565,42 +2523,75 @@
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B22" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C22" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D22" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E22" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F22" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
         <v>18</v>
       </c>
       <c r="AA22" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2612,7 +2603,7 @@
         <v>138.94</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2620,11 +2611,17 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM22" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
@@ -2633,51 +2630,51 @@
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B23" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C23" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D23" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E23" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I23" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N23" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O23" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R23" t="n">
         <v>3.5</v>
@@ -2686,22 +2683,22 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2710,10 +2707,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2722,16 +2719,16 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS23" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM23" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
@@ -2740,75 +2737,75 @@
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B24" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C24" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D24" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E24" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H24" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J24" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K24" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N24" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O24" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R24" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2817,10 +2814,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2829,93 +2826,93 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM24" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO24" t="n">
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B25" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D25" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E25" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F25" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H25" t="n">
         <v>25.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J25" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K25" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N25" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O25" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2924,10 +2921,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2936,93 +2933,93 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM25" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN25" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO25" t="n">
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B26" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C26" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D26" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E26" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F26" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H26" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I26" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J26" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O26" t="n">
         <v>38.4</v>
       </c>
-      <c r="K26" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q26" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3031,10 +3028,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3043,93 +3040,66 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS26" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM26" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN26" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO26" t="n">
         <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B27" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C27" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D27" t="n">
         <v>34.5</v>
       </c>
       <c r="E27" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F27" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H27" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K27" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N27" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O27" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF27" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3138,10 +3108,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3149,17 +3119,11 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM27" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
@@ -3168,48 +3132,48 @@
         <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B28" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C28" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D28" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E28" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
         <v>9.6</v>
       </c>
       <c r="K28" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28" t="n">
         <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG28" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3218,10 +3182,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3230,60 +3194,87 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM28" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP28" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B29" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C29" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D29" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38.7</v>
       </c>
       <c r="K29" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>33</v>
       </c>
       <c r="O29" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG29" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3295,7 +3286,7 @@
         <v>128.27</v>
       </c>
       <c r="AL29" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3303,88 +3294,94 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM29" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP29" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B30" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C30" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D30" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F30" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H30" t="n">
         <v>25.1</v>
       </c>
       <c r="I30" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J30" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K30" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O30" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3393,10 +3390,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3405,72 +3402,72 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM30" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP30" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B31" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C31" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D31" t="n">
         <v>34</v>
       </c>
       <c r="E31" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F31" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H31" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I31" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K31" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O31" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q31" t="n">
         <v>23.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3479,19 +3476,19 @@
         <v>23.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3500,10 +3497,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL31" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3512,69 +3509,69 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM31" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP31" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B32" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C32" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D32" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E32" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F32" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I32" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J32" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K32" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O32" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
@@ -3583,22 +3580,22 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA32" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3607,10 +3604,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3619,93 +3616,93 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM32" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN32" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B33" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C33" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D33" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E33" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I33" t="n">
         <v>9.4</v>
       </c>
       <c r="J33" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O33" t="n">
         <v>39.5</v>
       </c>
-      <c r="K33" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q33" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG33" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3714,10 +3711,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3726,93 +3723,66 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS33" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM33" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO33" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP33" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B34" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C34" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D34" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E34" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F34" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y34" t="n">
         <v>8</v>
       </c>
-      <c r="H34" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N34" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O34" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10</v>
-      </c>
       <c r="Z34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3821,10 +3791,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3832,67 +3802,61 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM34" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN34" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP34" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B35" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C35" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D35" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E35" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K35" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O35" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA35" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3901,10 +3865,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL35" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3913,60 +3877,87 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM35" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP35" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B36" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C36" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F36" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>36.7</v>
       </c>
       <c r="O36" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3978,7 +3969,7 @@
         <v>125.11</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3986,88 +3977,94 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>14</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM36" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN36" t="n">
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP36" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B37" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C37" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H37" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K37" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O37" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T37" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4076,10 +4073,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4088,93 +4085,93 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS37" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM37" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN37" t="n">
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP37" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B38" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C38" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E38" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F38" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H38" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K38" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O38" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T38" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG38" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4183,10 +4180,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL38" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4195,93 +4192,93 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS38" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM38" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN38" t="n">
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP38" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B39" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C39" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D39" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E39" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F39" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H39" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q39" t="n">
         <v>23.7</v>
       </c>
-      <c r="I39" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K39" t="n">
-        <v>73</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>34</v>
-      </c>
-      <c r="O39" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S39" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T39" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG39" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4290,10 +4287,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL39" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4302,93 +4299,93 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM39" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN39" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO39" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP39" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B40" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C40" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E40" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F40" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H40" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I40" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>40.8</v>
       </c>
       <c r="K40" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O40" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T40" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4397,10 +4394,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL40" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4409,93 +4406,66 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS40" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM40" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN40" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO40" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP40" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B41" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C41" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E41" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J41" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K41" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4</v>
-      </c>
-      <c r="N41" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O41" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z41" t="n">
         <v>13</v>
       </c>
       <c r="AA41" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF41" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4504,10 +4474,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL41" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4515,67 +4485,61 @@
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM41" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN41" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO41" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP41" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B42" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C42" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E42" t="n">
         <v>29.8</v>
       </c>
       <c r="F42" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K42" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O42" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA42" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4584,10 +4548,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4596,33 +4560,33 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM42" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN42" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP42" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B43" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C43" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D43" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E43" t="n">
         <v>29.8</v>
@@ -4631,25 +4595,25 @@
         <v>6.6</v>
       </c>
       <c r="K43" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA43" t="n">
         <v>12.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG43" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4658,10 +4622,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL43" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4670,60 +4634,87 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM43" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN43" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO43" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP43" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B44" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C44" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D44" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E44" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F44" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>41.1</v>
       </c>
       <c r="K44" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>37.4</v>
       </c>
       <c r="O44" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y44" t="n">
         <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA44" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF44" t="n">
         <v>220</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4735,7 +4726,7 @@
         <v>126.54</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4743,88 +4734,94 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM44" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN44" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO44" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP44" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B45" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C45" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D45" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E45" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F45" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H45" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I45" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K45" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N45" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O45" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF45" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4833,10 +4830,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4845,93 +4842,93 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS45" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM45" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN45" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO45" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP45" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B46" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C46" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E46" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F46" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H46" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I46" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K46" t="n">
         <v>76.5</v>
       </c>
       <c r="M46" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N46" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O46" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R46" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z46" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA46" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG46" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4940,10 +4937,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4952,72 +4949,72 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS46" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM46" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN46" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO46" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP46" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B47" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C47" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D47" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E47" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H47" t="n">
         <v>26.1</v>
       </c>
       <c r="I47" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J47" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K47" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N47" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O47" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q47" t="n">
         <v>24.2</v>
       </c>
       <c r="R47" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -5026,19 +5023,19 @@
         <v>24.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z47" t="n">
         <v>16</v>
       </c>
       <c r="AA47" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5047,10 +5044,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5059,93 +5056,66 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS47" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM47" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN47" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO47" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP47" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B48" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C48" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D48" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E48" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H48" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K48" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M48" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="n">
         <v>16</v>
       </c>
       <c r="AA48" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF48" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5154,10 +5124,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL48" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5165,67 +5135,61 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM48" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN48" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO48" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP48" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B49" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C49" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D49" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E49" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F49" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K49" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
         <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF49" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5234,10 +5198,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>133</v>
+        <v>125.03</v>
       </c>
       <c r="AL49" t="n">
-        <v>8.34</v>
+        <v>-0.9</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5246,60 +5210,87 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM49" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN49" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP49" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B50" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C50" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D50" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E50" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F50" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J50" t="n">
+        <v>41.3</v>
       </c>
       <c r="K50" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N50" t="n">
+        <v>37.1</v>
       </c>
       <c r="O50" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z50" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF50" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5308,7 +5299,7 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>133</v>
+        <v>125.03</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -5319,88 +5310,94 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM50" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN50" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO50" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP50" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B51" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C51" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E51" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F51" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I51" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K51" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M51" t="n">
         <v>2.7</v>
       </c>
       <c r="N51" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O51" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R51" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T51" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Y51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA51" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5409,10 +5406,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL51" t="n">
-        <v>-7.97</v>
+        <v>4.54</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5421,78 +5418,78 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM51" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN51" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO51" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP51" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B52" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C52" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D52" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E52" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F52" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I52" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K52" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O52" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R52" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>16</v>
       </c>
       <c r="T52" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y52" t="n">
         <v>10</v>
@@ -5501,13 +5498,13 @@
         <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF52" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5516,10 +5513,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL52" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5528,93 +5525,93 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM52" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN52" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO52" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP52" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B53" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C53" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D53" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E53" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F53" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H53" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I53" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K53" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N53" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O53" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S53" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y53" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF53" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5623,10 +5620,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL53" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5635,78 +5632,78 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM53" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN53" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO53" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP53" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B54" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C54" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D54" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E54" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F54" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H54" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I54" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J54" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K54" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M54" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O54" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
       </c>
       <c r="T54" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y54" t="n">
         <v>13</v>
@@ -5715,13 +5712,13 @@
         <v>18</v>
       </c>
       <c r="AA54" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF54" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5730,10 +5727,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL54" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5742,93 +5739,66 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS54" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM54" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN54" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO54" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP54" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B55" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C55" t="n">
         <v>57.9</v>
       </c>
       <c r="D55" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E55" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F55" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H55" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N55" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S55" t="n">
-        <v>12</v>
-      </c>
-      <c r="T55" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="Y55" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z55" t="n">
         <v>18</v>
       </c>
       <c r="AA55" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5837,10 +5807,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL55" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5848,67 +5818,61 @@
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM55" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN55" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO55" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP55" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B56" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C56" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D56" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E56" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K56" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O56" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Y56" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z56" t="n">
         <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF56" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5917,10 +5881,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>133</v>
+        <v>128.43</v>
       </c>
       <c r="AL56" t="n">
-        <v>8.27</v>
+        <v>2.54</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5929,60 +5893,87 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM56" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN56" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO56" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP56" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B57" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C57" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D57" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E57" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F57" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40.6</v>
       </c>
       <c r="K57" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>36</v>
       </c>
       <c r="O57" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>11</v>
+      </c>
+      <c r="T57" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA57" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF57" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5991,7 +5982,7 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>133</v>
+        <v>128.43</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -6002,88 +5993,94 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM57" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN57" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO57" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP57" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B58" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C58" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D58" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E58" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F58" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H58" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I58" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K58" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N58" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O58" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T58" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6092,10 +6089,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL58" t="n">
-        <v>-4.57</v>
+        <v>2.39</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6104,93 +6101,93 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS58" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM58" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN58" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO58" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP58" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B59" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C59" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D59" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E59" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F59" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H59" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I59" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K59" t="n">
         <v>75.7</v>
       </c>
       <c r="M59" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O59" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R59" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T59" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA59" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF59" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6199,10 +6196,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL59" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6211,93 +6208,93 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS59" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM59" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN59" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO59" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP59" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B60" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C60" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D60" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E60" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F60" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K60" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O60" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R60" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S60" t="n">
         <v>17</v>
       </c>
       <c r="T60" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA60" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF60" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6306,10 +6303,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL60" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6318,54 +6315,60 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS60" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM60" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN60" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO60" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP60" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B61" t="n">
-        <v>152.3</v>
+        <v>150.7</v>
       </c>
       <c r="C61" t="n">
-        <v>65.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>33.6</v>
+        <v>32.9</v>
       </c>
       <c r="E61" t="n">
-        <v>37</v>
+        <v>35.3</v>
       </c>
       <c r="F61" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z61" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA61" t="n">
-        <v>12</v>
+        <v>14.5</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>222.99</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>4.08</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6374,10 +6377,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>133</v>
+        <v>127.44</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.69</v>
+        <v>-0.09</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6386,36 +6389,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B62" t="n">
-        <v>150.7</v>
+        <v>147.9</v>
       </c>
       <c r="C62" t="n">
-        <v>66.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="D62" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E62" t="n">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
       <c r="F62" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="Y62" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z62" t="n">
         <v>17</v>
       </c>
       <c r="AA62" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6423,12 +6426,6 @@
       <c r="AI62" t="n">
         <v>235</v>
       </c>
-      <c r="AK62" t="n">
-        <v>133</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
       <c r="AM62" t="n">
         <v>110</v>
       </c>
@@ -6436,7 +6433,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>16</v>
       </c>
+      <c r="V2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>17</v>
       </c>
@@ -686,6 +695,15 @@
       </c>
       <c r="AA2" t="n">
         <v>19</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="AF2" t="n">
         <v>235.47</v>
@@ -782,6 +800,15 @@
       <c r="T3" t="n">
         <v>17</v>
       </c>
+      <c r="V3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="Y3" t="n">
         <v>18</v>
       </c>
@@ -790,6 +817,15 @@
       </c>
       <c r="AA3" t="n">
         <v>21</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>7.1</v>
       </c>
       <c r="AF3" t="n">
         <v>230.5</v>
@@ -889,6 +925,15 @@
       <c r="T4" t="n">
         <v>17</v>
       </c>
+      <c r="V4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="Y4" t="n">
         <v>20</v>
       </c>
@@ -897,6 +942,15 @@
       </c>
       <c r="AA4" t="n">
         <v>21</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7.9</v>
       </c>
       <c r="AF4" t="n">
         <v>225.8</v>
@@ -996,6 +1050,15 @@
       <c r="T5" t="n">
         <v>17</v>
       </c>
+      <c r="V5" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22</v>
+      </c>
       <c r="Y5" t="n">
         <v>19</v>
       </c>
@@ -1004,6 +1067,15 @@
       </c>
       <c r="AA5" t="n">
         <v>22</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10.9</v>
       </c>
       <c r="AF5" t="n">
         <v>220</v>
@@ -1088,6 +1160,15 @@
       <c r="T6" t="n">
         <v>17</v>
       </c>
+      <c r="V6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>22.5</v>
+      </c>
       <c r="Y6" t="n">
         <v>17</v>
       </c>
@@ -1096,6 +1177,15 @@
       </c>
       <c r="AA6" t="n">
         <v>20.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6.8</v>
       </c>
       <c r="AF6" t="n">
         <v>216.02</v>
@@ -1174,6 +1264,15 @@
       <c r="T7" t="n">
         <v>17</v>
       </c>
+      <c r="V7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>30</v>
+      </c>
+      <c r="X7" t="n">
+        <v>24.3</v>
+      </c>
       <c r="Y7" t="n">
         <v>15</v>
       </c>
@@ -1182,6 +1281,15 @@
       </c>
       <c r="AA7" t="n">
         <v>18.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.9</v>
       </c>
       <c r="AF7" t="n">
         <v>216.08</v>
@@ -1275,6 +1383,15 @@
       <c r="T8" t="n">
         <v>17</v>
       </c>
+      <c r="V8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>28</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23.9</v>
+      </c>
       <c r="Y8" t="n">
         <v>16</v>
       </c>
@@ -1283,6 +1400,15 @@
       </c>
       <c r="AA8" t="n">
         <v>19</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF8" t="n">
         <v>216.1</v>
@@ -1382,6 +1508,15 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1390,6 +1525,15 @@
       </c>
       <c r="AA9" t="n">
         <v>16</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.2</v>
       </c>
       <c r="AF9" t="n">
         <v>217.8</v>
@@ -1489,6 +1633,15 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y10" t="n">
         <v>10</v>
       </c>
@@ -1497,6 +1650,15 @@
       </c>
       <c r="AA10" t="n">
         <v>14</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF10" t="n">
         <v>213</v>
@@ -1596,6 +1758,15 @@
       <c r="T11" t="n">
         <v>21.5</v>
       </c>
+      <c r="V11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Y11" t="n">
         <v>12</v>
       </c>
@@ -1604,6 +1775,15 @@
       </c>
       <c r="AA11" t="n">
         <v>16.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>6.6</v>
       </c>
       <c r="AF11" t="n">
         <v>210.3</v>
@@ -1703,6 +1883,15 @@
       <c r="T12" t="n">
         <v>19.8</v>
       </c>
+      <c r="V12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>12</v>
       </c>
@@ -1711,6 +1900,15 @@
       </c>
       <c r="AA12" t="n">
         <v>17.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.3</v>
       </c>
       <c r="AF12" t="n">
         <v>214.63</v>
@@ -1783,6 +1981,15 @@
       <c r="O13" t="n">
         <v>28.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>18.4</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1791,6 +1998,15 @@
       </c>
       <c r="AA13" t="n">
         <v>18</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF13" t="n">
         <v>213.96</v>
@@ -1851,6 +2067,15 @@
       <c r="O14" t="n">
         <v>36.4</v>
       </c>
+      <c r="V14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>18.5</v>
+      </c>
       <c r="Y14" t="n">
         <v>14</v>
       </c>
@@ -1859,6 +2084,15 @@
       </c>
       <c r="AA14" t="n">
         <v>18.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF14" t="n">
         <v>212.08</v>
@@ -1946,6 +2180,15 @@
       <c r="T15" t="n">
         <v>16.2</v>
       </c>
+      <c r="V15" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19</v>
+      </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
@@ -1954,6 +2197,15 @@
       </c>
       <c r="AA15" t="n">
         <v>13.4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.1</v>
       </c>
       <c r="AF15" t="n">
         <v>212.1</v>
@@ -2053,6 +2305,15 @@
       <c r="T16" t="n">
         <v>24.5</v>
       </c>
+      <c r="V16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.5</v>
+      </c>
       <c r="Y16" t="n">
         <v>7</v>
       </c>
@@ -2061,6 +2322,15 @@
       </c>
       <c r="AA16" t="n">
         <v>11.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.1</v>
       </c>
       <c r="AF16" t="n">
         <v>211.95</v>
@@ -2160,6 +2430,15 @@
       <c r="T17" t="n">
         <v>21.8</v>
       </c>
+      <c r="V17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2168,6 +2447,15 @@
       </c>
       <c r="AA17" t="n">
         <v>15.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="AF17" t="n">
         <v>208.67</v>
@@ -2267,6 +2555,15 @@
       <c r="T18" t="n">
         <v>21</v>
       </c>
+      <c r="V18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y18" t="n">
         <v>12</v>
       </c>
@@ -2275,6 +2572,15 @@
       </c>
       <c r="AA18" t="n">
         <v>16</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF18" t="n">
         <v>208.07</v>
@@ -2341,6 +2647,15 @@
       <c r="F19" t="n">
         <v>9.800000000000001</v>
       </c>
+      <c r="V19" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>23</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.8</v>
+      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2349,6 +2664,15 @@
       </c>
       <c r="AA19" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>7.2</v>
       </c>
       <c r="AF19" t="n">
         <v>205.66</v>
@@ -2409,6 +2733,15 @@
       <c r="F20" t="n">
         <v>9.1</v>
       </c>
+      <c r="V20" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>18</v>
+      </c>
       <c r="Y20" t="n">
         <v>13</v>
       </c>
@@ -2417,6 +2750,15 @@
       </c>
       <c r="AA20" t="n">
         <v>19</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF20" t="n">
         <v>215.07</v>
@@ -2477,6 +2819,15 @@
       <c r="F21" t="n">
         <v>8.6</v>
       </c>
+      <c r="V21" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
       <c r="Y21" t="n">
         <v>13</v>
       </c>
@@ -2485,6 +2836,15 @@
       </c>
       <c r="AA21" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
         <v>218.94</v>
@@ -2578,6 +2938,15 @@
       <c r="T22" t="n">
         <v>22.3</v>
       </c>
+      <c r="V22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>5</v>
       </c>
@@ -2586,6 +2955,15 @@
       </c>
       <c r="AA22" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>6.8</v>
       </c>
       <c r="AF22" t="n">
         <v>216.4</v>
@@ -2685,6 +3063,15 @@
       <c r="T23" t="n">
         <v>22.2</v>
       </c>
+      <c r="V23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2693,6 +3080,15 @@
       </c>
       <c r="AA23" t="n">
         <v>16.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
         <v>224.66</v>
@@ -2792,6 +3188,15 @@
       <c r="T24" t="n">
         <v>22.9</v>
       </c>
+      <c r="V24" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19.7</v>
+      </c>
       <c r="Y24" t="n">
         <v>13</v>
       </c>
@@ -2800,6 +3205,15 @@
       </c>
       <c r="AA24" t="n">
         <v>20.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>7.5</v>
       </c>
       <c r="AF24" t="n">
         <v>223.02</v>
@@ -2899,6 +3313,15 @@
       <c r="T25" t="n">
         <v>19.7</v>
       </c>
+      <c r="V25" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y25" t="n">
         <v>19</v>
       </c>
@@ -2907,6 +3330,15 @@
       </c>
       <c r="AA25" t="n">
         <v>22.1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>6.9</v>
       </c>
       <c r="AF25" t="n">
         <v>225.57</v>
@@ -3006,6 +3438,15 @@
       <c r="T26" t="n">
         <v>20.6</v>
       </c>
+      <c r="V26" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W26" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y26" t="n">
         <v>15</v>
       </c>
@@ -3014,6 +3455,15 @@
       </c>
       <c r="AA26" t="n">
         <v>13.9</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF26" t="n">
         <v>232.44</v>
@@ -3086,6 +3536,15 @@
       <c r="O27" t="n">
         <v>36.5</v>
       </c>
+      <c r="V27" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W27" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X27" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Y27" t="n">
         <v>7</v>
       </c>
@@ -3094,6 +3553,15 @@
       </c>
       <c r="AA27" t="n">
         <v>10</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
         <v>228.64</v>
@@ -3160,6 +3628,15 @@
       <c r="O28" t="n">
         <v>34.2</v>
       </c>
+      <c r="V28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y28" t="n">
         <v>6</v>
       </c>
@@ -3168,6 +3645,15 @@
       </c>
       <c r="AA28" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
         <v>225.16</v>
@@ -3261,6 +3747,15 @@
       <c r="T29" t="n">
         <v>23.3</v>
       </c>
+      <c r="V29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X29" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y29" t="n">
         <v>3</v>
       </c>
@@ -3269,6 +3764,15 @@
       </c>
       <c r="AA29" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>6.8</v>
       </c>
       <c r="AF29" t="n">
         <v>225.13</v>
@@ -3368,6 +3872,15 @@
       <c r="T30" t="n">
         <v>23.1</v>
       </c>
+      <c r="V30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y30" t="n">
         <v>4</v>
       </c>
@@ -3376,6 +3889,15 @@
       </c>
       <c r="AA30" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>7.7</v>
       </c>
       <c r="AF30" t="n">
         <v>223.85</v>
@@ -3475,6 +3997,15 @@
       <c r="T31" t="n">
         <v>23.1</v>
       </c>
+      <c r="V31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y31" t="n">
         <v>9</v>
       </c>
@@ -3483,6 +4014,15 @@
       </c>
       <c r="AA31" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>8.6</v>
       </c>
       <c r="AF31" t="n">
         <v>222.91</v>
@@ -3582,6 +4122,15 @@
       <c r="T32" t="n">
         <v>22.7</v>
       </c>
+      <c r="V32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23</v>
+      </c>
+      <c r="X32" t="n">
+        <v>16.2</v>
+      </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
@@ -3590,6 +4139,15 @@
       </c>
       <c r="AA32" t="n">
         <v>12.6</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>5.9</v>
       </c>
       <c r="AF32" t="n">
         <v>222.98</v>
@@ -3689,6 +4247,15 @@
       <c r="T33" t="n">
         <v>23.5</v>
       </c>
+      <c r="V33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X33" t="n">
+        <v>15.9</v>
+      </c>
       <c r="Y33" t="n">
         <v>10</v>
       </c>
@@ -3697,6 +4264,15 @@
       </c>
       <c r="AA33" t="n">
         <v>12.2</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>6.6</v>
       </c>
       <c r="AF33" t="n">
         <v>221.26</v>
@@ -3769,6 +4345,15 @@
       <c r="O34" t="n">
         <v>39.1</v>
       </c>
+      <c r="V34" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3777,6 +4362,15 @@
       </c>
       <c r="AA34" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>5.2</v>
       </c>
       <c r="AF34" t="n">
         <v>221.88</v>
@@ -3843,6 +4437,15 @@
       <c r="O35" t="n">
         <v>38.7</v>
       </c>
+      <c r="V35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X35" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3851,6 +4454,15 @@
       </c>
       <c r="AA35" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4</v>
       </c>
       <c r="AF35" t="n">
         <v>223.58</v>
@@ -3944,6 +4556,15 @@
       <c r="T36" t="n">
         <v>23.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W36" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3952,6 +4573,15 @@
       </c>
       <c r="AA36" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF36" t="n">
         <v>223.6</v>
@@ -4051,6 +4681,15 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
+      <c r="V37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>3</v>
       </c>
@@ -4059,6 +4698,15 @@
       </c>
       <c r="AA37" t="n">
         <v>10.7</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF37" t="n">
         <v>223.66</v>
@@ -4158,6 +4806,15 @@
       <c r="T38" t="n">
         <v>22.8</v>
       </c>
+      <c r="V38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W38" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X38" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y38" t="n">
         <v>6</v>
       </c>
@@ -4166,6 +4823,15 @@
       </c>
       <c r="AA38" t="n">
         <v>12.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.5</v>
       </c>
       <c r="AF38" t="n">
         <v>220.58</v>
@@ -4265,6 +4931,15 @@
       <c r="T39" t="n">
         <v>23.7</v>
       </c>
+      <c r="V39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W39" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X39" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y39" t="n">
         <v>8</v>
       </c>
@@ -4273,6 +4948,15 @@
       </c>
       <c r="AA39" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>8.4</v>
       </c>
       <c r="AF39" t="n">
         <v>218.18</v>
@@ -4372,6 +5056,15 @@
       <c r="T40" t="n">
         <v>23.9</v>
       </c>
+      <c r="V40" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12.7</v>
+      </c>
       <c r="Y40" t="n">
         <v>6</v>
       </c>
@@ -4380,6 +5073,15 @@
       </c>
       <c r="AA40" t="n">
         <v>8.4</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF40" t="n">
         <v>212.3</v>
@@ -4452,6 +5154,15 @@
       <c r="O41" t="n">
         <v>34.4</v>
       </c>
+      <c r="V41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W41" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y41" t="n">
         <v>5</v>
       </c>
@@ -4460,6 +5171,15 @@
       </c>
       <c r="AA41" t="n">
         <v>9</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF41" t="n">
         <v>214.64</v>
@@ -4526,6 +5246,15 @@
       <c r="O42" t="n">
         <v>35.2</v>
       </c>
+      <c r="V42" t="n">
+        <v>8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.2</v>
+      </c>
       <c r="Y42" t="n">
         <v>10</v>
       </c>
@@ -4534,6 +5263,15 @@
       </c>
       <c r="AA42" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>6</v>
       </c>
       <c r="AF42" t="n">
         <v>218.66</v>
@@ -4600,6 +5338,15 @@
       <c r="O43" t="n">
         <v>39.6</v>
       </c>
+      <c r="V43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W43" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4608,6 +5355,15 @@
       </c>
       <c r="AA43" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>5.6</v>
       </c>
       <c r="AF43" t="n">
         <v>220</v>
@@ -4701,6 +5457,15 @@
       <c r="T44" t="n">
         <v>24.4</v>
       </c>
+      <c r="V44" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y44" t="n">
         <v>9</v>
       </c>
@@ -4709,6 +5474,15 @@
       </c>
       <c r="AA44" t="n">
         <v>12.7</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>8.6</v>
       </c>
       <c r="AF44" t="n">
         <v>220</v>
@@ -4808,6 +5582,15 @@
       <c r="T45" t="n">
         <v>24.1</v>
       </c>
+      <c r="V45" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>15.1</v>
+      </c>
       <c r="Y45" t="n">
         <v>7.2</v>
       </c>
@@ -4816,6 +5599,15 @@
       </c>
       <c r="AA45" t="n">
         <v>12.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF45" t="n">
         <v>219.23</v>
@@ -4915,6 +5707,15 @@
       <c r="T46" t="n">
         <v>24.2</v>
       </c>
+      <c r="V46" t="n">
+        <v>10</v>
+      </c>
+      <c r="W46" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="X46" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y46" t="n">
         <v>9</v>
       </c>
@@ -4923,6 +5724,15 @@
       </c>
       <c r="AA46" t="n">
         <v>13.3</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF46" t="n">
         <v>216.29</v>
@@ -5022,6 +5832,15 @@
       <c r="T47" t="n">
         <v>24.2</v>
       </c>
+      <c r="V47" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W47" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>15.4</v>
+      </c>
       <c r="Y47" t="n">
         <v>11</v>
       </c>
@@ -5030,6 +5849,15 @@
       </c>
       <c r="AA47" t="n">
         <v>13.8</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>7.6</v>
       </c>
       <c r="AF47" t="n">
         <v>216.91</v>
@@ -5102,6 +5930,15 @@
       <c r="O48" t="n">
         <v>37.8</v>
       </c>
+      <c r="V48" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W48" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>16</v>
+      </c>
       <c r="Y48" t="n">
         <v>12</v>
       </c>
@@ -5110,6 +5947,15 @@
       </c>
       <c r="AA48" t="n">
         <v>14</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF48" t="n">
         <v>217.5</v>
@@ -5176,6 +6022,15 @@
       <c r="O49" t="n">
         <v>37.7</v>
       </c>
+      <c r="V49" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="X49" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y49" t="n">
         <v>10</v>
       </c>
@@ -5184,6 +6039,15 @@
       </c>
       <c r="AA49" t="n">
         <v>13</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>7.9</v>
       </c>
       <c r="AF49" t="n">
         <v>217.82</v>
@@ -5277,6 +6141,15 @@
       <c r="T50" t="n">
         <v>23.9</v>
       </c>
+      <c r="V50" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y50" t="n">
         <v>3</v>
       </c>
@@ -5285,6 +6158,15 @@
       </c>
       <c r="AA50" t="n">
         <v>12</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF50" t="n">
         <v>217.8</v>
@@ -5384,6 +6266,15 @@
       <c r="T51" t="n">
         <v>24</v>
       </c>
+      <c r="V51" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W51" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y51" t="n">
         <v>10</v>
       </c>
@@ -5392,6 +6283,15 @@
       </c>
       <c r="AA51" t="n">
         <v>11.9</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.9</v>
       </c>
       <c r="AF51" t="n">
         <v>219.54</v>
@@ -5491,6 +6391,15 @@
       <c r="T52" t="n">
         <v>23.9</v>
       </c>
+      <c r="V52" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X52" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Y52" t="n">
         <v>10</v>
       </c>
@@ -5499,6 +6408,15 @@
       </c>
       <c r="AA52" t="n">
         <v>14.1</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF52" t="n">
         <v>220.65</v>
@@ -5598,6 +6516,15 @@
       <c r="T53" t="n">
         <v>23.7</v>
       </c>
+      <c r="V53" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>19.2</v>
+      </c>
       <c r="Y53" t="n">
         <v>13</v>
       </c>
@@ -5606,6 +6533,15 @@
       </c>
       <c r="AA53" t="n">
         <v>14</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.2</v>
       </c>
       <c r="AF53" t="n">
         <v>219.97</v>
@@ -5705,6 +6641,15 @@
       <c r="T54" t="n">
         <v>23.5</v>
       </c>
+      <c r="V54" t="n">
+        <v>17</v>
+      </c>
+      <c r="W54" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y54" t="n">
         <v>13</v>
       </c>
@@ -5713,6 +6658,15 @@
       </c>
       <c r="AA54" t="n">
         <v>15.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF54" t="n">
         <v>223.97</v>
@@ -5785,6 +6739,15 @@
       <c r="O55" t="n">
         <v>39</v>
       </c>
+      <c r="V55" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X55" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y55" t="n">
         <v>15</v>
       </c>
@@ -5793,6 +6756,15 @@
       </c>
       <c r="AA55" t="n">
         <v>16.5</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF55" t="n">
         <v>226.45</v>
@@ -6390,6 +7362,18 @@
       </c>
       <c r="BL61" s="1" t="n">
         <v>46184</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>705.1</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>2933.3</v>
       </c>
     </row>
     <row r="62">

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,46 +628,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B2" t="n">
-        <v>119.7</v>
+        <v>116.54</v>
       </c>
       <c r="C2" t="n">
-        <v>25.9</v>
+        <v>23.39</v>
       </c>
       <c r="D2" t="n">
-        <v>38.7</v>
+        <v>36.98</v>
       </c>
       <c r="E2" t="n">
-        <v>34.5</v>
+        <v>35.59</v>
       </c>
       <c r="F2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="H2" t="n">
         <v>20.5</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J2" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
       <c r="K2" t="n">
         <v>62.9</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>30.6</v>
+        <v>29.2</v>
       </c>
       <c r="O2" t="n">
         <v>31.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -676,40 +676,40 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V2" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="W2" t="n">
-        <v>24.8</v>
+        <v>26.2</v>
       </c>
       <c r="X2" t="n">
-        <v>19.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="n">
         <v>21</v>
       </c>
-      <c r="AA2" t="n">
-        <v>19</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.7</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>235.47</v>
+        <v>230.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4.98</v>
+        <v>-4.67</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,7 +718,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>136.17</v>
+        <v>136.01</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -733,13 +733,13 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="BM2" t="n">
-        <v>54.51</v>
+        <v>37.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>285.1</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -750,40 +750,40 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B3" t="n">
-        <v>116.54</v>
+        <v>117.05</v>
       </c>
       <c r="C3" t="n">
-        <v>23.39</v>
+        <v>23.91</v>
       </c>
       <c r="D3" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
       <c r="E3" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="F3" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="H3" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J3" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="K3" t="n">
         <v>62.9</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N3" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="O3" t="n">
         <v>31.8</v>
@@ -801,37 +801,37 @@
         <v>17</v>
       </c>
       <c r="V3" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="W3" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="X3" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
         <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>230.5</v>
+        <v>225.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4.67</v>
+        <v>-5.78</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -840,10 +840,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>136.01</v>
+        <v>132.41</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.16</v>
+        <v>-3.6</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="BM3" t="n">
-        <v>37.84</v>
+        <v>41.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>285.1</v>
+        <v>334.1</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -875,40 +875,40 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B4" t="n">
-        <v>117.05</v>
+        <v>117.63</v>
       </c>
       <c r="C4" t="n">
-        <v>23.91</v>
+        <v>24.3</v>
       </c>
       <c r="D4" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="E4" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="F4" t="n">
-        <v>10.56</v>
+        <v>10.75</v>
       </c>
       <c r="H4" t="n">
         <v>22.3</v>
       </c>
       <c r="I4" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K4" t="n">
         <v>62.9</v>
       </c>
       <c r="M4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N4" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="O4" t="n">
         <v>31.8</v>
@@ -929,34 +929,34 @@
         <v>19.1</v>
       </c>
       <c r="W4" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="X4" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA4" t="n">
         <v>22</v>
       </c>
-      <c r="AA4" t="n">
-        <v>21</v>
-      </c>
       <c r="AB4" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>225.8</v>
+        <v>220</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5.78</v>
+        <v>-2.67</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -965,10 +965,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>132.41</v>
+        <v>131.69</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3.6</v>
+        <v>-0.72</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -983,13 +983,13 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BM4" t="n">
-        <v>41.59</v>
+        <v>42.83</v>
       </c>
       <c r="BN4" t="n">
-        <v>334.1</v>
+        <v>106.5</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -1000,41 +1000,26 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B5" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C5" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D5" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E5" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F5" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H5" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K5" t="n">
         <v>62.9</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O5" t="n">
         <v>31.8</v>
       </c>
@@ -1051,37 +1036,37 @@
         <v>17</v>
       </c>
       <c r="V5" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="W5" t="n">
-        <v>24.8</v>
+        <v>26.7</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.9</v>
+        <v>6.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1089,12 +1074,6 @@
       <c r="AI5" t="n">
         <v>235</v>
       </c>
-      <c r="AK5" t="n">
-        <v>131.69</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
@@ -1108,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM5" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1125,19 +1104,19 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C6" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D6" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E6" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F6" t="n">
         <v>10.92</v>
@@ -1161,37 +1140,37 @@
         <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="W6" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="X6" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.1</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1212,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM6" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -1229,26 +1208,41 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B7" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C7" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E7" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F7" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.1</v>
       </c>
       <c r="K7" t="n">
         <v>62.9</v>
       </c>
+      <c r="M7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O7" t="n">
         <v>31.8</v>
       </c>
@@ -1265,37 +1259,37 @@
         <v>17</v>
       </c>
       <c r="V7" t="n">
-        <v>18.6</v>
+        <v>19.9</v>
       </c>
       <c r="W7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="X7" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1303,6 +1297,12 @@
       <c r="AI7" t="n">
         <v>235</v>
       </c>
+      <c r="AK7" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.46</v>
+      </c>
       <c r="AM7" t="n">
         <v>110</v>
       </c>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM7" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
@@ -1333,46 +1333,46 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B8" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C8" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D8" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E8" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F8" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I8" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.9</v>
       </c>
       <c r="N8" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O8" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1381,40 +1381,40 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>19.9</v>
+        <v>17.5</v>
       </c>
       <c r="W8" t="n">
-        <v>28</v>
+        <v>20.8</v>
       </c>
       <c r="X8" t="n">
-        <v>23.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA8" t="n">
         <v>16</v>
       </c>
-      <c r="Z8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>19</v>
-      </c>
       <c r="AB8" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>11.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1423,10 +1423,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1441,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM8" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -1458,43 +1458,43 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B9" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C9" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D9" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E9" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M9" t="n">
         <v>1.9</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O9" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1509,37 +1509,37 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>17.5</v>
+        <v>16.1</v>
       </c>
       <c r="W9" t="n">
-        <v>20.8</v>
+        <v>18</v>
       </c>
       <c r="X9" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG9" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1548,10 +1548,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM9" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN9" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
@@ -1583,88 +1583,88 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B10" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C10" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D10" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E10" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H10" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K10" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N10" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O10" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V10" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="W10" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="X10" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1673,10 +1673,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL10" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1685,19 +1685,19 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM10" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
@@ -1708,46 +1708,46 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B11" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C11" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D11" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E11" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F11" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H11" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K11" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N11" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O11" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R11" t="n">
         <v>0.6</v>
@@ -1756,40 +1756,40 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="V11" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W11" t="n">
-        <v>20.5</v>
+        <v>19.6</v>
       </c>
       <c r="X11" t="n">
-        <v>18.2</v>
+        <v>17.6</v>
       </c>
       <c r="Y11" t="n">
         <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>12.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.6</v>
+        <v>10.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1798,10 +1798,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1810,19 +1810,19 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS11" t="n">
         <v>13.07</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM11" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN11" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
@@ -1833,88 +1833,61 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B12" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C12" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D12" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E12" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J12" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O12" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.7</v>
+        <v>14.4</v>
       </c>
       <c r="W12" t="n">
-        <v>19.6</v>
+        <v>22.4</v>
       </c>
       <c r="X12" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="Y12" t="n">
         <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.3</v>
+        <v>6.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1922,35 +1895,23 @@
       <c r="AI12" t="n">
         <v>235</v>
       </c>
-      <c r="AK12" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM12" t="n">
         <v>110</v>
       </c>
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM12" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP12" t="n">
         <v>0</v>
@@ -1958,61 +1919,61 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B13" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C13" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D13" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E13" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W13" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="X13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -2027,78 +1988,105 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM13" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B14" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C14" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D14" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E14" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>35.6</v>
       </c>
       <c r="K14" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>34</v>
       </c>
       <c r="O14" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>16.2</v>
       </c>
       <c r="V14" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="W14" t="n">
-        <v>22.5</v>
+        <v>24.6</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>-5.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.7</v>
+        <v>0.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -2106,17 +2094,29 @@
       <c r="AI14" t="n">
         <v>235</v>
       </c>
+      <c r="AK14" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM14" t="n">
         <v>110</v>
       </c>
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM14" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -2125,93 +2125,93 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B15" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C15" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E15" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F15" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H15" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I15" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K15" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O15" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X15" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-5.8</v>
-      </c>
       <c r="AC15" t="n">
-        <v>5.9</v>
+        <v>10.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1</v>
+        <v>6.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2220,10 +2220,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2232,16 +2232,16 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM15" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -2250,30 +2250,30 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B16" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D16" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E16" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F16" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H16" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I16" t="n">
         <v>9.800000000000001</v>
@@ -2282,61 +2282,61 @@
         <v>38.6</v>
       </c>
       <c r="K16" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O16" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>17.8</v>
+        <v>16.9</v>
       </c>
       <c r="X16" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AF16" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2345,10 +2345,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2357,111 +2357,111 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM16" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO16" t="n">
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B17" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C17" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D17" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N17" t="n">
         <v>35.2</v>
       </c>
-      <c r="E17" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O17" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="W17" t="n">
-        <v>16.9</v>
+        <v>20.6</v>
       </c>
       <c r="X17" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2470,10 +2470,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL17" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2482,111 +2482,78 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM17" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO17" t="n">
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B18" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C18" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D18" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E18" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H18" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>21</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="W18" t="n">
-        <v>20.6</v>
+        <v>23</v>
       </c>
       <c r="X18" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
         <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2595,10 +2562,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2606,79 +2573,73 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM18" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN18" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B19" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C19" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D19" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="V19" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="W19" t="n">
-        <v>23</v>
+        <v>24.9</v>
       </c>
       <c r="X19" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.1</v>
+        <v>6.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2687,10 +2648,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2699,10 +2660,10 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM19" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -2711,60 +2672,60 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B20" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C20" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D20" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E20" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F20" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="V20" t="n">
-        <v>11.2</v>
+        <v>15.9</v>
       </c>
       <c r="W20" t="n">
-        <v>24.9</v>
+        <v>18.1</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
         <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2773,10 +2734,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL20" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2785,10 +2746,10 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM20" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -2797,60 +2758,93 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B21" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C21" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D21" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E21" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F21" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>22.3</v>
       </c>
       <c r="V21" t="n">
-        <v>15.9</v>
+        <v>11.8</v>
       </c>
       <c r="W21" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="X21" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
         <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>11.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2862,7 +2856,7 @@
         <v>138.94</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2870,11 +2864,17 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM21" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
@@ -2883,51 +2883,51 @@
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B22" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C22" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D22" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E22" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I22" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M22" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O22" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R22" t="n">
         <v>3.5</v>
@@ -2936,40 +2936,40 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W22" t="n">
         <v>22.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>21</v>
       </c>
       <c r="X22" t="n">
         <v>16.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.4</v>
+        <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AF22" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2978,10 +2978,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2990,16 +2990,16 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS22" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM22" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
@@ -3008,93 +3008,93 @@
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B23" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C23" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E23" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H23" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J23" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K23" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N23" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O23" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R23" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="V23" t="n">
-        <v>10.4</v>
+        <v>13.6</v>
       </c>
       <c r="W23" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="X23" t="n">
-        <v>16.4</v>
+        <v>19.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AB23" t="n">
         <v>5.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG23" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -3103,10 +3103,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -3115,111 +3115,111 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM23" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO23" t="n">
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B24" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D24" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E24" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F24" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H24" t="n">
         <v>25.4</v>
       </c>
       <c r="I24" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J24" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K24" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AB24" t="n">
         <v>4.8</v>
       </c>
-      <c r="N24" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V24" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AC24" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -3228,10 +3228,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -3240,111 +3240,111 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM24" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN24" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO24" t="n">
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B25" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C25" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D25" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F25" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H25" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I25" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J25" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O25" t="n">
         <v>38.4</v>
       </c>
-      <c r="K25" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q25" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="V25" t="n">
-        <v>14.7</v>
+        <v>12.9</v>
       </c>
       <c r="W25" t="n">
-        <v>27.2</v>
+        <v>19.4</v>
       </c>
       <c r="X25" t="n">
-        <v>20.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>6.9</v>
+        <v>3.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG25" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3353,10 +3353,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3365,111 +3365,84 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM25" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN25" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO25" t="n">
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B26" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C26" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D26" t="n">
         <v>34.5</v>
       </c>
       <c r="E26" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F26" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H26" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K26" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N26" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O26" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="V26" t="n">
-        <v>12.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>19.4</v>
+        <v>17.7</v>
       </c>
       <c r="X26" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3478,10 +3451,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3489,17 +3462,11 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
-      <c r="AP26" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL26" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM26" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
@@ -3508,66 +3475,66 @@
         <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B27" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C27" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D27" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E27" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
         <v>9.6</v>
       </c>
       <c r="K27" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="V27" t="n">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X27" t="n">
-        <v>13.7</v>
+        <v>10.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
         <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG27" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3576,10 +3543,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3588,78 +3555,105 @@
         <v>142</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM27" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP27" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B28" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C28" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D28" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F28" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>38.7</v>
       </c>
       <c r="K28" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33</v>
       </c>
       <c r="O28" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>23.3</v>
       </c>
       <c r="V28" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>13.9</v>
+        <v>16.9</v>
       </c>
       <c r="X28" t="n">
         <v>10.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>-1.6</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>11.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG28" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3671,7 +3665,7 @@
         <v>128.27</v>
       </c>
       <c r="AL28" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3679,106 +3673,112 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM28" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP28" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B29" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C29" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D29" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F29" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H29" t="n">
         <v>25.1</v>
       </c>
       <c r="I29" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J29" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K29" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O29" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
-        <v>16.9</v>
+        <v>19.3</v>
       </c>
       <c r="X29" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA29" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3787,10 +3787,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3799,72 +3799,72 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM29" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP29" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B30" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C30" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D30" t="n">
         <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F30" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H30" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I30" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O30" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q30" t="n">
         <v>23.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3873,37 +3873,37 @@
         <v>23.1</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="W30" t="n">
-        <v>19.3</v>
+        <v>22.9</v>
       </c>
       <c r="X30" t="n">
-        <v>12.4</v>
+        <v>15.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.2</v>
+        <v>13.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3912,10 +3912,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL30" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3924,69 +3924,69 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM30" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO30" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP30" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B31" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C31" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D31" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E31" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F31" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J31" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K31" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N31" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O31" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R31" t="n">
         <v>1.3</v>
@@ -3995,40 +3995,40 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="V31" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="W31" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="X31" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="Y31" t="n">
         <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AD31" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -4037,10 +4037,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL31" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -4049,111 +4049,111 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM31" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN31" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B32" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C32" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D32" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E32" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I32" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O32" t="n">
         <v>39.5</v>
       </c>
-      <c r="K32" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q32" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="V32" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="W32" t="n">
-        <v>23</v>
+        <v>20.8</v>
       </c>
       <c r="X32" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -4162,10 +4162,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -4174,111 +4174,84 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS32" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM32" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO32" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP32" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B33" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C33" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D33" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E33" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y33" t="n">
         <v>8</v>
       </c>
-      <c r="H33" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K33" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N33" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X33" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>10</v>
-      </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>11.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -4287,10 +4260,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -4298,85 +4271,79 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM33" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN33" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP33" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B34" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C34" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D34" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E34" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K34" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O34" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="V34" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="W34" t="n">
-        <v>21.3</v>
+        <v>17.9</v>
       </c>
       <c r="X34" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA34" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>-1.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AF34" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -4385,10 +4352,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL34" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -4397,78 +4364,105 @@
         <v>142</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM34" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN34" t="n">
         <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP34" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B35" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C35" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F35" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>40</v>
       </c>
       <c r="K35" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>36.7</v>
       </c>
       <c r="O35" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>23.1</v>
       </c>
       <c r="V35" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W35" t="n">
-        <v>17.9</v>
+        <v>13.1</v>
       </c>
       <c r="X35" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-1.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AF35" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -4480,7 +4474,7 @@
         <v>125.11</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -4488,106 +4482,112 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
+      <c r="AP35" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>14</v>
+      </c>
       <c r="BL35" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM35" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B36" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C36" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E36" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F36" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H36" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O36" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T36" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V36" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="W36" t="n">
-        <v>13.1</v>
+        <v>16.2</v>
       </c>
       <c r="X36" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.1</v>
+        <v>4</v>
       </c>
       <c r="AC36" t="n">
-        <v>11.4</v>
+        <v>14.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4596,10 +4596,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4608,111 +4608,111 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS36" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM36" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN36" t="n">
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP36" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B37" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C37" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E37" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F37" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H37" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K37" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O37" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T37" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="V37" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="W37" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="X37" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG37" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4721,10 +4721,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4733,111 +4733,111 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS37" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM37" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN37" t="n">
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP37" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B38" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C38" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D38" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E38" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F38" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H38" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q38" t="n">
         <v>23.7</v>
       </c>
-      <c r="I38" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J38" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K38" t="n">
-        <v>73</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N38" t="n">
-        <v>34</v>
-      </c>
-      <c r="O38" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S38" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T38" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="V38" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="W38" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="X38" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG38" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4846,10 +4846,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL38" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4858,111 +4858,111 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM38" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO38" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP38" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B39" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C39" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E39" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F39" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H39" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I39" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>40.8</v>
       </c>
       <c r="K39" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O39" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T39" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V39" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="W39" t="n">
-        <v>18.3</v>
+        <v>15.5</v>
       </c>
       <c r="X39" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4971,10 +4971,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL39" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4983,111 +4983,84 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS39" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM39" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN39" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO39" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP39" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B40" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C40" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E40" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K40" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M40" t="n">
-        <v>4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O40" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2</v>
-      </c>
-      <c r="S40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="V40" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W40" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="X40" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z40" t="n">
         <v>13</v>
       </c>
       <c r="AA40" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC40" t="n">
-        <v>13.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -5096,10 +5069,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL40" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -5107,85 +5080,79 @@
       <c r="AN40" t="n">
         <v>142</v>
       </c>
-      <c r="AP40" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL40" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM40" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN40" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO40" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP40" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B41" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C41" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D41" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E41" t="n">
         <v>29.8</v>
       </c>
       <c r="F41" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K41" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O41" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V41" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W41" t="n">
-        <v>15.9</v>
+        <v>16.5</v>
       </c>
       <c r="X41" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AF41" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -5194,10 +5161,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -5206,33 +5173,33 @@
         <v>142</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM41" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN41" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B42" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C42" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D42" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E42" t="n">
         <v>29.8</v>
@@ -5241,25 +5208,25 @@
         <v>6.6</v>
       </c>
       <c r="K42" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="V42" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W42" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="X42" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
         <v>12.5</v>
@@ -5268,16 +5235,16 @@
         <v>1.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -5286,10 +5253,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL42" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -5298,78 +5265,105 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM42" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN42" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO42" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP42" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B43" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C43" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D43" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E43" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F43" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>41.1</v>
       </c>
       <c r="K43" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>37.4</v>
       </c>
       <c r="O43" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>24.4</v>
       </c>
       <c r="V43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W43" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="X43" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AF43" t="n">
         <v>220</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -5381,7 +5375,7 @@
         <v>126.54</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -5389,106 +5383,112 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM43" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN43" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO43" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP43" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B44" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C44" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D44" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E44" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F44" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H44" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I44" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K44" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N44" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O44" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="V44" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W44" t="n">
-        <v>19.4</v>
+        <v>21.2</v>
       </c>
       <c r="X44" t="n">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AC44" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -5497,10 +5497,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -5509,111 +5509,111 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS44" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM44" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN44" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO44" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP44" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B45" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C45" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E45" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F45" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I45" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K45" t="n">
         <v>76.5</v>
       </c>
       <c r="M45" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N45" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O45" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R45" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="V45" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="W45" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="X45" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z45" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA45" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AC45" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5622,10 +5622,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5634,72 +5634,72 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS45" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM45" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN45" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO45" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP45" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B46" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C46" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D46" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E46" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F46" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H46" t="n">
         <v>26.1</v>
       </c>
       <c r="I46" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J46" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K46" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N46" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O46" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q46" t="n">
         <v>24.2</v>
       </c>
       <c r="R46" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -5708,37 +5708,37 @@
         <v>24.2</v>
       </c>
       <c r="V46" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W46" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="X46" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z46" t="n">
         <v>16</v>
       </c>
       <c r="AA46" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AB46" t="n">
         <v>3.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="AD46" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AF46" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5747,10 +5747,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL46" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5759,111 +5759,84 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS46" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM46" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN46" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO46" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP46" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B47" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C47" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D47" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E47" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H47" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I47" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K47" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M47" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="V47" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="W47" t="n">
-        <v>21.1</v>
+        <v>20.4</v>
       </c>
       <c r="X47" t="n">
-        <v>15.4</v>
+        <v>16</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z47" t="n">
         <v>16</v>
       </c>
       <c r="AA47" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="AD47" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AF47" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5872,10 +5845,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL47" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5883,85 +5856,79 @@
       <c r="AN47" t="n">
         <v>142</v>
       </c>
-      <c r="AP47" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL47" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM47" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN47" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO47" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP47" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B48" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C48" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D48" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E48" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F48" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K48" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="V48" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="W48" t="n">
-        <v>20.4</v>
+        <v>19.6</v>
       </c>
       <c r="X48" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="Y48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z48" t="n">
         <v>16</v>
       </c>
       <c r="AA48" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB48" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="AF48" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5970,10 +5937,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5982,78 +5949,105 @@
         <v>142</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM48" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN48" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO48" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP48" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B49" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C49" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D49" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E49" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F49" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>41.3</v>
       </c>
       <c r="K49" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>37.1</v>
       </c>
       <c r="O49" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
+        <v>23.9</v>
       </c>
       <c r="V49" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="W49" t="n">
-        <v>19.6</v>
+        <v>22.1</v>
       </c>
       <c r="X49" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB49" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>12.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD49" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -6065,7 +6059,7 @@
         <v>125.03</v>
       </c>
       <c r="AL49" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -6073,106 +6067,112 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
+      <c r="AP49" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL49" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM49" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN49" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP49" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B50" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C50" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E50" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F50" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K50" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M50" t="n">
         <v>2.7</v>
       </c>
       <c r="N50" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O50" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R50" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T50" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="V50" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="W50" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="X50" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.699999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>6.2</v>
+        <v>9.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -6181,10 +6181,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -6193,87 +6193,87 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM50" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN50" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO50" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP50" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B51" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C51" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D51" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E51" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F51" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I51" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K51" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O51" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>16</v>
       </c>
       <c r="T51" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V51" t="n">
-        <v>11.9</v>
+        <v>14.9</v>
       </c>
       <c r="W51" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="X51" t="n">
-        <v>16.5</v>
+        <v>17.9</v>
       </c>
       <c r="Y51" t="n">
         <v>10</v>
@@ -6282,22 +6282,22 @@
         <v>15</v>
       </c>
       <c r="AA51" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -6306,10 +6306,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL51" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -6318,111 +6318,111 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM51" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN51" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO51" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP51" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B52" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C52" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D52" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E52" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F52" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H52" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K52" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N52" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O52" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T52" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V52" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
       </c>
       <c r="W52" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X52" t="n">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AB52" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="AD52" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AF52" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -6431,10 +6431,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL52" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -6443,87 +6443,87 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM52" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN52" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO52" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP52" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B53" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C53" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D53" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E53" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F53" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H53" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I53" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J53" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K53" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M53" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O53" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S53" t="n">
         <v>12</v>
       </c>
       <c r="T53" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V53" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="W53" t="n">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
       <c r="X53" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="Y53" t="n">
         <v>13</v>
@@ -6532,22 +6532,22 @@
         <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -6556,10 +6556,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL53" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -6568,111 +6568,84 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS53" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM53" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN53" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO53" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP53" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B54" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C54" t="n">
         <v>57.9</v>
       </c>
       <c r="D54" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E54" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H54" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J54" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M54" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N54" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S54" t="n">
-        <v>12</v>
-      </c>
-      <c r="T54" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="V54" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W54" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="X54" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z54" t="n">
         <v>18</v>
       </c>
       <c r="AA54" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6681,10 +6654,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL54" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -6692,85 +6665,79 @@
       <c r="AN54" t="n">
         <v>142</v>
       </c>
-      <c r="AP54" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL54" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM54" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN54" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO54" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP54" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B55" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C55" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D55" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E55" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K55" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O55" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="V55" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W55" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="X55" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z55" t="n">
         <v>18</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6779,10 +6746,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -6791,60 +6758,87 @@
         <v>142</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM55" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN55" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO55" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP55" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B56" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C56" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D56" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E56" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F56" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J56" t="n">
+        <v>40.6</v>
       </c>
       <c r="K56" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N56" t="n">
+        <v>36</v>
       </c>
       <c r="O56" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>11</v>
+      </c>
+      <c r="T56" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA56" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF56" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6856,7 +6850,7 @@
         <v>128.43</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -6864,88 +6858,94 @@
       <c r="AN56" t="n">
         <v>142</v>
       </c>
+      <c r="AP56" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL56" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM56" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN56" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO56" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP56" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B57" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C57" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D57" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E57" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F57" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H57" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I57" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K57" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N57" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O57" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T57" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6954,10 +6954,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6966,93 +6966,93 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS57" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM57" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN57" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO57" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP57" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B58" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C58" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D58" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E58" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F58" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H58" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I58" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K58" t="n">
         <v>75.7</v>
       </c>
       <c r="M58" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O58" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R58" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T58" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA58" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF58" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -7061,10 +7061,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL58" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -7073,93 +7073,93 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS58" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM58" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN58" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO58" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP58" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B59" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C59" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D59" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E59" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F59" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H59" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K59" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N59" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O59" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R59" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S59" t="n">
         <v>17</v>
       </c>
       <c r="T59" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z59" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA59" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF59" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -7168,10 +7168,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL59" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -7180,93 +7180,93 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS59" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM59" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN59" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO59" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP59" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B60" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C60" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D60" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E60" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H60" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I60" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J60" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K60" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M60" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N60" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O60" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R60" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S60" t="n">
         <v>17</v>
       </c>
       <c r="T60" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z60" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA60" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF60" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG60" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -7275,10 +7275,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL60" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -7287,60 +7287,54 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM60" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN60" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO60" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP60" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B61" t="n">
-        <v>150.7</v>
+        <v>147.9</v>
       </c>
       <c r="C61" t="n">
-        <v>66.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="D61" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E61" t="n">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
       <c r="F61" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="Y61" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z61" t="n">
         <v>17</v>
       </c>
       <c r="AA61" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>222.99</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>4.08</v>
+        <v>12</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -7349,10 +7343,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>127.44</v>
+        <v>128.28</v>
       </c>
       <c r="AL61" t="n">
-        <v>-0.09</v>
+        <v>0.21</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -7361,48 +7355,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>705.1</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>1122.7</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>2933.3</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B62" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C62" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E62" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F62" t="n">
         <v>5</v>
       </c>
       <c r="Y62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z62" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA62" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -7417,7 +7399,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,40 +628,40 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B2" t="n">
-        <v>116.54</v>
+        <v>117.05</v>
       </c>
       <c r="C2" t="n">
-        <v>23.39</v>
+        <v>23.91</v>
       </c>
       <c r="D2" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
       <c r="E2" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="F2" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="H2" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="I2" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J2" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="K2" t="n">
         <v>62.9</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N2" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="O2" t="n">
         <v>31.8</v>
@@ -679,37 +679,28 @@
         <v>17</v>
       </c>
       <c r="V2" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="W2" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="X2" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
         <v>21</v>
       </c>
-      <c r="AB2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>7.1</v>
-      </c>
       <c r="AF2" t="n">
-        <v>230.5</v>
+        <v>225.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4.67</v>
+        <v>-5.78</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,7 +709,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>136.01</v>
+        <v>132.41</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -733,13 +724,13 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="BM2" t="n">
-        <v>37.84</v>
+        <v>41.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>285.1</v>
+        <v>334.1</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -750,40 +741,40 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B3" t="n">
-        <v>117.05</v>
+        <v>117.63</v>
       </c>
       <c r="C3" t="n">
-        <v>23.91</v>
+        <v>24.3</v>
       </c>
       <c r="D3" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="E3" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="F3" t="n">
-        <v>10.56</v>
+        <v>10.75</v>
       </c>
       <c r="H3" t="n">
         <v>22.3</v>
       </c>
       <c r="I3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K3" t="n">
         <v>62.9</v>
       </c>
       <c r="M3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N3" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="O3" t="n">
         <v>31.8</v>
@@ -804,34 +795,25 @@
         <v>19.1</v>
       </c>
       <c r="W3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="X3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA3" t="n">
         <v>22</v>
       </c>
-      <c r="AA3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AF3" t="n">
-        <v>225.8</v>
+        <v>220</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5.78</v>
+        <v>-2.67</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -840,10 +822,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>132.41</v>
+        <v>131.69</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.6</v>
+        <v>-0.72</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -858,13 +840,13 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BM3" t="n">
-        <v>41.59</v>
+        <v>42.83</v>
       </c>
       <c r="BN3" t="n">
-        <v>334.1</v>
+        <v>106.5</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -875,41 +857,26 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B4" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C4" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D4" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E4" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F4" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K4" t="n">
         <v>62.9</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O4" t="n">
         <v>31.8</v>
       </c>
@@ -926,37 +893,28 @@
         <v>17</v>
       </c>
       <c r="V4" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="W4" t="n">
-        <v>24.8</v>
+        <v>26.7</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.9</v>
+        <v>20.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -964,12 +922,6 @@
       <c r="AI4" t="n">
         <v>235</v>
       </c>
-      <c r="AK4" t="n">
-        <v>131.69</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="AM4" t="n">
         <v>110</v>
       </c>
@@ -983,13 +935,13 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM4" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -1000,19 +952,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C5" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D5" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E5" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F5" t="n">
         <v>10.92</v>
@@ -1036,37 +988,28 @@
         <v>17</v>
       </c>
       <c r="V5" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="W5" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="X5" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1087,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM5" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
@@ -1104,26 +1047,41 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B6" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C6" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D6" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E6" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F6" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.1</v>
       </c>
       <c r="K6" t="n">
         <v>62.9</v>
       </c>
+      <c r="M6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O6" t="n">
         <v>31.8</v>
       </c>
@@ -1140,37 +1098,28 @@
         <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>18.6</v>
+        <v>19.9</v>
       </c>
       <c r="W6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="X6" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1178,6 +1127,12 @@
       <c r="AI6" t="n">
         <v>235</v>
       </c>
+      <c r="AK6" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.46</v>
+      </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
@@ -1191,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM6" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -1208,46 +1163,46 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B7" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C7" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D7" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E7" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I7" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.9</v>
       </c>
       <c r="N7" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1256,40 +1211,31 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>19.9</v>
+        <v>17.5</v>
       </c>
       <c r="W7" t="n">
-        <v>28</v>
+        <v>20.8</v>
       </c>
       <c r="X7" t="n">
-        <v>23.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA7" t="n">
         <v>16</v>
       </c>
-      <c r="Z7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF7" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1298,10 +1244,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1316,13 +1262,13 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM7" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1333,43 +1279,43 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B8" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C8" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D8" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E8" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M8" t="n">
         <v>1.9</v>
       </c>
       <c r="N8" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O8" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1384,37 +1330,28 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>17.5</v>
+        <v>16.1</v>
       </c>
       <c r="W8" t="n">
-        <v>20.8</v>
+        <v>18</v>
       </c>
       <c r="X8" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG8" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1423,10 +1360,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1441,13 +1378,13 @@
         <v>0</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM8" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN8" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -1458,88 +1395,79 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B9" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C9" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E9" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K9" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N9" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O9" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V9" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="W9" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="X9" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6.2</v>
+        <v>16.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1548,10 +1476,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1560,19 +1488,19 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM9" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
@@ -1583,46 +1511,46 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B10" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C10" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D10" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E10" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F10" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K10" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N10" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O10" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R10" t="n">
         <v>0.6</v>
@@ -1631,40 +1559,31 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="V10" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W10" t="n">
-        <v>20.5</v>
+        <v>19.6</v>
       </c>
       <c r="X10" t="n">
-        <v>18.2</v>
+        <v>17.6</v>
       </c>
       <c r="Y10" t="n">
         <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>6.6</v>
+        <v>17.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1673,10 +1592,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1685,19 +1604,19 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS10" t="n">
         <v>13.07</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM10" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN10" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
@@ -1708,88 +1627,52 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B11" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C11" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E11" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O11" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="V11" t="n">
-        <v>15.7</v>
+        <v>14.4</v>
       </c>
       <c r="W11" t="n">
-        <v>19.6</v>
+        <v>22.4</v>
       </c>
       <c r="X11" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="Y11" t="n">
         <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>10.3</v>
+        <v>18</v>
       </c>
       <c r="AF11" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1797,35 +1680,23 @@
       <c r="AI11" t="n">
         <v>235</v>
       </c>
-      <c r="AK11" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM11" t="n">
         <v>110</v>
       </c>
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM11" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP11" t="n">
         <v>0</v>
@@ -1833,61 +1704,52 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B12" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C12" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D12" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E12" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="V12" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W12" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="X12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>6.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1902,78 +1764,96 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM12" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B13" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C13" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D13" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>35.6</v>
       </c>
       <c r="K13" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>34</v>
       </c>
       <c r="O13" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>16.2</v>
       </c>
       <c r="V13" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="W13" t="n">
-        <v>22.5</v>
+        <v>24.6</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1981,17 +1861,29 @@
       <c r="AI13" t="n">
         <v>235</v>
       </c>
+      <c r="AK13" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM13" t="n">
         <v>110</v>
       </c>
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM13" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -2000,93 +1892,84 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B14" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C14" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E14" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F14" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I14" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K14" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O14" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>11.2</v>
       </c>
       <c r="W14" t="n">
-        <v>24.6</v>
+        <v>17.8</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.1</v>
+        <v>11.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -2095,10 +1978,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -2107,16 +1990,16 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM14" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -2125,30 +2008,30 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B15" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D15" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E15" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H15" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I15" t="n">
         <v>9.800000000000001</v>
@@ -2157,61 +2040,52 @@
         <v>38.6</v>
       </c>
       <c r="K15" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O15" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="V15" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>17.8</v>
+        <v>16.9</v>
       </c>
       <c r="X15" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>6.1</v>
+        <v>15.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2220,10 +2094,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2232,111 +2106,102 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS15" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM15" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B16" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C16" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D16" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N16" t="n">
         <v>35.2</v>
       </c>
-      <c r="E16" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O16" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="W16" t="n">
-        <v>16.9</v>
+        <v>20.6</v>
       </c>
       <c r="X16" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>8.300000000000001</v>
+        <v>16</v>
       </c>
       <c r="AF16" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2345,10 +2210,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL16" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2357,111 +2222,69 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS16" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM16" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO16" t="n">
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B17" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C17" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D17" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E17" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10</v>
-      </c>
-      <c r="J17" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="W17" t="n">
-        <v>20.6</v>
+        <v>23</v>
       </c>
       <c r="X17" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
         <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>7.3</v>
+        <v>15.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2470,10 +2293,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2481,79 +2304,64 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM17" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO17" t="n">
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B18" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C18" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D18" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="V18" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="W18" t="n">
-        <v>23</v>
+        <v>24.9</v>
       </c>
       <c r="X18" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AF18" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2562,10 +2370,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2574,10 +2382,10 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM18" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -2586,60 +2394,51 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B19" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C19" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D19" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E19" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F19" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="V19" t="n">
-        <v>11.2</v>
+        <v>15.9</v>
       </c>
       <c r="W19" t="n">
-        <v>24.9</v>
+        <v>18.1</v>
       </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>15.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG19" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2648,10 +2447,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL19" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2660,10 +2459,10 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM19" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -2672,60 +2471,84 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B20" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C20" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D20" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E20" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F20" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>22.3</v>
       </c>
       <c r="V20" t="n">
-        <v>15.9</v>
+        <v>11.8</v>
       </c>
       <c r="W20" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.2</v>
+        <v>11.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2737,7 +2560,7 @@
         <v>138.94</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2745,11 +2568,17 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
+      <c r="AP20" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL20" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM20" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -2758,51 +2587,51 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B21" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C21" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D21" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I21" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M21" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O21" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R21" t="n">
         <v>3.5</v>
@@ -2811,40 +2640,31 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W21" t="n">
         <v>22.3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>21</v>
       </c>
       <c r="X21" t="n">
         <v>16.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>6.8</v>
+        <v>16.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2853,10 +2673,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2865,16 +2685,16 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS21" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM21" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
@@ -2883,93 +2703,84 @@
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B22" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C22" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E22" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H22" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J22" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K22" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O22" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R22" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="V22" t="n">
-        <v>10.4</v>
+        <v>13.6</v>
       </c>
       <c r="W22" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="X22" t="n">
-        <v>16.4</v>
+        <v>19.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>7</v>
+        <v>20.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG22" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2978,10 +2789,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2990,111 +2801,102 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM22" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO22" t="n">
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B23" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D23" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E23" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F23" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H23" t="n">
         <v>25.4</v>
       </c>
       <c r="I23" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J23" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K23" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N23" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O23" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="V23" t="n">
-        <v>13.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="X23" t="n">
-        <v>19.7</v>
+        <v>20.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>7.5</v>
+        <v>22.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -3103,10 +2905,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -3115,111 +2917,102 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM23" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN23" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO23" t="n">
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B24" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C24" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D24" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E24" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F24" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H24" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I24" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J24" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O24" t="n">
         <v>38.4</v>
       </c>
-      <c r="K24" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q24" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="V24" t="n">
-        <v>14.7</v>
+        <v>12.9</v>
       </c>
       <c r="W24" t="n">
-        <v>27.2</v>
+        <v>19.4</v>
       </c>
       <c r="X24" t="n">
-        <v>20.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.9</v>
+        <v>13.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG24" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -3228,10 +3021,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -3240,111 +3033,75 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM24" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN24" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO24" t="n">
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B25" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C25" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D25" t="n">
         <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F25" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H25" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K25" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N25" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O25" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="V25" t="n">
-        <v>12.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>19.4</v>
+        <v>17.7</v>
       </c>
       <c r="X25" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3353,10 +3110,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3364,17 +3121,11 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM25" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
@@ -3383,66 +3134,57 @@
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B26" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C26" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D26" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E26" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
         <v>9.6</v>
       </c>
       <c r="K26" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="V26" t="n">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X26" t="n">
-        <v>13.7</v>
+        <v>10.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26" t="n">
         <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG26" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3451,10 +3193,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3463,78 +3205,96 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM26" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP26" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B27" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C27" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D27" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>38.7</v>
       </c>
       <c r="K27" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>33</v>
       </c>
       <c r="O27" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>23.3</v>
       </c>
       <c r="V27" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="W27" t="n">
-        <v>13.9</v>
+        <v>16.9</v>
       </c>
       <c r="X27" t="n">
         <v>10.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
+        <v>10.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG27" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3546,7 +3306,7 @@
         <v>128.27</v>
       </c>
       <c r="AL27" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3554,106 +3314,103 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
+      <c r="AP27" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL27" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM27" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP27" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B28" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C28" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D28" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F28" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="n">
         <v>25.1</v>
       </c>
       <c r="I28" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J28" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K28" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O28" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>16.9</v>
+        <v>19.3</v>
       </c>
       <c r="X28" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>6.8</v>
+        <v>12.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3662,10 +3419,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3674,72 +3431,72 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS28" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM28" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP28" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B29" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C29" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D29" t="n">
         <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F29" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H29" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K29" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N29" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O29" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q29" t="n">
         <v>23.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -3748,37 +3505,28 @@
         <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="W29" t="n">
-        <v>19.3</v>
+        <v>22.9</v>
       </c>
       <c r="X29" t="n">
-        <v>12.4</v>
+        <v>15.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>7.7</v>
+        <v>15.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3787,10 +3535,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL29" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3799,69 +3547,69 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM29" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP29" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B30" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C30" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F30" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I30" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J30" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K30" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N30" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O30" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R30" t="n">
         <v>1.3</v>
@@ -3870,40 +3618,31 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="V30" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="W30" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="X30" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="Y30" t="n">
         <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3912,10 +3651,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL30" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3924,111 +3663,102 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM30" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN30" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP30" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B31" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C31" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D31" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E31" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I31" t="n">
         <v>9.4</v>
       </c>
       <c r="J31" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O31" t="n">
         <v>39.5</v>
       </c>
-      <c r="K31" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q31" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="V31" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="W31" t="n">
-        <v>23</v>
+        <v>20.8</v>
       </c>
       <c r="X31" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>5.9</v>
+        <v>12.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -4037,10 +3767,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -4049,111 +3779,75 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM31" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO31" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP31" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B32" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C32" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D32" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E32" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y32" t="n">
         <v>8</v>
       </c>
-      <c r="H32" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J32" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K32" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N32" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O32" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X32" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -4162,10 +3856,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -4173,85 +3867,70 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM32" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN32" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP32" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B33" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C33" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D33" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E33" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F33" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K33" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O33" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="V33" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="W33" t="n">
-        <v>21.3</v>
+        <v>17.9</v>
       </c>
       <c r="X33" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -4260,10 +3939,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL33" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -4272,78 +3951,96 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM33" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN33" t="n">
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP33" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B34" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C34" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F34" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>36.7</v>
       </c>
       <c r="O34" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23.1</v>
       </c>
       <c r="V34" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>17.9</v>
+        <v>13.1</v>
       </c>
       <c r="X34" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z34" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4</v>
+        <v>11.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -4355,7 +4052,7 @@
         <v>125.11</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -4363,106 +4060,103 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>14</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM34" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN34" t="n">
         <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP34" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B35" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C35" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E35" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F35" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H35" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I35" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K35" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O35" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T35" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V35" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="W35" t="n">
-        <v>13.1</v>
+        <v>16.2</v>
       </c>
       <c r="X35" t="n">
         <v>10.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>5.7</v>
+        <v>10.7</v>
       </c>
       <c r="AF35" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -4471,10 +4165,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -4483,111 +4177,102 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS35" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM35" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B36" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C36" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E36" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F36" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H36" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K36" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O36" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T36" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="V36" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="W36" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="X36" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>9.1</v>
+        <v>12.3</v>
       </c>
       <c r="AF36" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG36" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4596,10 +4281,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL36" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4608,111 +4293,102 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS36" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM36" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN36" t="n">
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP36" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B37" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C37" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D37" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E37" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F37" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H37" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q37" t="n">
         <v>23.7</v>
       </c>
-      <c r="I37" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J37" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K37" t="n">
-        <v>73</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>34</v>
-      </c>
-      <c r="O37" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S37" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T37" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="V37" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="X37" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG37" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4721,10 +4397,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL37" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4733,111 +4409,102 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM37" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO37" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP37" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B38" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C38" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E38" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F38" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H38" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I38" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>40.8</v>
       </c>
       <c r="K38" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O38" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T38" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V38" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="W38" t="n">
-        <v>18.3</v>
+        <v>15.5</v>
       </c>
       <c r="X38" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="AD38" t="n">
         <v>8.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4846,10 +4513,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4858,111 +4525,75 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS38" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM38" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN38" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO38" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP38" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B39" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C39" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E39" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K39" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O39" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2</v>
-      </c>
-      <c r="S39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="V39" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="X39" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z39" t="n">
         <v>13</v>
       </c>
       <c r="AA39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AF39" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4971,10 +4602,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL39" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4982,85 +4613,70 @@
       <c r="AN39" t="n">
         <v>142</v>
       </c>
-      <c r="AP39" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL39" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM39" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN39" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO39" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP39" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B40" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C40" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D40" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E40" t="n">
         <v>29.8</v>
       </c>
       <c r="F40" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K40" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O40" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V40" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>15.9</v>
+        <v>16.5</v>
       </c>
       <c r="X40" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -5069,10 +4685,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -5081,33 +4697,33 @@
         <v>142</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM40" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN40" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO40" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP40" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B41" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C41" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D41" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E41" t="n">
         <v>29.8</v>
@@ -5116,43 +4732,34 @@
         <v>6.6</v>
       </c>
       <c r="K41" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="V41" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W41" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="X41" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>6</v>
-      </c>
       <c r="AF41" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -5161,10 +4768,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -5173,78 +4780,96 @@
         <v>142</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM41" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN41" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO41" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP41" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B42" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C42" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D42" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E42" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F42" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>41.1</v>
       </c>
       <c r="K42" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>37.4</v>
       </c>
       <c r="O42" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>24.4</v>
       </c>
       <c r="V42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W42" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="X42" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y42" t="n">
         <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.6</v>
+        <v>12.7</v>
       </c>
       <c r="AF42" t="n">
         <v>220</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -5256,7 +4881,7 @@
         <v>126.54</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -5264,106 +4889,103 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM42" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN42" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP42" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B43" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C43" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D43" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E43" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F43" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H43" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I43" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K43" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N43" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O43" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="V43" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W43" t="n">
-        <v>19.4</v>
+        <v>21.2</v>
       </c>
       <c r="X43" t="n">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>8.6</v>
+        <v>12.1</v>
       </c>
       <c r="AF43" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -5372,10 +4994,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -5384,111 +5006,102 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS43" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM43" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN43" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO43" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP43" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B44" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C44" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E44" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F44" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I44" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K44" t="n">
         <v>76.5</v>
       </c>
       <c r="M44" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N44" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O44" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R44" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="V44" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="W44" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="X44" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA44" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>7.3</v>
+        <v>13.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -5497,10 +5110,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -5509,72 +5122,72 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS44" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM44" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN44" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO44" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP44" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B45" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C45" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D45" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E45" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H45" t="n">
         <v>26.1</v>
       </c>
       <c r="I45" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J45" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K45" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N45" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O45" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q45" t="n">
         <v>24.2</v>
       </c>
       <c r="R45" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -5583,37 +5196,28 @@
         <v>24.2</v>
       </c>
       <c r="V45" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="X45" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z45" t="n">
         <v>16</v>
       </c>
       <c r="AA45" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>7.8</v>
+        <v>13.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5622,10 +5226,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL45" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5634,111 +5238,75 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM45" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN45" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO45" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP45" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B46" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C46" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D46" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E46" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F46" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H46" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K46" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M46" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="V46" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="W46" t="n">
-        <v>21.1</v>
+        <v>20.4</v>
       </c>
       <c r="X46" t="n">
-        <v>15.4</v>
+        <v>16</v>
       </c>
       <c r="Y46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
         <v>16</v>
       </c>
       <c r="AA46" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AF46" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5747,10 +5315,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL46" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5758,85 +5326,70 @@
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM46" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN46" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO46" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP46" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B47" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C47" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D47" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E47" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F47" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K47" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="V47" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="W47" t="n">
-        <v>20.4</v>
+        <v>19.6</v>
       </c>
       <c r="X47" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
         <v>16</v>
       </c>
       <c r="AA47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AF47" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5845,10 +5398,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5857,78 +5410,96 @@
         <v>142</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM47" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN47" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO47" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP47" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B48" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C48" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D48" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E48" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F48" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>41.3</v>
       </c>
       <c r="K48" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N48" t="n">
+        <v>37.1</v>
       </c>
       <c r="O48" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>23.9</v>
       </c>
       <c r="V48" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="W48" t="n">
-        <v>19.6</v>
+        <v>22.1</v>
       </c>
       <c r="X48" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>7.9</v>
+        <v>12</v>
       </c>
       <c r="AF48" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5940,7 +5511,7 @@
         <v>125.03</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5948,106 +5519,103 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM48" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN48" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO48" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP48" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B49" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C49" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E49" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F49" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K49" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M49" t="n">
         <v>2.7</v>
       </c>
       <c r="N49" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O49" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R49" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T49" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="V49" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="W49" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="X49" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA49" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>6.2</v>
+        <v>11.9</v>
       </c>
       <c r="AF49" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -6056,10 +5624,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -6068,87 +5636,87 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS49" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM49" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN49" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO49" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP49" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B50" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C50" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D50" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E50" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F50" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I50" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K50" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O50" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R50" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>16</v>
       </c>
       <c r="T50" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V50" t="n">
-        <v>11.9</v>
+        <v>14.9</v>
       </c>
       <c r="W50" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="X50" t="n">
-        <v>16.5</v>
+        <v>17.9</v>
       </c>
       <c r="Y50" t="n">
         <v>10</v>
@@ -6157,22 +5725,13 @@
         <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>9.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF50" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -6181,10 +5740,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL50" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -6193,111 +5752,102 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM50" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN50" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO50" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP50" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B51" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C51" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D51" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E51" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F51" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H51" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I51" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K51" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N51" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O51" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S51" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V51" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
       </c>
       <c r="W51" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X51" t="n">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z51" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AF51" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -6306,10 +5856,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL51" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -6318,87 +5868,87 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM51" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN51" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO51" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP51" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B52" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C52" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D52" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E52" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F52" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H52" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I52" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J52" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K52" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M52" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N52" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O52" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S52" t="n">
         <v>12</v>
       </c>
       <c r="T52" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V52" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="W52" t="n">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
       <c r="X52" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="Y52" t="n">
         <v>13</v>
@@ -6407,22 +5957,13 @@
         <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>7.2</v>
+        <v>15.3</v>
       </c>
       <c r="AF52" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -6431,10 +5972,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL52" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -6443,111 +5984,75 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS52" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM52" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN52" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO52" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP52" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B53" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C53" t="n">
         <v>57.9</v>
       </c>
       <c r="D53" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E53" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F53" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H53" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I53" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J53" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N53" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S53" t="n">
-        <v>12</v>
-      </c>
-      <c r="T53" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="V53" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W53" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="X53" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z53" t="n">
         <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="AF53" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -6556,10 +6061,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL53" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -6567,85 +6072,70 @@
       <c r="AN53" t="n">
         <v>142</v>
       </c>
-      <c r="AP53" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL53" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM53" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN53" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO53" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP53" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B54" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C54" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D54" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E54" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F54" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K54" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O54" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="V54" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W54" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="X54" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z54" t="n">
         <v>18</v>
       </c>
       <c r="AA54" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AF54" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6654,10 +6144,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -6666,78 +6156,96 @@
         <v>142</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM54" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN54" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO54" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP54" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B55" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C55" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D55" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E55" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F55" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J55" t="n">
+        <v>40.6</v>
       </c>
       <c r="K55" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N55" t="n">
+        <v>36</v>
       </c>
       <c r="O55" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>11</v>
+      </c>
+      <c r="T55" t="n">
+        <v>19.4</v>
       </c>
       <c r="V55" t="n">
-        <v>17</v>
+        <v>15.8</v>
       </c>
       <c r="W55" t="n">
-        <v>22.6</v>
+        <v>17.4</v>
       </c>
       <c r="X55" t="n">
-        <v>19.8</v>
+        <v>16.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z55" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA55" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>5.7</v>
+        <v>15.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6749,7 +6257,7 @@
         <v>128.43</v>
       </c>
       <c r="AL55" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -6757,88 +6265,94 @@
       <c r="AN55" t="n">
         <v>142</v>
       </c>
+      <c r="AP55" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL55" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM55" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN55" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO55" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP55" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B56" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C56" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D56" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E56" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F56" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H56" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I56" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K56" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N56" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O56" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T56" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6847,10 +6361,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -6859,93 +6373,93 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM56" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN56" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO56" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP56" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B57" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C57" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D57" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E57" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F57" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H57" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I57" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K57" t="n">
         <v>75.7</v>
       </c>
       <c r="M57" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O57" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R57" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T57" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA57" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF57" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6954,10 +6468,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6966,93 +6480,93 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS57" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM57" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN57" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO57" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP57" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B58" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C58" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D58" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E58" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F58" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K58" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M58" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O58" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R58" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S58" t="n">
         <v>17</v>
       </c>
       <c r="T58" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA58" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF58" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -7061,10 +6575,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL58" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -7073,93 +6587,93 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS58" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM58" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN58" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO58" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP58" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B59" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C59" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D59" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E59" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H59" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I59" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J59" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K59" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M59" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N59" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O59" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R59" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S59" t="n">
         <v>17</v>
       </c>
       <c r="T59" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z59" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG59" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -7168,10 +6682,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL59" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -7180,93 +6694,54 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS59" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM59" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN59" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO59" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP59" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B60" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C60" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D60" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E60" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F60" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H60" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J60" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="K60" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M60" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N60" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O60" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S60" t="n">
-        <v>17</v>
-      </c>
-      <c r="T60" t="n">
-        <v>22.9</v>
+        <v>5</v>
       </c>
       <c r="Y60" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z60" t="n">
         <v>17</v>
       </c>
       <c r="AA60" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>218.89</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>4.08</v>
+        <v>12</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -7275,10 +6750,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -7286,55 +6761,37 @@
       <c r="AN60" t="n">
         <v>142</v>
       </c>
-      <c r="AP60" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="BM60" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="BN60" t="n">
-        <v>705.1</v>
-      </c>
-      <c r="BO60" t="n">
-        <v>1122.7</v>
-      </c>
-      <c r="BP60" t="n">
-        <v>2933.3</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B61" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C61" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E61" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F61" t="n">
         <v>5</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z61" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA61" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -7343,10 +6800,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -7355,36 +6812,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B62" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C62" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E62" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z62" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA62" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -7399,7 +6856,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,40 +628,40 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B2" t="n">
-        <v>117.05</v>
+        <v>117.63</v>
       </c>
       <c r="C2" t="n">
-        <v>23.91</v>
+        <v>24.3</v>
       </c>
       <c r="D2" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="E2" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="F2" t="n">
-        <v>10.56</v>
+        <v>10.75</v>
       </c>
       <c r="H2" t="n">
         <v>22.3</v>
       </c>
       <c r="I2" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K2" t="n">
         <v>62.9</v>
       </c>
       <c r="M2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N2" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="O2" t="n">
         <v>31.8</v>
@@ -678,29 +678,20 @@
       <c r="T2" t="n">
         <v>17</v>
       </c>
-      <c r="V2" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA2" t="n">
         <v>22</v>
       </c>
-      <c r="AA2" t="n">
-        <v>21</v>
-      </c>
       <c r="AF2" t="n">
-        <v>225.8</v>
+        <v>220</v>
       </c>
       <c r="AG2" t="n">
-        <v>-5.78</v>
+        <v>-2.67</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -709,7 +700,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>132.41</v>
+        <v>131.69</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -724,13 +715,13 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BM2" t="n">
-        <v>41.59</v>
+        <v>42.83</v>
       </c>
       <c r="BN2" t="n">
-        <v>334.1</v>
+        <v>106.5</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -741,41 +732,26 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B3" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D3" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E3" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F3" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K3" t="n">
         <v>62.9</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O3" t="n">
         <v>31.8</v>
       </c>
@@ -791,29 +767,20 @@
       <c r="T3" t="n">
         <v>17</v>
       </c>
-      <c r="V3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>22</v>
-      </c>
       <c r="Y3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -821,12 +788,6 @@
       <c r="AI3" t="n">
         <v>235</v>
       </c>
-      <c r="AK3" t="n">
-        <v>131.69</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="AM3" t="n">
         <v>110</v>
       </c>
@@ -840,13 +801,13 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM3" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -857,19 +818,19 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B4" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D4" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E4" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F4" t="n">
         <v>10.92</v>
@@ -892,29 +853,20 @@
       <c r="T4" t="n">
         <v>17</v>
       </c>
-      <c r="V4" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="X4" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -935,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM4" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
@@ -952,26 +904,41 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B5" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C5" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D5" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E5" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F5" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.1</v>
       </c>
       <c r="K5" t="n">
         <v>62.9</v>
       </c>
+      <c r="M5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O5" t="n">
         <v>31.8</v>
       </c>
@@ -987,29 +954,20 @@
       <c r="T5" t="n">
         <v>17</v>
       </c>
-      <c r="V5" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>30</v>
-      </c>
-      <c r="X5" t="n">
-        <v>24.3</v>
-      </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1017,6 +975,12 @@
       <c r="AI5" t="n">
         <v>235</v>
       </c>
+      <c r="AK5" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.46</v>
+      </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
@@ -1030,10 +994,10 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM5" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
@@ -1047,46 +1011,46 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B6" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C6" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E6" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F6" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I6" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.9</v>
       </c>
       <c r="N6" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1095,31 +1059,22 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>28</v>
-      </c>
-      <c r="X6" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA6" t="n">
         <v>16</v>
       </c>
-      <c r="Z6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>19</v>
-      </c>
       <c r="AF6" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1128,10 +1083,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1146,13 +1101,13 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM6" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1163,43 +1118,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B7" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C7" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D7" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M7" t="n">
         <v>1.9</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O7" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1213,29 +1168,20 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF7" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG7" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1244,10 +1190,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1262,13 +1208,13 @@
         <v>0</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM7" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN7" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1279,79 +1225,70 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B8" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C8" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D8" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E8" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H8" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K8" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N8" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O8" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>18</v>
-      </c>
-      <c r="X8" t="n">
-        <v>17.1</v>
+        <v>21.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1360,10 +1297,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1372,19 +1309,19 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM8" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -1395,46 +1332,46 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B9" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C9" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D9" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E9" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F9" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H9" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K9" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N9" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O9" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R9" t="n">
         <v>0.6</v>
@@ -1443,31 +1380,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="Y9" t="n">
         <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1476,10 +1404,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL9" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1488,19 +1416,19 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS9" t="n">
         <v>13.07</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM9" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN9" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
@@ -1511,79 +1439,43 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B10" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C10" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D10" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E10" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O10" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>17.6</v>
+        <v>28.5</v>
       </c>
       <c r="Y10" t="n">
         <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF10" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1591,35 +1483,23 @@
       <c r="AI10" t="n">
         <v>235</v>
       </c>
-      <c r="AK10" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM10" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP10" t="n">
         <v>0</v>
@@ -1627,52 +1507,43 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B11" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C11" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D11" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E11" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>18.4</v>
+        <v>36.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1687,69 +1558,87 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM11" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B12" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C12" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D12" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E12" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>35.6</v>
       </c>
       <c r="K12" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>34</v>
       </c>
       <c r="O12" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>18.5</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA12" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1757,17 +1646,29 @@
       <c r="AI12" t="n">
         <v>235</v>
       </c>
+      <c r="AK12" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM12" t="n">
         <v>110</v>
       </c>
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM12" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -1776,84 +1677,75 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B13" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C13" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E13" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F13" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I13" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K13" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O13" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1862,10 +1754,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1874,16 +1766,16 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM13" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -1892,30 +1784,30 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B14" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D14" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E14" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H14" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I14" t="n">
         <v>9.800000000000001</v>
@@ -1924,52 +1816,43 @@
         <v>38.6</v>
       </c>
       <c r="K14" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O14" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>14.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1978,10 +1861,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1990,102 +1873,93 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS14" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM14" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B15" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C15" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D15" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N15" t="n">
         <v>35.2</v>
       </c>
-      <c r="E15" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O15" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X15" t="n">
-        <v>12.6</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2094,10 +1968,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL15" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2106,102 +1980,60 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM15" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B16" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C16" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D16" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E16" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>21</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>21</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
         <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2210,10 +2042,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2221,70 +2053,55 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM16" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN16" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO16" t="n">
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B17" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C17" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D17" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V17" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>23</v>
-      </c>
-      <c r="X17" t="n">
-        <v>16.8</v>
+        <v>9.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2293,10 +2110,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2305,10 +2122,10 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM17" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2317,51 +2134,42 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B18" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C18" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D18" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E18" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X18" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="Y18" t="n">
         <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2370,10 +2178,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL18" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2382,10 +2190,10 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM18" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -2394,51 +2202,75 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B19" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C19" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D19" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E19" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>17</v>
+        <v>9.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
         <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2450,7 +2282,7 @@
         <v>138.94</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2458,11 +2290,17 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AP19" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL19" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM19" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -2471,51 +2309,51 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B20" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C20" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D20" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E20" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I20" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N20" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O20" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R20" t="n">
         <v>3.5</v>
@@ -2524,31 +2362,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W20" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" t="n">
         <v>21</v>
       </c>
-      <c r="X20" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>18</v>
-      </c>
       <c r="AA20" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2557,10 +2386,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2569,16 +2398,16 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS20" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM20" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -2587,84 +2416,75 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B21" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C21" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E21" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H21" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J21" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K21" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O21" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>16.4</v>
+        <v>22.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG21" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2673,10 +2493,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2685,102 +2505,93 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM21" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO21" t="n">
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B22" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D22" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E22" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F22" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H22" t="n">
         <v>25.4</v>
       </c>
       <c r="I22" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J22" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K22" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N22" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O22" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V22" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X22" t="n">
         <v>19.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2789,10 +2600,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2801,102 +2612,93 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM22" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN22" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO22" t="n">
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B23" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C23" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D23" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E23" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F23" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H23" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I23" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J23" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O23" t="n">
         <v>38.4</v>
       </c>
-      <c r="K23" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q23" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG23" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2905,10 +2707,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2917,102 +2719,66 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM23" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN23" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO23" t="n">
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B24" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C24" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D24" t="n">
         <v>34.5</v>
       </c>
       <c r="E24" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F24" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H24" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K24" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O24" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X24" t="n">
-        <v>16.1</v>
+        <v>36.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA24" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF24" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -3021,10 +2787,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -3032,17 +2798,11 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM24" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
@@ -3051,57 +2811,48 @@
         <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B25" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C25" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D25" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E25" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
         <v>9.6</v>
       </c>
       <c r="K25" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W25" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X25" t="n">
-        <v>13.7</v>
+        <v>34.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25" t="n">
         <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3110,10 +2861,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3122,69 +2873,87 @@
         <v>142</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM25" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP25" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B26" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C26" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D26" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>38.7</v>
       </c>
       <c r="K26" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>33</v>
       </c>
       <c r="O26" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W26" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X26" t="n">
-        <v>10.9</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3196,7 +2965,7 @@
         <v>128.27</v>
       </c>
       <c r="AL26" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3204,97 +2973,94 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
+      <c r="AP26" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL26" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM26" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP26" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B27" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C27" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D27" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E27" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F27" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="n">
         <v>25.1</v>
       </c>
       <c r="I27" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J27" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K27" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O27" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>10.9</v>
+        <v>23.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3303,10 +3069,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3315,72 +3081,72 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM27" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP27" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B28" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C28" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D28" t="n">
         <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F28" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H28" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O28" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q28" t="n">
         <v>23.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -3388,29 +3154,20 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
-      <c r="V28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3419,10 +3176,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL28" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3431,69 +3188,69 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS28" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM28" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP28" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B29" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C29" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E29" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F29" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I29" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J29" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K29" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O29" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R29" t="n">
         <v>1.3</v>
@@ -3502,31 +3259,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X29" t="n">
-        <v>15.8</v>
+        <v>22.7</v>
       </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA29" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3535,10 +3283,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3547,102 +3295,93 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM29" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN29" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP29" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B30" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C30" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D30" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E30" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H30" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I30" t="n">
         <v>9.4</v>
       </c>
       <c r="J30" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O30" t="n">
         <v>39.5</v>
       </c>
-      <c r="K30" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q30" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>23</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.2</v>
+        <v>23.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3651,10 +3390,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3663,102 +3402,66 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM30" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO30" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP30" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B31" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C31" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D31" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E31" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F31" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y31" t="n">
         <v>8</v>
       </c>
-      <c r="H31" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K31" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N31" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10</v>
-      </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3767,10 +3470,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3778,76 +3481,61 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM31" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN31" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP31" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B32" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C32" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D32" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E32" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F32" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K32" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O32" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>16.4</v>
+        <v>38.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3856,10 +3544,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL32" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3868,69 +3556,87 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM32" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP32" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B33" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C33" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F33" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>40</v>
       </c>
       <c r="K33" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>36.7</v>
       </c>
       <c r="O33" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X33" t="n">
-        <v>14.2</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3942,7 +3648,7 @@
         <v>125.11</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3950,97 +3656,94 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>14</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM33" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN33" t="n">
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP33" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B34" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C34" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E34" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F34" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H34" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K34" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O34" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T34" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W34" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10.6</v>
+        <v>23.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA34" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -4049,10 +3752,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -4061,102 +3764,93 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS34" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM34" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN34" t="n">
         <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP34" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B35" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C35" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E35" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F35" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H35" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K35" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O35" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T35" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10.6</v>
+        <v>22.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -4165,10 +3859,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -4177,102 +3871,93 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS35" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM35" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP35" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B36" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C36" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D36" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E36" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F36" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H36" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q36" t="n">
         <v>23.7</v>
       </c>
-      <c r="I36" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J36" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K36" t="n">
-        <v>73</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>34</v>
-      </c>
-      <c r="O36" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S36" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T36" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W36" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>10.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG36" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4281,10 +3966,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL36" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4293,102 +3978,93 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM36" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO36" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP36" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B37" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C37" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E37" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F37" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I37" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>40.8</v>
       </c>
       <c r="K37" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O37" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T37" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>11.4</v>
+        <v>23.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4397,10 +4073,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL37" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4409,102 +4085,66 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS37" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM37" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN37" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO37" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP37" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B38" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C38" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E38" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H38" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J38" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K38" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O38" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2</v>
-      </c>
-      <c r="S38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>12.7</v>
+        <v>34.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="n">
         <v>13</v>
       </c>
       <c r="AA38" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF38" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4513,10 +4153,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4524,76 +4164,61 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
-      <c r="AP38" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL38" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM38" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN38" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO38" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP38" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B39" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C39" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D39" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E39" t="n">
         <v>29.8</v>
       </c>
       <c r="F39" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K39" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O39" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W39" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X39" t="n">
-        <v>12.6</v>
+        <v>35.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4602,10 +4227,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4614,33 +4239,33 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM39" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN39" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO39" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP39" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B40" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C40" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D40" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E40" t="n">
         <v>29.8</v>
@@ -4649,34 +4274,25 @@
         <v>6.6</v>
       </c>
       <c r="K40" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
         <v>12.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4685,10 +4301,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4697,69 +4313,87 @@
         <v>142</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM40" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN40" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO40" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP40" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B41" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C41" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D41" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E41" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F41" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>41.1</v>
       </c>
       <c r="K41" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4</v>
+      </c>
+      <c r="N41" t="n">
+        <v>37.4</v>
       </c>
       <c r="O41" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="V41" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W41" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>13.2</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y41" t="n">
         <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF41" t="n">
         <v>220</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4771,7 +4405,7 @@
         <v>126.54</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4779,97 +4413,94 @@
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM41" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN41" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP41" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B42" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C42" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D42" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E42" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F42" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H42" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I42" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K42" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N42" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O42" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W42" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X42" t="n">
-        <v>14.1</v>
+        <v>24.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF42" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4878,10 +4509,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4890,102 +4521,93 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM42" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN42" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO42" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP42" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B43" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C43" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E43" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F43" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I43" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K43" t="n">
         <v>76.5</v>
       </c>
       <c r="M43" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N43" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O43" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R43" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>15.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA43" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4994,10 +4616,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -5006,72 +4628,72 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS43" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM43" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN43" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO43" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP43" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B44" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C44" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E44" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H44" t="n">
         <v>26.1</v>
       </c>
       <c r="I44" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J44" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K44" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N44" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O44" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q44" t="n">
         <v>24.2</v>
       </c>
       <c r="R44" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -5079,29 +4701,20 @@
       <c r="T44" t="n">
         <v>24.2</v>
       </c>
-      <c r="V44" t="n">
-        <v>10</v>
-      </c>
-      <c r="W44" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X44" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z44" t="n">
         <v>16</v>
       </c>
       <c r="AA44" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -5110,10 +4723,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -5122,102 +4735,66 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS44" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM44" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN44" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO44" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP44" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B45" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C45" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D45" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E45" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F45" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H45" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K45" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M45" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V45" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W45" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>15.4</v>
+        <v>37.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z45" t="n">
         <v>16</v>
       </c>
       <c r="AA45" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF45" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5226,10 +4803,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5237,76 +4814,61 @@
       <c r="AN45" t="n">
         <v>142</v>
       </c>
-      <c r="AP45" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL45" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM45" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN45" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP45" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B46" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C46" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D46" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E46" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F46" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K46" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V46" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>16</v>
+        <v>37.7</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
         <v>16</v>
       </c>
       <c r="AA46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF46" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5315,10 +4877,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5327,69 +4889,87 @@
         <v>142</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM46" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN46" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO46" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP46" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B47" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C47" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D47" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E47" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F47" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>41.3</v>
       </c>
       <c r="K47" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N47" t="n">
+        <v>37.1</v>
       </c>
       <c r="O47" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="V47" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.6</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF47" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5401,7 +4981,7 @@
         <v>125.03</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5409,97 +4989,94 @@
       <c r="AN47" t="n">
         <v>142</v>
       </c>
+      <c r="AP47" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL47" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM47" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN47" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO47" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP47" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B48" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C48" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E48" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F48" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I48" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K48" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M48" t="n">
         <v>2.7</v>
       </c>
       <c r="N48" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O48" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R48" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T48" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V48" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W48" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X48" t="n">
-        <v>17.4</v>
+        <v>24</v>
       </c>
       <c r="Y48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA48" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF48" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5508,10 +5085,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5520,87 +5097,78 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS48" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM48" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN48" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO48" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP48" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B49" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C49" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D49" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E49" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F49" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I49" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K49" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O49" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>16</v>
       </c>
       <c r="T49" t="n">
-        <v>24</v>
-      </c>
-      <c r="V49" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W49" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>16.5</v>
+        <v>23.9</v>
       </c>
       <c r="Y49" t="n">
         <v>10</v>
@@ -5609,13 +5177,13 @@
         <v>15</v>
       </c>
       <c r="AA49" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF49" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5624,10 +5192,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL49" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5636,102 +5204,93 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS49" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM49" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN49" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO49" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP49" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B50" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C50" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D50" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E50" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F50" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H50" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I50" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K50" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N50" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O50" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S50" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T50" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V50" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z50" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF50" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5740,10 +5299,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL50" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5752,87 +5311,78 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM50" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN50" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO50" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP50" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B51" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C51" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D51" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E51" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F51" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I51" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J51" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K51" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M51" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N51" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O51" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S51" t="n">
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V51" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.2</v>
+        <v>23.5</v>
       </c>
       <c r="Y51" t="n">
         <v>13</v>
@@ -5841,13 +5391,13 @@
         <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF51" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5856,10 +5406,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL51" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5868,102 +5418,66 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS51" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM51" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN51" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO51" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP51" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B52" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C52" t="n">
         <v>57.9</v>
       </c>
       <c r="D52" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E52" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H52" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I52" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N52" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S52" t="n">
-        <v>12</v>
-      </c>
-      <c r="T52" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V52" t="n">
-        <v>17</v>
-      </c>
-      <c r="W52" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X52" t="n">
-        <v>18.9</v>
+        <v>39</v>
       </c>
       <c r="Y52" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z52" t="n">
         <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF52" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5972,10 +5486,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL52" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5983,76 +5497,61 @@
       <c r="AN52" t="n">
         <v>142</v>
       </c>
-      <c r="AP52" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM52" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN52" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO52" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP52" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B53" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C53" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D53" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E53" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K53" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O53" t="n">
-        <v>39</v>
-      </c>
-      <c r="V53" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X53" t="n">
-        <v>19.5</v>
+        <v>40.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z53" t="n">
         <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF53" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -6061,10 +5560,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -6073,69 +5572,87 @@
         <v>142</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM53" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN53" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO53" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP53" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B54" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C54" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D54" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E54" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F54" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H54" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J54" t="n">
+        <v>40.6</v>
       </c>
       <c r="K54" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N54" t="n">
+        <v>36</v>
       </c>
       <c r="O54" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>17</v>
-      </c>
-      <c r="W54" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X54" t="n">
-        <v>19.8</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA54" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6147,7 +5664,7 @@
         <v>128.43</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -6155,97 +5672,94 @@
       <c r="AN54" t="n">
         <v>142</v>
       </c>
+      <c r="AP54" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL54" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM54" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN54" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO54" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP54" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B55" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C55" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D55" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E55" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F55" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H55" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I55" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K55" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N55" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O55" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W55" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X55" t="n">
-        <v>16.6</v>
+        <v>22.2</v>
       </c>
       <c r="Y55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6254,10 +5768,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -6266,93 +5780,93 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM55" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN55" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO55" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP55" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B56" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C56" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D56" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E56" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F56" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H56" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I56" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K56" t="n">
         <v>75.7</v>
       </c>
       <c r="M56" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O56" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R56" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T56" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA56" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF56" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6361,10 +5875,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -6373,93 +5887,93 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS56" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM56" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN56" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO56" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP56" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B57" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C57" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D57" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E57" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F57" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K57" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O57" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R57" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S57" t="n">
         <v>17</v>
       </c>
       <c r="T57" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA57" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF57" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6468,10 +5982,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL57" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6480,93 +5994,93 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS57" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM57" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN57" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO57" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP57" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B58" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C58" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D58" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E58" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H58" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I58" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J58" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K58" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N58" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O58" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R58" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S58" t="n">
         <v>17</v>
       </c>
       <c r="T58" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y58" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG58" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6575,10 +6089,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL58" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6587,93 +6101,60 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS58" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM58" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN58" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO58" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP58" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B59" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C59" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D59" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E59" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F59" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H59" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J59" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="K59" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N59" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O59" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S59" t="n">
-        <v>17</v>
-      </c>
-      <c r="T59" t="n">
-        <v>22.9</v>
+        <v>5</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z59" t="n">
         <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AF59" t="n">
-        <v>218.89</v>
+        <v>222.39</v>
       </c>
       <c r="AG59" t="n">
-        <v>4.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6682,10 +6163,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6693,55 +6174,43 @@
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="BM59" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="BN59" t="n">
-        <v>705.1</v>
-      </c>
-      <c r="BO59" t="n">
-        <v>1122.7</v>
-      </c>
-      <c r="BP59" t="n">
-        <v>2933.3</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B60" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C60" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E60" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
       </c>
       <c r="Y60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
-        <v>12</v>
+        <v>11.5</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>221.63</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>-0.76</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6750,10 +6219,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6762,36 +6231,42 @@
         <v>142</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B61" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C61" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E61" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA61" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>222.64</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.02</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6800,10 +6275,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>129.31</v>
+        <v>130.65</v>
       </c>
       <c r="AL61" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6812,36 +6287,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B62" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="C62" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>30.9</v>
+        <v>31.5</v>
       </c>
       <c r="E62" t="n">
-        <v>34</v>
+        <v>32.9</v>
       </c>
       <c r="F62" t="n">
         <v>5.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6856,7 +6331,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,41 +628,26 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2" t="n">
-        <v>117.63</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="D2" t="n">
-        <v>36.99</v>
+        <v>37.02</v>
       </c>
       <c r="E2" t="n">
-        <v>35.59</v>
+        <v>35.31</v>
       </c>
       <c r="F2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.1</v>
+        <v>10.92</v>
       </c>
       <c r="K2" t="n">
         <v>62.9</v>
       </c>
-      <c r="M2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>31.8</v>
-      </c>
       <c r="O2" t="n">
         <v>31.8</v>
       </c>
@@ -678,20 +663,29 @@
       <c r="T2" t="n">
         <v>17</v>
       </c>
+      <c r="V2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>22.5</v>
+      </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>220</v>
+        <v>216.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -699,9 +693,6 @@
       <c r="AI2" t="n">
         <v>235</v>
       </c>
-      <c r="AK2" t="n">
-        <v>131.69</v>
-      </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
@@ -715,13 +706,13 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="BM2" t="n">
-        <v>42.83</v>
+        <v>43.65</v>
       </c>
       <c r="BN2" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -732,19 +723,19 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B3" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C3" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D3" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E3" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F3" t="n">
         <v>10.92</v>
@@ -767,20 +758,29 @@
       <c r="T3" t="n">
         <v>17</v>
       </c>
+      <c r="V3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>30</v>
+      </c>
+      <c r="X3" t="n">
+        <v>24.3</v>
+      </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM3" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
@@ -818,26 +818,41 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B4" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C4" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D4" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E4" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F4" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.1</v>
       </c>
       <c r="K4" t="n">
         <v>62.9</v>
       </c>
+      <c r="M4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O4" t="n">
         <v>31.8</v>
       </c>
@@ -853,20 +868,29 @@
       <c r="T4" t="n">
         <v>17</v>
       </c>
+      <c r="V4" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>28</v>
+      </c>
+      <c r="X4" t="n">
+        <v>23.9</v>
+      </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -874,6 +898,9 @@
       <c r="AI4" t="n">
         <v>235</v>
       </c>
+      <c r="AK4" t="n">
+        <v>133.15</v>
+      </c>
       <c r="AM4" t="n">
         <v>110</v>
       </c>
@@ -887,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM4" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
@@ -904,46 +931,46 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B5" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C5" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D5" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E5" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F5" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I5" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M5" t="n">
         <v>1.9</v>
       </c>
       <c r="N5" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -952,22 +979,31 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA5" t="n">
         <v>16</v>
       </c>
-      <c r="Z5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>19</v>
-      </c>
       <c r="AF5" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -976,10 +1012,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.46</v>
+        <v>4.18</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -994,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM5" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1011,43 +1047,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B6" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C6" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D6" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E6" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M6" t="n">
         <v>1.9</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O6" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1061,20 +1097,29 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>18</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG6" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1083,10 +1128,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1101,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM6" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN6" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1118,70 +1163,79 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B7" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D7" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E7" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H7" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K7" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O7" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>21.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1190,10 +1244,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1202,19 +1256,19 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM7" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1225,46 +1279,46 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B8" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C8" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D8" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E8" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F8" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H8" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K8" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N8" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O8" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R8" t="n">
         <v>0.6</v>
@@ -1273,22 +1327,31 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17.6</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1297,10 +1360,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1309,19 +1372,19 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS8" t="n">
         <v>13.07</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM8" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN8" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -1332,70 +1395,52 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B9" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C9" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D9" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E9" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J9" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O9" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>18.4</v>
       </c>
       <c r="Y9" t="n">
         <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1403,35 +1448,23 @@
       <c r="AI9" t="n">
         <v>235</v>
       </c>
-      <c r="AK9" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM9" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP9" t="n">
         <v>0</v>
@@ -1439,43 +1472,52 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B10" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C10" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D10" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E10" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1490,60 +1532,96 @@
         <v>142</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM10" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B11" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D11" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E11" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.6</v>
       </c>
       <c r="K11" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>34</v>
       </c>
       <c r="O11" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1551,17 +1629,29 @@
       <c r="AI11" t="n">
         <v>235</v>
       </c>
+      <c r="AK11" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM11" t="n">
         <v>110</v>
       </c>
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM11" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -1570,75 +1660,84 @@
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B12" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C12" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E12" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F12" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H12" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I12" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K12" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O12" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1647,10 +1746,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1659,16 +1758,16 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM12" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -1677,30 +1776,30 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B13" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D13" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E13" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H13" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I13" t="n">
         <v>9.800000000000001</v>
@@ -1709,43 +1808,52 @@
         <v>38.6</v>
       </c>
       <c r="K13" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O13" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1754,10 +1862,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1766,93 +1874,102 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM13" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B14" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C14" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D14" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N14" t="n">
         <v>35.2</v>
       </c>
-      <c r="E14" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J14" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O14" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>21.8</v>
+        <v>21</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>14.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF14" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1861,10 +1978,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL14" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1873,93 +1990,69 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM14" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B15" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C15" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D15" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E15" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>21</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V15" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
         <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG15" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1968,10 +2061,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL15" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1979,61 +2072,64 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM15" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN15" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B16" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C16" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D16" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X16" t="n">
+        <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2042,10 +2138,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2054,10 +2150,10 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM16" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -2066,42 +2162,51 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B17" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C17" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D17" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E17" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F17" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
         <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2110,10 +2215,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL17" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2122,10 +2227,10 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM17" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2134,42 +2239,84 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B18" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C18" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D18" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E18" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F18" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
         <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2181,7 +2328,7 @@
         <v>138.94</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2189,11 +2336,17 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM18" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -2202,51 +2355,51 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B19" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C19" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D19" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E19" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I19" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N19" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O19" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R19" t="n">
         <v>3.5</v>
@@ -2255,22 +2408,31 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W19" t="n">
         <v>22.3</v>
       </c>
+      <c r="X19" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2279,10 +2441,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2291,16 +2453,16 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS19" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM19" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -2309,75 +2471,84 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B20" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C20" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E20" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H20" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J20" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K20" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O20" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
+      </c>
+      <c r="V20" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2386,10 +2557,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2398,93 +2569,102 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM20" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B21" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D21" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E21" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F21" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H21" t="n">
         <v>25.4</v>
       </c>
       <c r="I21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J21" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K21" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N21" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O21" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>20.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2493,10 +2673,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2505,93 +2685,102 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS21" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM21" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN21" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO21" t="n">
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B22" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C22" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D22" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E22" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F22" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H22" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I22" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J22" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O22" t="n">
         <v>38.4</v>
       </c>
-      <c r="K22" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q22" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
+      </c>
+      <c r="V22" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG22" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2600,10 +2789,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2612,93 +2801,75 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM22" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN22" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO22" t="n">
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B23" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C23" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D23" t="n">
         <v>34.5</v>
       </c>
       <c r="E23" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F23" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H23" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I23" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K23" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N23" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O23" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>13.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF23" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2707,10 +2878,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2718,17 +2889,11 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
-      <c r="AP23" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM23" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
@@ -2737,48 +2902,57 @@
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B24" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C24" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D24" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E24" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
         <v>9.6</v>
       </c>
       <c r="K24" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z24" t="n">
         <v>13</v>
       </c>
       <c r="AA24" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2787,10 +2961,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2799,60 +2973,96 @@
         <v>142</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM24" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP24" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B25" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C25" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D25" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>38.7</v>
       </c>
       <c r="K25" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>33</v>
       </c>
       <c r="O25" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2864,7 +3074,7 @@
         <v>128.27</v>
       </c>
       <c r="AL25" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2872,88 +3082,103 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM25" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP25" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B26" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C26" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D26" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="n">
         <v>25.1</v>
       </c>
       <c r="I26" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J26" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K26" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O26" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2962,10 +3187,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2974,72 +3199,72 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM26" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP26" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B27" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C27" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D27" t="n">
         <v>34</v>
       </c>
       <c r="E27" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F27" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H27" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I27" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K27" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O27" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q27" t="n">
         <v>23.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -3047,20 +3272,29 @@
       <c r="T27" t="n">
         <v>23.1</v>
       </c>
+      <c r="V27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3069,10 +3303,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL27" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3081,69 +3315,69 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS27" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM27" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP27" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B28" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C28" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E28" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F28" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I28" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J28" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K28" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O28" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R28" t="n">
         <v>1.3</v>
@@ -3152,22 +3386,31 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
+      </c>
+      <c r="V28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>23</v>
+      </c>
+      <c r="X28" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y28" t="n">
         <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3176,10 +3419,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3188,93 +3431,102 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS28" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM28" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN28" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP28" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B29" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C29" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D29" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E29" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I29" t="n">
         <v>9.4</v>
       </c>
       <c r="J29" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O29" t="n">
         <v>39.5</v>
       </c>
-      <c r="K29" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q29" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>15.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA29" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG29" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3283,10 +3535,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3295,93 +3547,75 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM29" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO29" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP29" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B30" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C30" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D30" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E30" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y30" t="n">
         <v>8</v>
       </c>
-      <c r="H30" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K30" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N30" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>10</v>
-      </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3390,10 +3624,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3401,67 +3635,70 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
-      <c r="AP30" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM30" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN30" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP30" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B31" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C31" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D31" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E31" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K31" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O31" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
+      </c>
+      <c r="V31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3470,10 +3707,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL31" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3482,60 +3719,96 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM31" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP31" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B32" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C32" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F32" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>36.7</v>
       </c>
       <c r="O32" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W32" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3547,7 +3820,7 @@
         <v>125.11</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3555,88 +3828,103 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>14</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM32" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B33" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C33" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E33" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H33" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I33" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K33" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O33" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T33" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA33" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3645,10 +3933,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3657,93 +3945,102 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS33" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM33" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN33" t="n">
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP33" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B34" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C34" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E34" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F34" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H34" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K34" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O34" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T34" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3752,10 +4049,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3764,93 +4061,102 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS34" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM34" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN34" t="n">
         <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP34" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B35" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C35" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D35" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E35" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F35" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H35" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q35" t="n">
         <v>23.7</v>
       </c>
-      <c r="I35" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J35" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K35" t="n">
-        <v>73</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>34</v>
-      </c>
-      <c r="O35" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S35" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T35" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG35" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3859,10 +4165,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL35" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3871,93 +4177,102 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM35" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO35" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B36" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C36" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E36" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F36" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H36" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I36" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>40.8</v>
       </c>
       <c r="K36" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O36" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T36" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>12.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF36" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3966,10 +4281,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL36" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3978,93 +4293,75 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS36" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM36" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN36" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO36" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP36" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B37" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C37" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E37" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H37" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J37" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K37" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4</v>
-      </c>
-      <c r="N37" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O37" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T37" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X37" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z37" t="n">
         <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF37" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4073,10 +4370,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL37" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4084,67 +4381,70 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
-      <c r="AP37" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL37" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM37" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN37" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO37" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP37" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B38" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C38" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D38" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E38" t="n">
         <v>29.8</v>
       </c>
       <c r="F38" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K38" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O38" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>8</v>
+      </c>
+      <c r="W38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4153,10 +4453,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL38" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4165,33 +4465,33 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM38" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN38" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO38" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP38" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B39" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C39" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D39" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E39" t="n">
         <v>29.8</v>
@@ -4200,25 +4500,34 @@
         <v>6.6</v>
       </c>
       <c r="K39" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
+      </c>
+      <c r="V39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W39" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA39" t="n">
         <v>12.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4227,10 +4536,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4239,60 +4548,96 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM39" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN39" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO39" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP39" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B40" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C40" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D40" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E40" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F40" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>41.1</v>
       </c>
       <c r="K40" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>37.4</v>
       </c>
       <c r="O40" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>14.1</v>
       </c>
       <c r="Y40" t="n">
         <v>9</v>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF40" t="n">
         <v>220</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4304,7 +4649,7 @@
         <v>126.54</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4312,88 +4657,103 @@
       <c r="AN40" t="n">
         <v>142</v>
       </c>
+      <c r="AP40" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL40" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM40" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN40" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO40" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP40" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B41" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D41" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E41" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F41" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H41" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I41" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K41" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N41" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O41" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>15.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF41" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4402,10 +4762,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4414,93 +4774,102 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS41" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM41" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN41" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO41" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP41" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B42" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C42" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E42" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F42" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I42" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K42" t="n">
         <v>76.5</v>
       </c>
       <c r="M42" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N42" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O42" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R42" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
+      </c>
+      <c r="V42" t="n">
+        <v>10</v>
+      </c>
+      <c r="W42" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>15.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG42" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4509,10 +4878,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4521,72 +4890,72 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM42" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN42" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO42" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP42" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B43" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C43" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D43" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E43" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H43" t="n">
         <v>26.1</v>
       </c>
       <c r="I43" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J43" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K43" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N43" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O43" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q43" t="n">
         <v>24.2</v>
       </c>
       <c r="R43" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -4594,20 +4963,29 @@
       <c r="T43" t="n">
         <v>24.2</v>
       </c>
+      <c r="V43" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W43" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>15.4</v>
+      </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z43" t="n">
         <v>16</v>
       </c>
       <c r="AA43" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4616,10 +4994,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4628,93 +5006,75 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS43" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM43" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN43" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO43" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP43" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B44" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C44" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D44" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E44" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H44" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J44" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K44" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
+      </c>
+      <c r="V44" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16</v>
       </c>
       <c r="Y44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
         <v>16</v>
       </c>
       <c r="AA44" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF44" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4723,10 +5083,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL44" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4734,67 +5094,70 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
-      <c r="AP44" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL44" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM44" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN44" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO44" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP44" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B45" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C45" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D45" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E45" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F45" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K45" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
+      </c>
+      <c r="V45" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W45" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
         <v>16</v>
       </c>
       <c r="AA45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF45" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4803,10 +5166,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4815,60 +5178,96 @@
         <v>142</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM45" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN45" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP45" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B46" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C46" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D46" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E46" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F46" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H46" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J46" t="n">
+        <v>41.3</v>
       </c>
       <c r="K46" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N46" t="n">
+        <v>37.1</v>
       </c>
       <c r="O46" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="V46" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF46" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4880,7 +5279,7 @@
         <v>125.03</v>
       </c>
       <c r="AL46" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4888,88 +5287,103 @@
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM46" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN46" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO46" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP46" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B47" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C47" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E47" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F47" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K47" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M47" t="n">
         <v>2.7</v>
       </c>
       <c r="N47" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O47" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R47" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>23.9</v>
+        <v>24</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA47" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF47" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -4978,10 +5392,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -4990,78 +5404,87 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS47" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM47" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN47" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO47" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP47" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B48" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C48" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D48" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E48" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F48" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I48" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K48" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O48" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>16</v>
       </c>
       <c r="T48" t="n">
-        <v>24</v>
+        <v>23.9</v>
+      </c>
+      <c r="V48" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X48" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -5070,13 +5493,13 @@
         <v>15</v>
       </c>
       <c r="AA48" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5085,10 +5508,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL48" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5097,93 +5520,102 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS48" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM48" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN48" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO48" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP48" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B49" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C49" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D49" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E49" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F49" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H49" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I49" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K49" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N49" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O49" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S49" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T49" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X49" t="n">
+        <v>19.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z49" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF49" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5192,10 +5624,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL49" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5204,78 +5636,87 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS49" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM49" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN49" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO49" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP49" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B50" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C50" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D50" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E50" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F50" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J50" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K50" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M50" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O50" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S50" t="n">
         <v>12</v>
       </c>
       <c r="T50" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
+      </c>
+      <c r="V50" t="n">
+        <v>17</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X50" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y50" t="n">
         <v>13</v>
@@ -5284,13 +5725,13 @@
         <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF50" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5299,10 +5740,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL50" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5311,93 +5752,75 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS50" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM50" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN50" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO50" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP50" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B51" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C51" t="n">
         <v>57.9</v>
       </c>
       <c r="D51" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E51" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F51" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H51" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I51" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N51" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S51" t="n">
-        <v>12</v>
-      </c>
-      <c r="T51" t="n">
-        <v>23.5</v>
+        <v>39</v>
+      </c>
+      <c r="V51" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z51" t="n">
         <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF51" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5406,10 +5829,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL51" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5417,67 +5840,70 @@
       <c r="AN51" t="n">
         <v>142</v>
       </c>
-      <c r="AP51" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM51" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN51" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO51" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP51" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B52" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C52" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D52" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E52" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K52" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O52" t="n">
-        <v>39</v>
+        <v>40.1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>17</v>
+      </c>
+      <c r="W52" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z52" t="n">
         <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF52" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5486,10 +5912,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5498,60 +5924,96 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM52" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN52" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO52" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP52" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B53" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C53" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D53" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E53" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F53" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J53" t="n">
+        <v>40.6</v>
       </c>
       <c r="K53" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N53" t="n">
+        <v>36</v>
       </c>
       <c r="O53" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V53" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W53" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA53" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5563,7 +6025,7 @@
         <v>128.43</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5571,88 +6033,103 @@
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM53" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN53" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO53" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP53" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B54" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C54" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D54" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E54" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F54" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H54" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I54" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K54" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O54" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
+      </c>
+      <c r="V54" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W54" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA54" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5661,10 +6138,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5673,93 +6150,102 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM54" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN54" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO54" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP54" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B55" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C55" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D55" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E55" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F55" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H55" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I55" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K55" t="n">
         <v>75.7</v>
       </c>
       <c r="M55" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N55" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O55" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R55" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T55" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W55" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X55" t="n">
+        <v>15.4</v>
       </c>
       <c r="Y55" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA55" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5768,10 +6254,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL55" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5780,93 +6266,93 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS55" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM55" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN55" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO55" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP55" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B56" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C56" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D56" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E56" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F56" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K56" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N56" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O56" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R56" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S56" t="n">
         <v>17</v>
       </c>
       <c r="T56" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA56" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF56" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5875,10 +6361,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL56" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5887,93 +6373,93 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS56" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM56" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN56" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP56" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B57" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C57" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D57" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E57" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H57" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I57" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J57" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K57" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N57" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O57" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q57" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R57" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S57" t="n">
         <v>17</v>
       </c>
       <c r="T57" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y57" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA57" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG57" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5982,10 +6468,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL57" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5994,93 +6480,60 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS57" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM57" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN57" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO57" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP57" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B58" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C58" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D58" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E58" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F58" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H58" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J58" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="K58" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N58" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O58" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S58" t="n">
-        <v>17</v>
-      </c>
-      <c r="T58" t="n">
-        <v>22.9</v>
+        <v>5</v>
       </c>
       <c r="Y58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
         <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AF58" t="n">
-        <v>218.89</v>
+        <v>222.39</v>
       </c>
       <c r="AG58" t="n">
-        <v>4.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6089,10 +6542,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6100,61 +6553,43 @@
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="BN58" t="n">
-        <v>705.1</v>
-      </c>
-      <c r="BO58" t="n">
-        <v>1122.7</v>
-      </c>
-      <c r="BP58" t="n">
-        <v>2933.3</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B59" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C59" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E59" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
       </c>
       <c r="Y59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>222.39</v>
+        <v>221.63</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6163,10 +6598,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6175,42 +6610,42 @@
         <v>142</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B60" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C60" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E60" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA60" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AF60" t="n">
-        <v>221.63</v>
+        <v>222.64</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6219,10 +6654,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.31</v>
+        <v>130.65</v>
       </c>
       <c r="AL60" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6231,42 +6666,42 @@
         <v>142</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B61" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="C61" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>30.9</v>
+        <v>31.5</v>
       </c>
       <c r="E61" t="n">
-        <v>34</v>
+        <v>32.9</v>
       </c>
       <c r="F61" t="n">
         <v>5.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA61" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AF61" t="n">
-        <v>222.64</v>
+        <v>224.59</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6275,10 +6710,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>130.65</v>
+        <v>131.48</v>
       </c>
       <c r="AL61" t="n">
-        <v>1.34</v>
+        <v>0.83</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6287,36 +6722,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B62" t="n">
-        <v>152</v>
+        <v>156.5</v>
       </c>
       <c r="C62" t="n">
-        <v>72.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="D62" t="n">
-        <v>31.5</v>
+        <v>32.3</v>
       </c>
       <c r="E62" t="n">
-        <v>32.9</v>
+        <v>38.3</v>
       </c>
       <c r="F62" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Z62" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6331,7 +6766,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,19 +628,19 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>116.3</v>
       </c>
       <c r="C2" t="n">
-        <v>24.75</v>
+        <v>25.23</v>
       </c>
       <c r="D2" t="n">
-        <v>37.02</v>
+        <v>37.18</v>
       </c>
       <c r="E2" t="n">
-        <v>35.31</v>
+        <v>32.98</v>
       </c>
       <c r="F2" t="n">
         <v>10.92</v>
@@ -663,29 +663,20 @@
       <c r="T2" t="n">
         <v>17</v>
       </c>
-      <c r="V2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>216.02</v>
+        <v>216.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -706,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="BM2" t="n">
-        <v>43.65</v>
+        <v>39.75</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
@@ -723,26 +714,41 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B3" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C3" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D3" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E3" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F3" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.1</v>
       </c>
       <c r="K3" t="n">
         <v>62.9</v>
       </c>
+      <c r="M3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O3" t="n">
         <v>31.8</v>
       </c>
@@ -758,29 +764,20 @@
       <c r="T3" t="n">
         <v>17</v>
       </c>
-      <c r="V3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>30</v>
-      </c>
-      <c r="X3" t="n">
-        <v>24.3</v>
-      </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -788,6 +785,9 @@
       <c r="AI3" t="n">
         <v>235</v>
       </c>
+      <c r="AK3" t="n">
+        <v>133.15</v>
+      </c>
       <c r="AM3" t="n">
         <v>110</v>
       </c>
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM3" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
@@ -818,46 +818,46 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B4" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C4" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D4" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E4" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F4" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I4" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.9</v>
       </c>
       <c r="N4" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -866,31 +866,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>17</v>
-      </c>
-      <c r="V4" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>28</v>
-      </c>
-      <c r="X4" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA4" t="n">
         <v>16</v>
       </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>19</v>
-      </c>
       <c r="AF4" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -899,7 +890,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.18</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -914,13 +908,13 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM4" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -931,43 +925,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B5" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C5" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D5" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E5" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M5" t="n">
         <v>1.9</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O5" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -981,29 +975,20 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1012,10 +997,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1030,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM5" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN5" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1047,79 +1032,70 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B6" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C6" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D6" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E6" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H6" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K6" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O6" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>18</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.1</v>
+        <v>21.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1128,10 +1104,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL6" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1140,19 +1116,19 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM6" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1163,46 +1139,46 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B7" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C7" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D7" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E7" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F7" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K7" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N7" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O7" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R7" t="n">
         <v>0.6</v>
@@ -1211,31 +1187,22 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W7" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1244,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1256,19 +1223,19 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS7" t="n">
         <v>13.07</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM7" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN7" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -1279,79 +1246,43 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B8" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C8" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D8" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E8" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O8" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="W8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>17.6</v>
+        <v>28.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF8" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1359,35 +1290,23 @@
       <c r="AI8" t="n">
         <v>235</v>
       </c>
-      <c r="AK8" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
         <v>142</v>
       </c>
-      <c r="AP8" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL8" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM8" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP8" t="n">
         <v>0</v>
@@ -1395,52 +1314,43 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B9" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C9" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D9" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E9" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>18.4</v>
+        <v>36.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1455,69 +1365,87 @@
         <v>142</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM9" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B10" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C10" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D10" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E10" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35.6</v>
       </c>
       <c r="K10" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34</v>
       </c>
       <c r="O10" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>18.5</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1525,17 +1453,29 @@
       <c r="AI10" t="n">
         <v>235</v>
       </c>
+      <c r="AK10" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
         <v>142</v>
       </c>
+      <c r="AP10" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL10" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM10" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -1544,84 +1484,75 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B11" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C11" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E11" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F11" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I11" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K11" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O11" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1630,10 +1561,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1642,16 +1573,16 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM11" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -1660,30 +1591,30 @@
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B12" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D12" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H12" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I12" t="n">
         <v>9.800000000000001</v>
@@ -1692,52 +1623,43 @@
         <v>38.6</v>
       </c>
       <c r="K12" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O12" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1746,10 +1668,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1758,102 +1680,93 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM12" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B13" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C13" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D13" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N13" t="n">
         <v>35.2</v>
       </c>
-      <c r="E13" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O13" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>12.6</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF13" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1862,10 +1775,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL13" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1874,102 +1787,60 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM13" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B14" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C14" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D14" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E14" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>21</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X14" t="n">
-        <v>14.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
         <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1978,10 +1849,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL14" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1989,70 +1860,55 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM14" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN14" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B15" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C15" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D15" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V15" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>23</v>
-      </c>
-      <c r="X15" t="n">
-        <v>16.8</v>
+        <v>9.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2061,10 +1917,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2073,10 +1929,10 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM15" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -2085,51 +1941,42 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B16" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C16" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D16" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E16" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F16" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X16" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2138,10 +1985,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL16" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2150,10 +1997,10 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM16" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -2162,51 +2009,75 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B17" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C17" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D17" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E17" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>17</v>
+        <v>9.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
         <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,7 +2089,7 @@
         <v>138.94</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2226,11 +2097,17 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM17" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2239,51 +2116,51 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B18" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C18" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E18" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I18" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K18" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N18" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O18" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R18" t="n">
         <v>3.5</v>
@@ -2292,31 +2169,22 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W18" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z18" t="n">
         <v>21</v>
       </c>
-      <c r="X18" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>18</v>
-      </c>
       <c r="AA18" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2325,10 +2193,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2337,16 +2205,16 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS18" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM18" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -2355,84 +2223,75 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B19" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C19" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E19" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H19" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J19" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K19" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O19" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>16.4</v>
+        <v>22.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2441,10 +2300,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2453,102 +2312,93 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM19" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B20" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C20" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D20" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E20" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F20" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H20" t="n">
         <v>25.4</v>
       </c>
       <c r="I20" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J20" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K20" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N20" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O20" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V20" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X20" t="n">
         <v>19.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2557,10 +2407,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2569,102 +2419,93 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM20" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN20" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B21" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C21" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D21" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F21" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H21" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I21" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J21" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O21" t="n">
         <v>38.4</v>
       </c>
-      <c r="K21" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q21" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2673,10 +2514,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2685,102 +2526,66 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM21" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN21" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO21" t="n">
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B22" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C22" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D22" t="n">
         <v>34.5</v>
       </c>
       <c r="E22" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F22" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H22" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K22" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N22" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O22" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W22" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.1</v>
+        <v>36.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2789,10 +2594,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2800,17 +2605,11 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
-      <c r="AP22" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL22" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM22" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
@@ -2819,57 +2618,48 @@
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B23" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C23" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D23" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E23" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
         <v>9.6</v>
       </c>
       <c r="K23" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>13.7</v>
+        <v>34.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="n">
         <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2878,10 +2668,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL23" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2890,69 +2680,87 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM23" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP23" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B24" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C24" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D24" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>38.7</v>
       </c>
       <c r="K24" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>33</v>
       </c>
       <c r="O24" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>10.9</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG24" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2964,7 +2772,7 @@
         <v>128.27</v>
       </c>
       <c r="AL24" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2972,97 +2780,94 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM24" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP24" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B25" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C25" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D25" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F25" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H25" t="n">
         <v>25.1</v>
       </c>
       <c r="I25" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J25" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K25" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O25" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X25" t="n">
-        <v>10.9</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3071,10 +2876,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3083,72 +2888,72 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM25" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP25" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B26" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C26" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D26" t="n">
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F26" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H26" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I26" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O26" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q26" t="n">
         <v>23.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -3156,29 +2961,20 @@
       <c r="T26" t="n">
         <v>23.1</v>
       </c>
-      <c r="V26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3187,10 +2983,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL26" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3199,69 +2995,69 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS26" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM26" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP26" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B27" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C27" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E27" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I27" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J27" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K27" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O27" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
@@ -3270,31 +3066,22 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>15.8</v>
+        <v>22.7</v>
       </c>
       <c r="Y27" t="n">
         <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3303,10 +3090,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3315,102 +3102,93 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS27" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM27" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN27" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP27" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B28" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C28" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D28" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E28" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I28" t="n">
         <v>9.4</v>
       </c>
       <c r="J28" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O28" t="n">
         <v>39.5</v>
       </c>
-      <c r="K28" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q28" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>23</v>
-      </c>
-      <c r="X28" t="n">
-        <v>16.2</v>
+        <v>23.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3419,10 +3197,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3431,102 +3209,66 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS28" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM28" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO28" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP28" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B29" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C29" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D29" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E29" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F29" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y29" t="n">
         <v>8</v>
       </c>
-      <c r="H29" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N29" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X29" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>10</v>
-      </c>
       <c r="Z29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA29" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3535,10 +3277,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3546,76 +3288,61 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM29" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN29" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP29" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B30" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C30" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D30" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E30" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K30" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O30" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="V30" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.4</v>
+        <v>38.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3624,10 +3351,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL30" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3636,69 +3363,87 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM30" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP30" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B31" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C31" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F31" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>36.7</v>
       </c>
       <c r="O31" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="V31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>14.2</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3710,7 +3455,7 @@
         <v>125.11</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3718,97 +3463,94 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>14</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM31" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B32" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C32" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E32" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F32" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H32" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I32" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K32" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O32" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T32" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W32" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>10.6</v>
+        <v>23.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3817,10 +3559,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3829,102 +3571,93 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS32" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM32" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B33" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C33" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E33" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H33" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K33" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O33" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T33" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>10.6</v>
+        <v>22.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF33" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG33" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3933,10 +3666,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3945,102 +3678,93 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM33" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN33" t="n">
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP33" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B34" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C34" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D34" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E34" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H34" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q34" t="n">
         <v>23.7</v>
       </c>
-      <c r="I34" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J34" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>73</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>34</v>
-      </c>
-      <c r="O34" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S34" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T34" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG34" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -4049,10 +3773,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL34" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -4061,102 +3785,93 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM34" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO34" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP34" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B35" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C35" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E35" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F35" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H35" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I35" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>40.8</v>
       </c>
       <c r="K35" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O35" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T35" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X35" t="n">
-        <v>11.4</v>
+        <v>23.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -4165,10 +3880,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -4177,102 +3892,66 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS35" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM35" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN35" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO35" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP35" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B36" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C36" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E36" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H36" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J36" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K36" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O36" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>12.7</v>
+        <v>34.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="n">
         <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF36" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4281,10 +3960,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL36" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4292,76 +3971,61 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM36" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN36" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP36" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B37" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C37" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D37" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E37" t="n">
         <v>29.8</v>
       </c>
       <c r="F37" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K37" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O37" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="V37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X37" t="n">
-        <v>12.6</v>
+        <v>35.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4370,10 +4034,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4382,33 +4046,33 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM37" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN37" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP37" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B38" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C38" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D38" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E38" t="n">
         <v>29.8</v>
@@ -4417,34 +4081,25 @@
         <v>6.6</v>
       </c>
       <c r="K38" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="V38" t="n">
-        <v>8</v>
-      </c>
-      <c r="W38" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>12.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA38" t="n">
         <v>12.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG38" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4453,10 +4108,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL38" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4465,69 +4120,87 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM38" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN38" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO38" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP38" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B39" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C39" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D39" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E39" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F39" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>41.1</v>
       </c>
       <c r="K39" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4</v>
+      </c>
+      <c r="N39" t="n">
+        <v>37.4</v>
       </c>
       <c r="O39" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W39" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X39" t="n">
-        <v>13.2</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y39" t="n">
         <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF39" t="n">
         <v>220</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4539,7 +4212,7 @@
         <v>126.54</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4547,97 +4220,94 @@
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM39" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN39" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO39" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP39" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B40" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C40" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D40" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E40" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F40" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H40" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I40" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K40" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N40" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O40" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X40" t="n">
-        <v>14.1</v>
+        <v>24.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF40" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4646,10 +4316,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4658,102 +4328,93 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS40" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM40" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN40" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO40" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP40" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B41" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C41" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E41" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F41" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I41" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K41" t="n">
         <v>76.5</v>
       </c>
       <c r="M41" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N41" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O41" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R41" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="X41" t="n">
-        <v>15.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG41" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4762,10 +4423,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4774,72 +4435,72 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS41" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM41" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN41" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO41" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B42" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C42" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E42" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H42" t="n">
         <v>26.1</v>
       </c>
       <c r="I42" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J42" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K42" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N42" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O42" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q42" t="n">
         <v>24.2</v>
       </c>
       <c r="R42" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -4847,29 +4508,20 @@
       <c r="T42" t="n">
         <v>24.2</v>
       </c>
-      <c r="V42" t="n">
-        <v>10</v>
-      </c>
-      <c r="W42" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z42" t="n">
         <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4878,10 +4530,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4890,102 +4542,66 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM42" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN42" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO42" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP42" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B43" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C43" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D43" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E43" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J43" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K43" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V43" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W43" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>15.4</v>
+        <v>37.8</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z43" t="n">
         <v>16</v>
       </c>
       <c r="AA43" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF43" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4994,10 +4610,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL43" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -5005,76 +4621,61 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM43" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN43" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO43" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP43" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B44" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C44" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E44" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F44" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K44" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V44" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W44" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16</v>
+        <v>37.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
         <v>16</v>
       </c>
       <c r="AA44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF44" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -5083,10 +4684,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -5095,69 +4696,87 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM44" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN44" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO44" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP44" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B45" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C45" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D45" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E45" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F45" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>41.3</v>
       </c>
       <c r="K45" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>37.1</v>
       </c>
       <c r="O45" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="V45" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W45" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>16.6</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF45" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5169,7 +4788,7 @@
         <v>125.03</v>
       </c>
       <c r="AL45" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5177,97 +4796,94 @@
       <c r="AN45" t="n">
         <v>142</v>
       </c>
+      <c r="AP45" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL45" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM45" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN45" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP45" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B46" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C46" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E46" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F46" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I46" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K46" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M46" t="n">
         <v>2.7</v>
       </c>
       <c r="N46" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O46" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T46" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V46" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>17.4</v>
+        <v>24</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA46" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF46" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5276,10 +4892,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5288,87 +4904,78 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS46" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM46" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN46" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO46" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP46" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B47" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C47" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D47" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E47" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F47" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K47" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O47" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>24</v>
-      </c>
-      <c r="V47" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.5</v>
+        <v>23.9</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -5377,13 +4984,13 @@
         <v>15</v>
       </c>
       <c r="AA47" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5392,10 +4999,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL47" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5404,102 +5011,93 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS47" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM47" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN47" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO47" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP47" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B48" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C48" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D48" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E48" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F48" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I48" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K48" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N48" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O48" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S48" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T48" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V48" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W48" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X48" t="n">
-        <v>17.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z48" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF48" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5508,10 +5106,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL48" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5520,87 +5118,78 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS48" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM48" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN48" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO48" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP48" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B49" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C49" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D49" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E49" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F49" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K49" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M49" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O49" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S49" t="n">
         <v>12</v>
       </c>
       <c r="T49" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V49" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>19.2</v>
+        <v>23.5</v>
       </c>
       <c r="Y49" t="n">
         <v>13</v>
@@ -5609,13 +5198,13 @@
         <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF49" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5624,10 +5213,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL49" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5636,102 +5225,66 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS49" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM49" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN49" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP49" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B50" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C50" t="n">
         <v>57.9</v>
       </c>
       <c r="D50" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E50" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F50" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H50" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I50" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N50" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S50" t="n">
-        <v>12</v>
-      </c>
-      <c r="T50" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V50" t="n">
-        <v>17</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X50" t="n">
-        <v>18.9</v>
+        <v>39</v>
       </c>
       <c r="Y50" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z50" t="n">
         <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5740,10 +5293,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL50" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5751,76 +5304,61 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM50" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN50" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO50" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP50" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B51" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C51" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D51" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E51" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K51" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O51" t="n">
-        <v>39</v>
-      </c>
-      <c r="V51" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.5</v>
+        <v>40.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z51" t="n">
         <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF51" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5829,10 +5367,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5841,69 +5379,87 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM51" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN51" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO51" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP51" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B52" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C52" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D52" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E52" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F52" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J52" t="n">
+        <v>40.6</v>
       </c>
       <c r="K52" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>36</v>
       </c>
       <c r="O52" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="V52" t="n">
-        <v>17</v>
-      </c>
-      <c r="W52" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>19.8</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="T52" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA52" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5915,7 +5471,7 @@
         <v>128.43</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5923,97 +5479,94 @@
       <c r="AN52" t="n">
         <v>142</v>
       </c>
+      <c r="AP52" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL52" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM52" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN52" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO52" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP52" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B53" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C53" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D53" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E53" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F53" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H53" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I53" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K53" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O53" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V53" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W53" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>16.6</v>
+        <v>22.2</v>
       </c>
       <c r="Y53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA53" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF53" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -6022,10 +5575,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -6034,102 +5587,93 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM53" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN53" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO53" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP53" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B54" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C54" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D54" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E54" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F54" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H54" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I54" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K54" t="n">
         <v>75.7</v>
       </c>
       <c r="M54" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N54" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O54" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R54" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T54" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V54" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W54" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>16.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z54" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA54" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6138,10 +5682,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -6150,102 +5694,93 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS54" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM54" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN54" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO54" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP54" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B55" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C55" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D55" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E55" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F55" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H55" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K55" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O55" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R55" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S55" t="n">
         <v>17</v>
       </c>
       <c r="T55" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W55" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>15.4</v>
+        <v>23.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA55" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF55" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6254,10 +5789,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL55" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -6266,93 +5801,93 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS55" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM55" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN55" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO55" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP55" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B56" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C56" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D56" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E56" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H56" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I56" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J56" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K56" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M56" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N56" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O56" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R56" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S56" t="n">
         <v>17</v>
       </c>
       <c r="T56" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y56" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z56" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA56" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG56" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6361,10 +5896,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL56" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -6373,93 +5908,66 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM56" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN56" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO56" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP56" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B57" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C57" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D57" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E57" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F57" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H57" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>41.2</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N57" t="n">
-        <v>35.2</v>
+        <v>96</v>
       </c>
       <c r="O57" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S57" t="n">
-        <v>17</v>
-      </c>
-      <c r="T57" t="n">
-        <v>22.9</v>
+        <v>38.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z57" t="n">
         <v>17</v>
       </c>
       <c r="AA57" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AF57" t="n">
-        <v>218.89</v>
+        <v>222.39</v>
       </c>
       <c r="AG57" t="n">
-        <v>4.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6468,10 +5976,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6479,61 +5987,61 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BM57" t="n">
-        <v>42.16</v>
+        <v>40.4</v>
       </c>
       <c r="BN57" t="n">
-        <v>705.1</v>
+        <v>1138.8</v>
       </c>
       <c r="BO57" t="n">
-        <v>1122.7</v>
+        <v>491.3</v>
       </c>
       <c r="BP57" t="n">
-        <v>2933.3</v>
+        <v>2986.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B58" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C58" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E58" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
       </c>
+      <c r="K58" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>39.5</v>
+      </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>222.39</v>
+        <v>221.63</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6542,10 +6050,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6554,42 +6062,60 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>745.5</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>2960.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B59" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C59" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E59" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>5.3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>39.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>221.63</v>
+        <v>222.64</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6598,10 +6124,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>129.31</v>
+        <v>130.65</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6610,42 +6136,87 @@
         <v>142</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>757.1</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>3027.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B60" t="n">
-        <v>151.5</v>
+        <v>172</v>
       </c>
       <c r="C60" t="n">
-        <v>72.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D60" t="n">
-        <v>30.9</v>
+        <v>29.9</v>
       </c>
       <c r="E60" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="F60" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>11</v>
+      </c>
+      <c r="J60" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K60" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N60" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>17</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA60" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AF60" t="n">
-        <v>222.64</v>
+        <v>222.6</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6657,7 +6228,7 @@
         <v>130.65</v>
       </c>
       <c r="AL60" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6665,43 +6236,61 @@
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>14.74</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>252.8</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>3172.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B61" t="n">
-        <v>152</v>
+        <v>156.5</v>
       </c>
       <c r="C61" t="n">
-        <v>72.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="D61" t="n">
-        <v>31.5</v>
+        <v>32.3</v>
       </c>
       <c r="E61" t="n">
-        <v>32.9</v>
+        <v>38.3</v>
       </c>
       <c r="F61" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Z61" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA61" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="AF61" t="n">
-        <v>224.59</v>
+        <v>222.54</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.94</v>
+        <v>-2.05</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6710,10 +6299,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>131.48</v>
+        <v>126.17</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.83</v>
+        <v>-4.48</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6722,36 +6311,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B62" t="n">
-        <v>156.5</v>
+        <v>158.2</v>
       </c>
       <c r="C62" t="n">
-        <v>70</v>
+        <v>75.3</v>
       </c>
       <c r="D62" t="n">
-        <v>32.3</v>
+        <v>31.4</v>
       </c>
       <c r="E62" t="n">
-        <v>38.3</v>
+        <v>34.5</v>
       </c>
       <c r="F62" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z62" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA62" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6766,7 +6355,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,26 +628,41 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B2" t="n">
-        <v>116.3</v>
+        <v>112.71</v>
       </c>
       <c r="C2" t="n">
-        <v>25.23</v>
+        <v>25.48</v>
       </c>
       <c r="D2" t="n">
-        <v>37.18</v>
+        <v>37.35</v>
       </c>
       <c r="E2" t="n">
-        <v>32.98</v>
+        <v>28.98</v>
       </c>
       <c r="F2" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.1</v>
       </c>
       <c r="K2" t="n">
         <v>62.9</v>
       </c>
+      <c r="M2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29.9</v>
+      </c>
       <c r="O2" t="n">
         <v>31.8</v>
       </c>
@@ -664,19 +679,19 @@
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>216.08</v>
+        <v>216.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -684,6 +699,9 @@
       <c r="AI2" t="n">
         <v>235</v>
       </c>
+      <c r="AK2" t="n">
+        <v>133.15</v>
+      </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
@@ -697,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="BM2" t="n">
-        <v>39.75</v>
+        <v>38.59</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
@@ -714,46 +732,46 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B3" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C3" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D3" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E3" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F3" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H3" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M3" t="n">
         <v>1.9</v>
       </c>
       <c r="N3" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -762,22 +780,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA3" t="n">
         <v>16</v>
       </c>
-      <c r="Z3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>19</v>
-      </c>
       <c r="AF3" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -786,7 +804,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.18</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -801,13 +822,13 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM3" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -818,43 +839,43 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B4" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C4" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D4" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E4" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M4" t="n">
         <v>1.9</v>
       </c>
       <c r="N4" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O4" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -869,19 +890,19 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF4" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -890,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -908,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM4" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN4" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -925,70 +946,70 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B5" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C5" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D5" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E5" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H5" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K5" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O5" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -997,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1009,19 +1030,19 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM5" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1032,46 +1053,46 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B6" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C6" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D6" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E6" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F6" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H6" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K6" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N6" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O6" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R6" t="n">
         <v>0.6</v>
@@ -1080,22 +1101,22 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1104,10 +1125,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL6" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1116,19 +1137,19 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS6" t="n">
         <v>13.07</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM6" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN6" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
@@ -1139,70 +1160,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B7" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C7" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D7" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E7" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O7" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF7" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1210,35 +1204,23 @@
       <c r="AI7" t="n">
         <v>235</v>
       </c>
-      <c r="AK7" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM7" t="n">
         <v>110</v>
       </c>
       <c r="AN7" t="n">
         <v>142</v>
       </c>
-      <c r="AP7" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL7" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM7" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP7" t="n">
         <v>0</v>
@@ -1246,43 +1228,43 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B8" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C8" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D8" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E8" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1297,60 +1279,87 @@
         <v>142</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM8" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B9" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C9" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D9" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E9" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.6</v>
       </c>
       <c r="K9" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>34</v>
       </c>
       <c r="O9" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1358,17 +1367,29 @@
       <c r="AI9" t="n">
         <v>235</v>
       </c>
+      <c r="AK9" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM9" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -1377,75 +1398,75 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B10" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C10" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E10" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F10" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I10" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K10" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O10" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1454,10 +1475,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1466,16 +1487,16 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM10" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -1484,30 +1505,30 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B11" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D11" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E11" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F11" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H11" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I11" t="n">
         <v>9.800000000000001</v>
@@ -1516,43 +1537,43 @@
         <v>38.6</v>
       </c>
       <c r="K11" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O11" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1561,10 +1582,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1573,93 +1594,93 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM11" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B12" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C12" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D12" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N12" t="n">
         <v>35.2</v>
       </c>
-      <c r="E12" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J12" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O12" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF12" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1668,10 +1689,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL12" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1680,93 +1701,60 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM12" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B13" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C13" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D13" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E13" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>21</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
         <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1775,10 +1763,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1786,61 +1774,55 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM13" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B14" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C14" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D14" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF14" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1849,10 +1831,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1861,10 +1843,10 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM14" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -1873,42 +1855,42 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B15" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C15" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D15" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E15" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F15" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y15" t="n">
         <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG15" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1917,10 +1899,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL15" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1929,10 +1911,10 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM15" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -1941,42 +1923,75 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B16" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C16" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D16" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E16" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F16" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z16" t="n">
         <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -1988,7 +2003,7 @@
         <v>138.94</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -1996,11 +2011,17 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM16" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -2009,51 +2030,51 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B17" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C17" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D17" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E17" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I17" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O17" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R17" t="n">
         <v>3.5</v>
@@ -2062,22 +2083,22 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2086,10 +2107,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2098,16 +2119,16 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS17" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM17" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -2116,75 +2137,75 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B18" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C18" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E18" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H18" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J18" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K18" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O18" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF18" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2193,10 +2214,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2205,93 +2226,93 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM18" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B19" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D19" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E19" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F19" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H19" t="n">
         <v>25.4</v>
       </c>
       <c r="I19" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J19" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K19" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N19" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O19" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2300,10 +2321,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2312,93 +2333,93 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM19" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN19" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B20" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C20" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D20" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E20" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F20" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H20" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I20" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J20" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O20" t="n">
         <v>38.4</v>
       </c>
-      <c r="K20" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q20" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG20" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2407,10 +2428,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2419,93 +2440,66 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM20" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN20" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B21" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C21" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D21" t="n">
         <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F21" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K21" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O21" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF21" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2514,10 +2508,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2525,17 +2519,11 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM21" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
@@ -2544,48 +2532,48 @@
         <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B22" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C22" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D22" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E22" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F22" t="n">
         <v>9.6</v>
       </c>
       <c r="K22" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
         <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2594,10 +2582,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL22" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2606,60 +2594,87 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM22" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP22" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B23" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C23" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D23" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F23" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>38.7</v>
       </c>
       <c r="K23" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>33</v>
       </c>
       <c r="O23" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG23" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2671,7 +2686,7 @@
         <v>128.27</v>
       </c>
       <c r="AL23" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2679,88 +2694,94 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM23" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
       </c>
       <c r="BO23" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP23" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B24" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C24" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D24" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F24" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H24" t="n">
         <v>25.1</v>
       </c>
       <c r="I24" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J24" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K24" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O24" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2769,10 +2790,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2781,72 +2802,72 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM24" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN24" t="n">
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP24" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B25" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C25" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D25" t="n">
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F25" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H25" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K25" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O25" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q25" t="n">
         <v>23.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2855,19 +2876,19 @@
         <v>23.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2876,10 +2897,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL25" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2888,69 +2909,69 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM25" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP25" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B26" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C26" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E26" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F26" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I26" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J26" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K26" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O26" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R26" t="n">
         <v>1.3</v>
@@ -2959,22 +2980,22 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y26" t="n">
         <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2983,10 +3004,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2995,93 +3016,93 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS26" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM26" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN26" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP26" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B27" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C27" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D27" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E27" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I27" t="n">
         <v>9.4</v>
       </c>
       <c r="J27" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O27" t="n">
         <v>39.5</v>
       </c>
-      <c r="K27" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q27" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3090,10 +3111,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3102,93 +3123,66 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM27" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO27" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP27" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B28" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C28" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D28" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E28" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y28" t="n">
         <v>8</v>
       </c>
-      <c r="H28" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10</v>
-      </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3197,10 +3191,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3208,67 +3202,61 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM28" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN28" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP28" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B29" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C29" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D29" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K29" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O29" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3277,10 +3265,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL29" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3289,60 +3277,87 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM29" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP29" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B30" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C30" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F30" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J30" t="n">
+        <v>40</v>
       </c>
       <c r="K30" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>36.7</v>
       </c>
       <c r="O30" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3354,7 +3369,7 @@
         <v>125.11</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3362,88 +3377,94 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>14</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM30" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP30" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B31" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C31" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E31" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F31" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H31" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O31" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T31" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3452,10 +3473,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3464,93 +3485,93 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS31" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM31" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B32" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C32" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E32" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F32" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K32" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O32" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T32" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG32" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3559,10 +3580,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3571,93 +3592,93 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM32" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP32" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B33" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C33" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D33" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E33" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F33" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H33" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q33" t="n">
         <v>23.7</v>
       </c>
-      <c r="I33" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J33" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K33" t="n">
-        <v>73</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>34</v>
-      </c>
-      <c r="O33" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T33" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG33" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3666,10 +3687,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL33" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3678,93 +3699,93 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS33" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM33" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO33" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP33" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B34" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C34" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E34" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F34" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I34" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>40.8</v>
       </c>
       <c r="K34" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O34" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T34" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3773,10 +3794,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3785,93 +3806,66 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS34" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM34" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN34" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO34" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP34" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B35" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C35" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E35" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H35" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J35" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K35" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O35" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35" t="n">
         <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF35" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3880,10 +3874,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3891,67 +3885,61 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM35" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN35" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO35" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP35" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B36" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C36" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D36" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E36" t="n">
         <v>29.8</v>
       </c>
       <c r="F36" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K36" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O36" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3960,10 +3948,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3972,33 +3960,33 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM36" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN36" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP36" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B37" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C37" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D37" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E37" t="n">
         <v>29.8</v>
@@ -4007,25 +3995,25 @@
         <v>6.6</v>
       </c>
       <c r="K37" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA37" t="n">
         <v>12.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4034,10 +4022,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL37" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4046,60 +4034,87 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM37" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN37" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO37" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP37" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B38" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C38" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D38" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E38" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>41.1</v>
       </c>
       <c r="K38" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>37.4</v>
       </c>
       <c r="O38" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y38" t="n">
         <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF38" t="n">
         <v>220</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4111,7 +4126,7 @@
         <v>126.54</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4119,88 +4134,94 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM38" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN38" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO38" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP38" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B39" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C39" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D39" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E39" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F39" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H39" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I39" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K39" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N39" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O39" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4209,10 +4230,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4221,93 +4242,93 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS39" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM39" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN39" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO39" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP39" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B40" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C40" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E40" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F40" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I40" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K40" t="n">
         <v>76.5</v>
       </c>
       <c r="M40" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N40" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O40" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z40" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG40" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4316,10 +4337,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4328,72 +4349,72 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS40" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM40" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN40" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO40" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP40" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B41" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C41" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D41" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E41" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H41" t="n">
         <v>26.1</v>
       </c>
       <c r="I41" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J41" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K41" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N41" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O41" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q41" t="n">
         <v>24.2</v>
       </c>
       <c r="R41" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -4402,19 +4423,19 @@
         <v>24.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z41" t="n">
         <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4423,10 +4444,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4435,93 +4456,66 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM41" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN41" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO41" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP41" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B42" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C42" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D42" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E42" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H42" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J42" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K42" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z42" t="n">
         <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF42" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4530,10 +4524,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL42" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4541,67 +4535,61 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM42" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN42" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP42" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B43" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C43" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D43" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E43" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F43" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K43" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="Y43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
         <v>16</v>
       </c>
       <c r="AA43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF43" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4610,10 +4598,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4622,60 +4610,87 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM43" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN43" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO43" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP43" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B44" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C44" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D44" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E44" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F44" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>41.3</v>
       </c>
       <c r="K44" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>37.1</v>
       </c>
       <c r="O44" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF44" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4687,7 +4702,7 @@
         <v>125.03</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4695,88 +4710,94 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM44" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN44" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO44" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP44" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B45" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C45" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E45" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F45" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I45" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K45" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M45" t="n">
         <v>2.7</v>
       </c>
       <c r="N45" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O45" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R45" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T45" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA45" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF45" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4785,10 +4806,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4797,78 +4818,78 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM45" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN45" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO45" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP45" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B46" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C46" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E46" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F46" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I46" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K46" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O46" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>16</v>
       </c>
       <c r="T46" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y46" t="n">
         <v>10</v>
@@ -4877,13 +4898,13 @@
         <v>15</v>
       </c>
       <c r="AA46" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4892,10 +4913,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL46" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4904,93 +4925,93 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS46" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM46" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN46" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO46" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP46" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B47" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C47" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D47" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E47" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F47" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H47" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I47" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K47" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N47" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O47" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T47" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z47" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF47" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -4999,10 +5020,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL47" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5011,78 +5032,78 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS47" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM47" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN47" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO47" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP47" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B48" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C48" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D48" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E48" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F48" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H48" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I48" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J48" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K48" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M48" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O48" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S48" t="n">
         <v>12</v>
       </c>
       <c r="T48" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y48" t="n">
         <v>13</v>
@@ -5091,13 +5112,13 @@
         <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF48" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5106,10 +5127,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL48" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5118,93 +5139,66 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM48" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN48" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO48" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP48" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B49" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C49" t="n">
         <v>57.9</v>
       </c>
       <c r="D49" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E49" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F49" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H49" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I49" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J49" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S49" t="n">
-        <v>12</v>
-      </c>
-      <c r="T49" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="Y49" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z49" t="n">
         <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5213,10 +5207,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL49" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5224,67 +5218,61 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM49" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN49" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO49" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP49" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B50" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C50" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D50" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E50" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K50" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O50" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z50" t="n">
         <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF50" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5293,10 +5281,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5305,60 +5293,87 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM50" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN50" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO50" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP50" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B51" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C51" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D51" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E51" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F51" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J51" t="n">
+        <v>40.6</v>
       </c>
       <c r="K51" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N51" t="n">
+        <v>36</v>
       </c>
       <c r="O51" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>11</v>
+      </c>
+      <c r="T51" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z51" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA51" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF51" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5370,7 +5385,7 @@
         <v>128.43</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5378,88 +5393,94 @@
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM51" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN51" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO51" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP51" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B52" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C52" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D52" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E52" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F52" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H52" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K52" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N52" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O52" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T52" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA52" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF52" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5468,10 +5489,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5480,93 +5501,93 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM52" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN52" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO52" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP52" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B53" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C53" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D53" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E53" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F53" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H53" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I53" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K53" t="n">
         <v>75.7</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N53" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O53" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R53" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T53" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA53" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5575,10 +5596,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5587,93 +5608,93 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS53" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM53" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN53" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO53" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP53" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B54" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C54" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D54" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E54" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F54" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H54" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K54" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N54" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O54" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S54" t="n">
         <v>17</v>
       </c>
       <c r="T54" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z54" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA54" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF54" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5682,10 +5703,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL54" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5694,93 +5715,93 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS54" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM54" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN54" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO54" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP54" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B55" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C55" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D55" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E55" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H55" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I55" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J55" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K55" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M55" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N55" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O55" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R55" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S55" t="n">
         <v>17</v>
       </c>
       <c r="T55" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG55" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5789,10 +5810,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL55" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5801,93 +5822,66 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM55" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN55" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO55" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP55" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B56" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C56" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D56" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E56" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F56" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H56" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J56" t="n">
-        <v>41.2</v>
+        <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N56" t="n">
-        <v>35.2</v>
+        <v>96</v>
       </c>
       <c r="O56" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S56" t="n">
-        <v>17</v>
-      </c>
-      <c r="T56" t="n">
-        <v>22.9</v>
+        <v>38.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
         <v>17</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AF56" t="n">
-        <v>218.89</v>
+        <v>222.39</v>
       </c>
       <c r="AG56" t="n">
-        <v>4.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5896,10 +5890,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5907,67 +5901,61 @@
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BM56" t="n">
-        <v>42.16</v>
+        <v>40.4</v>
       </c>
       <c r="BN56" t="n">
-        <v>705.1</v>
+        <v>1138.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>1122.7</v>
+        <v>491.3</v>
       </c>
       <c r="BP56" t="n">
-        <v>2933.3</v>
+        <v>2986.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B57" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C57" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E57" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="O57" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z57" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>222.39</v>
+        <v>221.63</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5976,10 +5964,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5988,60 +5976,60 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="BM57" t="n">
-        <v>40.4</v>
+        <v>40.92</v>
       </c>
       <c r="BN57" t="n">
-        <v>1138.8</v>
+        <v>66.8</v>
       </c>
       <c r="BO57" t="n">
-        <v>491.3</v>
+        <v>745.5</v>
       </c>
       <c r="BP57" t="n">
-        <v>2986.4</v>
+        <v>2960.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B58" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C58" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E58" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K58" t="n">
-        <v>98.2</v>
+        <v>100.1</v>
       </c>
       <c r="O58" t="n">
         <v>39.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA58" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>221.63</v>
+        <v>222.64</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6050,10 +6038,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>129.31</v>
+        <v>130.65</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6062,60 +6050,87 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="BM58" t="n">
-        <v>40.92</v>
+        <v>39.77</v>
       </c>
       <c r="BN58" t="n">
-        <v>66.8</v>
+        <v>63.8</v>
       </c>
       <c r="BO58" t="n">
-        <v>745.5</v>
+        <v>757.1</v>
       </c>
       <c r="BP58" t="n">
-        <v>2960.5</v>
+        <v>3027.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B59" t="n">
-        <v>151.5</v>
+        <v>172</v>
       </c>
       <c r="C59" t="n">
-        <v>72.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D59" t="n">
-        <v>30.9</v>
+        <v>29.9</v>
       </c>
       <c r="E59" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="F59" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>11</v>
+      </c>
+      <c r="J59" t="n">
+        <v>40.6</v>
       </c>
       <c r="K59" t="n">
-        <v>100.1</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N59" t="n">
+        <v>36.9</v>
       </c>
       <c r="O59" t="n">
-        <v>39.5</v>
+        <v>40.4</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>17</v>
+      </c>
+      <c r="T59" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA59" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AF59" t="n">
-        <v>222.64</v>
+        <v>222.6</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6127,7 +6142,7 @@
         <v>130.65</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6135,88 +6150,94 @@
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>14.74</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="BM59" t="n">
-        <v>39.77</v>
+        <v>40.76</v>
       </c>
       <c r="BN59" t="n">
-        <v>63.8</v>
+        <v>252.8</v>
       </c>
       <c r="BO59" t="n">
-        <v>757.1</v>
+        <v>1156.4</v>
       </c>
       <c r="BP59" t="n">
-        <v>3027.1</v>
+        <v>3172.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B60" t="n">
-        <v>172</v>
+        <v>181.5</v>
       </c>
       <c r="C60" t="n">
-        <v>75.7</v>
+        <v>73.7</v>
       </c>
       <c r="D60" t="n">
-        <v>29.9</v>
+        <v>31.9</v>
       </c>
       <c r="E60" t="n">
-        <v>34.3</v>
+        <v>38</v>
       </c>
       <c r="F60" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="H60" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="I60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="K60" t="n">
-        <v>75.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>36.9</v>
+        <v>35.9</v>
       </c>
       <c r="O60" t="n">
-        <v>40.4</v>
+        <v>39.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="R60" t="n">
         <v>1</v>
       </c>
       <c r="S60" t="n">
+        <v>18</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z60" t="n">
         <v>17</v>
       </c>
-      <c r="T60" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>15</v>
-      </c>
       <c r="AA60" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AF60" t="n">
-        <v>222.6</v>
+        <v>224.57</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.94</v>
+        <v>-2.05</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6225,10 +6246,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>130.65</v>
+        <v>131.48</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6237,60 +6258,60 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>84.98999999999999</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="AS60" t="n">
-        <v>14.74</v>
+        <v>14.47</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="BM60" t="n">
-        <v>40.76</v>
+        <v>43.17</v>
       </c>
       <c r="BN60" t="n">
-        <v>252.8</v>
+        <v>2456.2</v>
       </c>
       <c r="BO60" t="n">
-        <v>1156.4</v>
+        <v>1075.8</v>
       </c>
       <c r="BP60" t="n">
-        <v>3172.7</v>
+        <v>3051.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B61" t="n">
-        <v>156.5</v>
+        <v>158.2</v>
       </c>
       <c r="C61" t="n">
-        <v>70</v>
+        <v>75.3</v>
       </c>
       <c r="D61" t="n">
-        <v>32.3</v>
+        <v>31.4</v>
       </c>
       <c r="E61" t="n">
-        <v>38.3</v>
+        <v>34.5</v>
       </c>
       <c r="F61" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z61" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA61" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF61" t="n">
-        <v>222.54</v>
+        <v>221.34</v>
       </c>
       <c r="AG61" t="n">
-        <v>-2.05</v>
+        <v>-1.2</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6299,10 +6320,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>126.17</v>
+        <v>123.51</v>
       </c>
       <c r="AL61" t="n">
-        <v>-4.48</v>
+        <v>-7.97</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6311,36 +6332,48 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>4128.6</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>1204.7</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>3187</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B62" t="n">
-        <v>158.2</v>
+        <v>146.2</v>
       </c>
       <c r="C62" t="n">
-        <v>75.3</v>
+        <v>69.3</v>
       </c>
       <c r="D62" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="E62" t="n">
-        <v>34.5</v>
+        <v>31.3</v>
       </c>
       <c r="F62" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="Y62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6355,7 +6388,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,46 +628,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B2" t="n">
-        <v>112.71</v>
+        <v>143.9</v>
       </c>
       <c r="C2" t="n">
-        <v>25.48</v>
+        <v>32.1</v>
       </c>
       <c r="D2" t="n">
-        <v>37.35</v>
+        <v>39.5</v>
       </c>
       <c r="E2" t="n">
-        <v>28.98</v>
+        <v>40.5</v>
       </c>
       <c r="F2" t="n">
-        <v>10.89</v>
+        <v>5.9</v>
       </c>
       <c r="H2" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="I2" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>62.9</v>
+        <v>70.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="O2" t="n">
-        <v>31.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -676,22 +676,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA2" t="n">
         <v>16</v>
       </c>
-      <c r="Z2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>19</v>
-      </c>
       <c r="AF2" t="n">
-        <v>216.1</v>
+        <v>217.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.73</v>
+        <v>-4.81</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -700,7 +700,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>133.15</v>
+        <v>137.33</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -715,13 +715,13 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BM2" t="n">
-        <v>38.59</v>
+        <v>43.16</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>212.4</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -732,43 +732,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B3" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D3" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E3" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M3" t="n">
         <v>1.9</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O3" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -783,19 +783,19 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -804,10 +804,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.18</v>
+        <v>-3.13</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -822,13 +822,13 @@
         <v>0</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM3" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN3" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -839,70 +839,70 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B4" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C4" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D4" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E4" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H4" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K4" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N4" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O4" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -911,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -923,19 +923,19 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM4" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -946,46 +946,46 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B5" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C5" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D5" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E5" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H5" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K5" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N5" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O5" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R5" t="n">
         <v>0.6</v>
@@ -994,22 +994,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y5" t="n">
         <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1018,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1030,19 +1030,19 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS5" t="n">
         <v>13.07</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM5" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN5" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1053,70 +1053,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B6" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D6" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E6" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O6" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1124,35 +1097,23 @@
       <c r="AI6" t="n">
         <v>235</v>
       </c>
-      <c r="AK6" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM6" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP6" t="n">
         <v>0</v>
@@ -1160,43 +1121,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B7" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D7" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E7" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,60 +1172,87 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM7" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B8" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C8" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D8" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E8" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.6</v>
       </c>
       <c r="K8" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>34</v>
       </c>
       <c r="O8" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1272,17 +1260,29 @@
       <c r="AI8" t="n">
         <v>235</v>
       </c>
+      <c r="AK8" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
         <v>142</v>
       </c>
+      <c r="AP8" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL8" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM8" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
@@ -1291,75 +1291,75 @@
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B9" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C9" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E9" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F9" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I9" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K9" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O9" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1368,10 +1368,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1380,16 +1380,16 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM9" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -1398,30 +1398,30 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B10" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D10" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E10" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H10" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I10" t="n">
         <v>9.800000000000001</v>
@@ -1430,43 +1430,43 @@
         <v>38.6</v>
       </c>
       <c r="K10" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O10" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1475,10 +1475,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1487,93 +1487,93 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM10" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B11" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C11" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D11" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N11" t="n">
         <v>35.2</v>
       </c>
-      <c r="E11" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O11" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AF11" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1582,10 +1582,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL11" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1594,93 +1594,60 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM11" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B12" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C12" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D12" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E12" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>21</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
         <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1689,10 +1656,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1700,61 +1667,55 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM12" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN12" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B13" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C13" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D13" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1763,10 +1724,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1775,10 +1736,10 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM13" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -1787,42 +1748,42 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B14" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C14" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D14" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E14" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F14" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1831,10 +1792,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL14" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1843,10 +1804,10 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM14" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -1855,42 +1816,75 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B15" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C15" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D15" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E15" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F15" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
         <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1902,7 +1896,7 @@
         <v>138.94</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1910,11 +1904,17 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM15" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -1923,51 +1923,51 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B16" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C16" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D16" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E16" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I16" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O16" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R16" t="n">
         <v>3.5</v>
@@ -1976,22 +1976,22 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2000,10 +2000,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2012,16 +2012,16 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS16" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM16" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -2030,75 +2030,75 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B17" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C17" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E17" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H17" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J17" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K17" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N17" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O17" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2107,10 +2107,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2119,93 +2119,93 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM17" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO17" t="n">
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B18" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D18" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E18" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F18" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H18" t="n">
         <v>25.4</v>
       </c>
       <c r="I18" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J18" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K18" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N18" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O18" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2214,10 +2214,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2226,93 +2226,93 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS18" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM18" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN18" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B19" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C19" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D19" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E19" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F19" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H19" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I19" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J19" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O19" t="n">
         <v>38.4</v>
       </c>
-      <c r="K19" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q19" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2321,10 +2321,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2333,93 +2333,66 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM19" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN19" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B20" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C20" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D20" t="n">
         <v>34.5</v>
       </c>
       <c r="E20" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H20" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K20" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N20" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O20" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2428,10 +2401,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2439,17 +2412,11 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM20" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -2458,48 +2425,48 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B21" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C21" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D21" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E21" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
         <v>9.6</v>
       </c>
       <c r="K21" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
         <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG21" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2508,10 +2475,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL21" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2520,60 +2487,87 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM21" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B22" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C22" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D22" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>38.7</v>
       </c>
       <c r="K22" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>33</v>
       </c>
       <c r="O22" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG22" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2585,7 +2579,7 @@
         <v>128.27</v>
       </c>
       <c r="AL22" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2593,88 +2587,94 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM22" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP22" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B23" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C23" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D23" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F23" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H23" t="n">
         <v>25.1</v>
       </c>
       <c r="I23" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K23" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O23" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2683,10 +2683,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2695,72 +2695,72 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM23" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
       </c>
       <c r="BO23" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP23" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B24" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C24" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D24" t="n">
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I24" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K24" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O24" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q24" t="n">
         <v>23.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2769,19 +2769,19 @@
         <v>23.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2790,10 +2790,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL24" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2802,69 +2802,69 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM24" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP24" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B25" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C25" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F25" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I25" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J25" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K25" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O25" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R25" t="n">
         <v>1.3</v>
@@ -2873,22 +2873,22 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2897,10 +2897,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2909,93 +2909,93 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM25" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN25" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP25" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B26" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C26" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D26" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E26" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I26" t="n">
         <v>9.4</v>
       </c>
       <c r="J26" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O26" t="n">
         <v>39.5</v>
       </c>
-      <c r="K26" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q26" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA26" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3004,10 +3004,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3016,93 +3016,66 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM26" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO26" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP26" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B27" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C27" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D27" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E27" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y27" t="n">
         <v>8</v>
       </c>
-      <c r="H27" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K27" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N27" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10</v>
-      </c>
       <c r="Z27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3111,10 +3084,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3122,67 +3095,61 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM27" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN27" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP27" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B28" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C28" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D28" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E28" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K28" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O28" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3191,10 +3158,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL28" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3203,60 +3170,87 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM28" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP28" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B29" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C29" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F29" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>36.7</v>
       </c>
       <c r="O29" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3268,7 +3262,7 @@
         <v>125.11</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3276,88 +3270,94 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>14</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM29" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP29" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B30" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C30" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E30" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F30" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H30" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K30" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O30" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T30" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3366,10 +3366,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3378,93 +3378,93 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS30" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM30" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP30" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B31" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C31" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E31" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F31" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H31" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K31" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O31" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T31" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3473,10 +3473,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3485,93 +3485,93 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM31" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN31" t="n">
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP31" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B32" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C32" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D32" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E32" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F32" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q32" t="n">
         <v>23.7</v>
       </c>
-      <c r="I32" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J32" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K32" t="n">
-        <v>73</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>34</v>
-      </c>
-      <c r="O32" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T32" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG32" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3580,10 +3580,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL32" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3592,93 +3592,93 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM32" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO32" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B33" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C33" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E33" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F33" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H33" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I33" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>40.8</v>
       </c>
       <c r="K33" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O33" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T33" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3687,10 +3687,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3699,93 +3699,66 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM33" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN33" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO33" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B34" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C34" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E34" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H34" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J34" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K34" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O34" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34" t="n">
         <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AF34" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3794,10 +3767,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3805,67 +3778,61 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM34" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN34" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO34" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP34" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B35" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C35" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D35" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E35" t="n">
         <v>29.8</v>
       </c>
       <c r="F35" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K35" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O35" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3874,10 +3841,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL35" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3886,33 +3853,33 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM35" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN35" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO35" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP35" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B36" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C36" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D36" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E36" t="n">
         <v>29.8</v>
@@ -3921,25 +3888,25 @@
         <v>6.6</v>
       </c>
       <c r="K36" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA36" t="n">
         <v>12.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3948,10 +3915,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL36" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3960,60 +3927,87 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM36" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN36" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO36" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP36" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B37" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C37" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D37" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E37" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F37" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41.1</v>
       </c>
       <c r="K37" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>37.4</v>
       </c>
       <c r="O37" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="AF37" t="n">
         <v>220</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4025,7 +4019,7 @@
         <v>126.54</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4033,88 +4027,94 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM37" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN37" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO37" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP37" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B38" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C38" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D38" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E38" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F38" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H38" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I38" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K38" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N38" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O38" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4123,10 +4123,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4135,93 +4135,93 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS38" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM38" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN38" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO38" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP38" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B39" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C39" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E39" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F39" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H39" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I39" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K39" t="n">
         <v>76.5</v>
       </c>
       <c r="M39" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N39" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O39" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R39" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG39" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4230,10 +4230,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4242,72 +4242,72 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS39" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM39" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN39" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO39" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP39" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B40" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C40" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E40" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H40" t="n">
         <v>26.1</v>
       </c>
       <c r="I40" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J40" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K40" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N40" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O40" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q40" t="n">
         <v>24.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -4316,19 +4316,19 @@
         <v>24.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
         <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4337,10 +4337,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4349,93 +4349,66 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM40" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN40" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO40" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP40" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B41" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C41" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D41" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E41" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H41" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J41" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K41" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z41" t="n">
         <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AF41" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4444,10 +4417,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL41" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4455,67 +4428,61 @@
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM41" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN41" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP41" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B42" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C42" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E42" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F42" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K42" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
         <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF42" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4524,10 +4491,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4536,60 +4503,87 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM42" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN42" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP42" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B43" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C43" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D43" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E43" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F43" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>41.3</v>
       </c>
       <c r="K43" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>37.1</v>
       </c>
       <c r="O43" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF43" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4601,7 +4595,7 @@
         <v>125.03</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4609,88 +4603,94 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM43" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN43" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO43" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP43" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B44" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C44" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E44" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F44" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K44" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M44" t="n">
         <v>2.7</v>
       </c>
       <c r="N44" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O44" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R44" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T44" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AF44" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4699,10 +4699,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4711,78 +4711,78 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM44" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN44" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO44" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP44" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B45" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C45" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D45" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E45" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F45" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I45" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K45" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O45" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>16</v>
       </c>
       <c r="T45" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y45" t="n">
         <v>10</v>
@@ -4791,13 +4791,13 @@
         <v>15</v>
       </c>
       <c r="AA45" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="AF45" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4806,10 +4806,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL45" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4818,93 +4818,93 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM45" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN45" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO45" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP45" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B46" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C46" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D46" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E46" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F46" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H46" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I46" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K46" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N46" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O46" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S46" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T46" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z46" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AF46" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4913,10 +4913,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL46" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4925,78 +4925,78 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS46" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM46" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN46" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO46" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP46" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B47" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C47" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D47" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E47" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F47" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H47" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J47" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K47" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M47" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O47" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S47" t="n">
         <v>12</v>
       </c>
       <c r="T47" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y47" t="n">
         <v>13</v>
@@ -5005,13 +5005,13 @@
         <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>14</v>
+        <v>15.3</v>
       </c>
       <c r="AF47" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5020,10 +5020,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL47" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5032,93 +5032,66 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM47" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN47" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO47" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP47" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B48" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C48" t="n">
         <v>57.9</v>
       </c>
       <c r="D48" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E48" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H48" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N48" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S48" t="n">
-        <v>12</v>
-      </c>
-      <c r="T48" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="Y48" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z48" t="n">
         <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="AF48" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5127,10 +5100,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL48" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5138,67 +5111,61 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM48" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN48" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO48" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP48" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B49" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C49" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D49" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E49" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K49" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O49" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z49" t="n">
         <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF49" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5207,10 +5174,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5219,60 +5186,87 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM49" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN49" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO49" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP49" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B50" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C50" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D50" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E50" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F50" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J50" t="n">
+        <v>40.6</v>
       </c>
       <c r="K50" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N50" t="n">
+        <v>36</v>
       </c>
       <c r="O50" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>11</v>
+      </c>
+      <c r="T50" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5284,7 +5278,7 @@
         <v>128.43</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5292,88 +5286,94 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM50" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN50" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO50" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP50" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B51" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C51" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D51" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E51" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F51" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H51" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I51" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K51" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N51" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O51" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA51" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="AF51" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5382,10 +5382,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5394,93 +5394,93 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM51" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN51" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO51" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP51" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B52" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C52" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D52" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E52" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F52" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H52" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I52" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K52" t="n">
         <v>75.7</v>
       </c>
       <c r="M52" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O52" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T52" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA52" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5489,10 +5489,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5501,93 +5501,93 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS52" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM52" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN52" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO52" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP52" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B53" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C53" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D53" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E53" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F53" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K53" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O53" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R53" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S53" t="n">
         <v>17</v>
       </c>
       <c r="T53" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA53" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="AF53" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5596,10 +5596,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL53" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5608,93 +5608,93 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS53" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM53" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN53" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO53" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP53" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B54" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C54" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D54" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E54" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H54" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I54" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J54" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K54" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N54" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O54" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R54" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S54" t="n">
         <v>17</v>
       </c>
       <c r="T54" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y54" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG54" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5703,10 +5703,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL54" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5715,93 +5715,66 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS54" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM54" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN54" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO54" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP54" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B55" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C55" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D55" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E55" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F55" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H55" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J55" t="n">
-        <v>41.2</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N55" t="n">
-        <v>35.2</v>
+        <v>96</v>
       </c>
       <c r="O55" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S55" t="n">
-        <v>17</v>
-      </c>
-      <c r="T55" t="n">
-        <v>22.9</v>
+        <v>38.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z55" t="n">
         <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AF55" t="n">
-        <v>218.89</v>
+        <v>222.39</v>
       </c>
       <c r="AG55" t="n">
-        <v>4.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5810,10 +5783,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5821,67 +5794,61 @@
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BM55" t="n">
-        <v>42.16</v>
+        <v>40.4</v>
       </c>
       <c r="BN55" t="n">
-        <v>705.1</v>
+        <v>1138.8</v>
       </c>
       <c r="BO55" t="n">
-        <v>1122.7</v>
+        <v>491.3</v>
       </c>
       <c r="BP55" t="n">
-        <v>2933.3</v>
+        <v>2986.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B56" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C56" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E56" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="O56" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z56" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>222.39</v>
+        <v>221.63</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5890,10 +5857,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5902,60 +5869,60 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="BM56" t="n">
-        <v>40.4</v>
+        <v>40.92</v>
       </c>
       <c r="BN56" t="n">
-        <v>1138.8</v>
+        <v>66.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>491.3</v>
+        <v>745.5</v>
       </c>
       <c r="BP56" t="n">
-        <v>2986.4</v>
+        <v>2960.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B57" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C57" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E57" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K57" t="n">
-        <v>98.2</v>
+        <v>100.1</v>
       </c>
       <c r="O57" t="n">
         <v>39.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>221.63</v>
+        <v>222.64</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5964,10 +5931,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>129.31</v>
+        <v>130.65</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5976,60 +5943,87 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="BM57" t="n">
-        <v>40.92</v>
+        <v>39.77</v>
       </c>
       <c r="BN57" t="n">
-        <v>66.8</v>
+        <v>63.8</v>
       </c>
       <c r="BO57" t="n">
-        <v>745.5</v>
+        <v>757.1</v>
       </c>
       <c r="BP57" t="n">
-        <v>2960.5</v>
+        <v>3027.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B58" t="n">
-        <v>151.5</v>
+        <v>172</v>
       </c>
       <c r="C58" t="n">
-        <v>72.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D58" t="n">
-        <v>30.9</v>
+        <v>29.9</v>
       </c>
       <c r="E58" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="F58" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>11</v>
+      </c>
+      <c r="J58" t="n">
+        <v>40.6</v>
       </c>
       <c r="K58" t="n">
-        <v>100.1</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>36.9</v>
       </c>
       <c r="O58" t="n">
-        <v>39.5</v>
+        <v>40.4</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>17</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA58" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AF58" t="n">
-        <v>222.64</v>
+        <v>222.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6041,7 +6035,7 @@
         <v>130.65</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6049,88 +6043,94 @@
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>14.74</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="BM58" t="n">
-        <v>39.77</v>
+        <v>40.76</v>
       </c>
       <c r="BN58" t="n">
-        <v>63.8</v>
+        <v>252.8</v>
       </c>
       <c r="BO58" t="n">
-        <v>757.1</v>
+        <v>1156.4</v>
       </c>
       <c r="BP58" t="n">
-        <v>3027.1</v>
+        <v>3172.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B59" t="n">
-        <v>172</v>
+        <v>181.5</v>
       </c>
       <c r="C59" t="n">
-        <v>75.7</v>
+        <v>73.7</v>
       </c>
       <c r="D59" t="n">
-        <v>29.9</v>
+        <v>31.9</v>
       </c>
       <c r="E59" t="n">
-        <v>34.3</v>
+        <v>38</v>
       </c>
       <c r="F59" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="H59" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="I59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="K59" t="n">
-        <v>75.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>36.9</v>
+        <v>35.9</v>
       </c>
       <c r="O59" t="n">
-        <v>40.4</v>
+        <v>39.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="R59" t="n">
         <v>1</v>
       </c>
       <c r="S59" t="n">
+        <v>18</v>
+      </c>
+      <c r="T59" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z59" t="n">
         <v>17</v>
       </c>
-      <c r="T59" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>15</v>
-      </c>
       <c r="AA59" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AF59" t="n">
-        <v>222.6</v>
+        <v>224.57</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.94</v>
+        <v>-2.05</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6139,10 +6139,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>130.65</v>
+        <v>131.48</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6151,69 +6151,69 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>84.98999999999999</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>14.74</v>
+        <v>14.47</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="BM59" t="n">
-        <v>40.76</v>
+        <v>43.17</v>
       </c>
       <c r="BN59" t="n">
-        <v>252.8</v>
+        <v>2456.2</v>
       </c>
       <c r="BO59" t="n">
-        <v>1156.4</v>
+        <v>1075.8</v>
       </c>
       <c r="BP59" t="n">
-        <v>3172.7</v>
+        <v>3051.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B60" t="n">
-        <v>181.5</v>
+        <v>176.9</v>
       </c>
       <c r="C60" t="n">
-        <v>73.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="E60" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F60" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="H60" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>41.1</v>
+        <v>42.5</v>
       </c>
       <c r="K60" t="n">
-        <v>74.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>35.9</v>
+        <v>34.6</v>
       </c>
       <c r="O60" t="n">
-        <v>39.2</v>
+        <v>37.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R60" t="n">
         <v>1</v>
@@ -6222,22 +6222,22 @@
         <v>18</v>
       </c>
       <c r="T60" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z60" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
-        <v>9.6</v>
+        <v>12.8</v>
       </c>
       <c r="AF60" t="n">
-        <v>224.57</v>
+        <v>222.52</v>
       </c>
       <c r="AG60" t="n">
-        <v>-2.05</v>
+        <v>-1.2</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6246,10 +6246,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>131.48</v>
+        <v>126.17</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.83</v>
+        <v>-5.31</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6258,60 +6258,60 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>84.06999999999999</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="AS60" t="n">
-        <v>14.47</v>
+        <v>14.28</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="BM60" t="n">
-        <v>43.17</v>
+        <v>41.78</v>
       </c>
       <c r="BN60" t="n">
-        <v>2456.2</v>
+        <v>4128.6</v>
       </c>
       <c r="BO60" t="n">
-        <v>1075.8</v>
+        <v>1204.7</v>
       </c>
       <c r="BP60" t="n">
-        <v>3051.6</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B61" t="n">
-        <v>158.2</v>
+        <v>146.2</v>
       </c>
       <c r="C61" t="n">
-        <v>75.3</v>
+        <v>69.3</v>
       </c>
       <c r="D61" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="E61" t="n">
-        <v>34.5</v>
+        <v>31.3</v>
       </c>
       <c r="F61" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AF61" t="n">
-        <v>221.34</v>
+        <v>219.56</v>
       </c>
       <c r="AG61" t="n">
-        <v>-1.2</v>
+        <v>-1.79</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6320,10 +6320,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>123.51</v>
+        <v>121.5</v>
       </c>
       <c r="AL61" t="n">
-        <v>-7.97</v>
+        <v>-4.67</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6332,45 +6332,45 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="BM61" t="n">
-        <v>41.78</v>
+        <v>38.65</v>
       </c>
       <c r="BN61" t="n">
-        <v>4128.6</v>
+        <v>6526.2</v>
       </c>
       <c r="BO61" t="n">
-        <v>1204.7</v>
+        <v>1242.5</v>
       </c>
       <c r="BP61" t="n">
-        <v>3187</v>
+        <v>2960.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B62" t="n">
-        <v>146.2</v>
+        <v>149.8</v>
       </c>
       <c r="C62" t="n">
-        <v>69.3</v>
+        <v>75.5</v>
       </c>
       <c r="D62" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="E62" t="n">
-        <v>31.3</v>
+        <v>29</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA62" t="n">
         <v>11.5</v>
@@ -6388,7 +6388,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,43 +628,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2" t="n">
-        <v>143.9</v>
+        <v>145.9</v>
       </c>
       <c r="C2" t="n">
-        <v>32.1</v>
+        <v>33.8</v>
       </c>
       <c r="D2" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="E2" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="M2" t="n">
         <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="O2" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -679,19 +679,28 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>217.8</v>
+        <v>213</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4.81</v>
+        <v>-2.75</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -700,7 +709,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>137.33</v>
+        <v>134.2</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -715,13 +724,13 @@
         <v>0</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BM2" t="n">
-        <v>43.16</v>
+        <v>47.06</v>
       </c>
       <c r="BN2" t="n">
-        <v>212.4</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -732,70 +741,79 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C3" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D3" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E3" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K3" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N3" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O3" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>14</v>
+        <v>16.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -804,10 +822,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.13</v>
+        <v>-5.41</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -816,19 +834,19 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM3" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -839,46 +857,46 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B4" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C4" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D4" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E4" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K4" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N4" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O4" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R4" t="n">
         <v>0.6</v>
@@ -887,22 +905,31 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -911,10 +938,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -923,19 +950,19 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS4" t="n">
         <v>13.07</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM4" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN4" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -946,70 +973,52 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B5" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C5" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D5" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E5" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J5" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O5" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y5" t="n">
         <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.7</v>
+        <v>18</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1017,35 +1026,23 @@
       <c r="AI5" t="n">
         <v>235</v>
       </c>
-      <c r="AK5" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
       <c r="AN5" t="n">
         <v>142</v>
       </c>
-      <c r="AP5" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL5" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM5" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP5" t="n">
         <v>0</v>
@@ -1053,43 +1050,52 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B6" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C6" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D6" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E6" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>18</v>
+        <v>18.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1104,60 +1110,96 @@
         <v>142</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM6" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B7" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C7" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D7" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E7" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.6</v>
       </c>
       <c r="K7" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>34</v>
       </c>
       <c r="O7" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.5</v>
+        <v>13.4</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1165,17 +1207,29 @@
       <c r="AI7" t="n">
         <v>235</v>
       </c>
+      <c r="AK7" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM7" t="n">
         <v>110</v>
       </c>
       <c r="AN7" t="n">
         <v>142</v>
       </c>
+      <c r="AP7" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL7" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM7" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
@@ -1184,75 +1238,84 @@
         <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B8" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C8" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E8" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F8" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I8" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K8" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O8" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>13.4</v>
+      <c r="AC8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1261,10 +1324,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1273,16 +1336,16 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM8" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
@@ -1291,30 +1354,30 @@
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B9" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D9" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E9" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H9" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I9" t="n">
         <v>9.800000000000001</v>
@@ -1323,43 +1386,52 @@
         <v>38.6</v>
       </c>
       <c r="K9" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O9" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="AF9" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1368,10 +1440,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1380,93 +1452,102 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM9" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B10" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C10" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D10" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N10" t="n">
         <v>35.2</v>
       </c>
-      <c r="E10" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O10" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.8</v>
+        <v>16</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1475,10 +1556,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL10" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1487,93 +1568,69 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM10" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B11" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C11" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D11" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E11" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>21</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
         <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>16</v>
+        <v>15.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>7.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1582,10 +1639,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1593,61 +1650,64 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM11" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN11" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B12" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C12" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D12" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.5</v>
+        <v>19</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1656,10 +1716,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1668,10 +1728,10 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM12" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -1680,42 +1740,51 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B13" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C13" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D13" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E13" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F13" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA13" t="n">
-        <v>19</v>
+        <v>15.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1724,10 +1793,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL13" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1736,10 +1805,10 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM13" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -1748,42 +1817,84 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B14" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C14" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D14" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E14" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F14" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z14" t="n">
         <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1795,7 +1906,7 @@
         <v>138.94</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1803,11 +1914,17 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM14" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -1816,51 +1933,51 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B15" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C15" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D15" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E15" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I15" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N15" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O15" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R15" t="n">
         <v>3.5</v>
@@ -1869,22 +1986,31 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>7</v>
       </c>
       <c r="AF15" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1893,10 +2019,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1905,16 +2031,16 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS15" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM15" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -1923,75 +2049,84 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B16" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C16" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E16" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H16" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J16" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K16" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N16" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O16" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R16" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>7.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2000,10 +2135,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2012,93 +2147,102 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM16" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO16" t="n">
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B17" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D17" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E17" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F17" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H17" t="n">
         <v>25.4</v>
       </c>
       <c r="I17" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J17" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K17" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AB17" t="n">
         <v>4.8</v>
       </c>
-      <c r="N17" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>20.3</v>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>6.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2107,10 +2251,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2119,93 +2263,102 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM17" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN17" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO17" t="n">
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B18" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C18" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D18" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E18" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F18" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H18" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I18" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J18" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O18" t="n">
         <v>38.4</v>
       </c>
-      <c r="K18" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q18" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.1</v>
+        <v>13.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2214,10 +2367,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2226,93 +2379,75 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM18" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN18" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B19" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C19" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D19" t="n">
         <v>34.5</v>
       </c>
       <c r="E19" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F19" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K19" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N19" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O19" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.9</v>
+        <v>10</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2321,10 +2456,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2332,17 +2467,11 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM19" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -2351,48 +2480,57 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B20" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C20" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D20" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E20" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
         <v>9.6</v>
       </c>
       <c r="K20" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>10</v>
+        <v>9.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2401,10 +2539,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2413,60 +2551,96 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM20" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B21" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C21" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D21" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>38.7</v>
       </c>
       <c r="K21" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>33</v>
       </c>
       <c r="O21" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG21" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2478,7 +2652,7 @@
         <v>128.27</v>
       </c>
       <c r="AL21" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2486,88 +2660,103 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM21" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP21" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B22" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C22" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D22" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F22" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H22" t="n">
         <v>25.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J22" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K22" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O22" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>7.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2576,10 +2765,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2588,72 +2777,72 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM22" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN22" t="n">
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP22" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B23" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C23" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D23" t="n">
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F23" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H23" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O23" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q23" t="n">
         <v>23.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2662,19 +2851,28 @@
         <v>23.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2683,10 +2881,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL23" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2695,69 +2893,69 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS23" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM23" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO23" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP23" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B24" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C24" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E24" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I24" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J24" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K24" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O24" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
@@ -2766,22 +2964,31 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y24" t="n">
         <v>9</v>
       </c>
       <c r="Z24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>5.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2790,10 +2997,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2802,93 +3009,102 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM24" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN24" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP24" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B25" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C25" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D25" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E25" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I25" t="n">
         <v>9.4</v>
       </c>
       <c r="J25" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O25" t="n">
         <v>39.5</v>
       </c>
-      <c r="K25" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q25" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>6.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2897,10 +3113,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2909,93 +3125,75 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS25" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM25" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP25" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B26" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C26" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D26" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E26" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F26" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y26" t="n">
         <v>8</v>
       </c>
-      <c r="H26" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N26" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10</v>
-      </c>
       <c r="Z26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3004,10 +3202,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3015,67 +3213,70 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
-      <c r="AP26" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL26" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM26" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN26" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP26" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B27" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C27" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D27" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E27" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K27" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O27" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3084,10 +3285,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL27" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3096,60 +3297,96 @@
         <v>142</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM27" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP27" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B28" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C28" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F28" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>36.7</v>
       </c>
       <c r="O28" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3161,7 +3398,7 @@
         <v>125.11</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3169,88 +3406,103 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>14</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM28" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP28" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B29" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C29" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E29" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F29" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H29" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K29" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O29" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T29" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3259,10 +3511,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3271,93 +3523,102 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM29" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP29" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B30" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C30" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E30" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F30" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K30" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O30" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T30" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>8.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG30" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3366,10 +3627,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3378,93 +3639,102 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM30" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP30" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B31" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C31" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D31" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E31" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H31" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q31" t="n">
         <v>23.7</v>
       </c>
-      <c r="I31" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J31" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K31" t="n">
-        <v>73</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>34</v>
-      </c>
-      <c r="O31" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>22.8</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="T31" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>8.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>220.58</v>
+        <v>218.18</v>
       </c>
       <c r="AG31" t="n">
-        <v>-2.41</v>
+        <v>-5.83</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3473,10 +3743,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>125</v>
+        <v>123.1</v>
       </c>
       <c r="AL31" t="n">
-        <v>-4.53</v>
+        <v>-1.9</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3485,93 +3755,102 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>81.27</v>
+        <v>78.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.01</v>
+        <v>13.16</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="BM31" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>668.9</v>
       </c>
       <c r="BO31" t="n">
-        <v>1174.9</v>
+        <v>2177.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>3385.6</v>
+        <v>3522.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B32" t="n">
-        <v>167.7</v>
+        <v>167.8</v>
       </c>
       <c r="C32" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="F32" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="H32" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="I32" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>40.8</v>
       </c>
       <c r="K32" t="n">
-        <v>73.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>35.2</v>
+        <v>38.1</v>
       </c>
       <c r="O32" t="n">
-        <v>39</v>
+        <v>42.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="T32" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>218.18</v>
+        <v>212.3</v>
       </c>
       <c r="AG32" t="n">
-        <v>-5.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3580,10 +3859,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>123.1</v>
+        <v>121.78</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.9</v>
+        <v>-1.32</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3592,93 +3871,75 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>78.2</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.16</v>
+        <v>12.62</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="BM32" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="BN32" t="n">
-        <v>668.9</v>
+        <v>10274.1</v>
       </c>
       <c r="BO32" t="n">
-        <v>2177.3</v>
+        <v>2925.4</v>
       </c>
       <c r="BP32" t="n">
-        <v>3522.9</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B33" t="n">
-        <v>167.8</v>
+        <v>146.5</v>
       </c>
       <c r="C33" t="n">
-        <v>71.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="E33" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="F33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H33" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J33" t="n">
-        <v>40.8</v>
+        <v>7.1</v>
       </c>
       <c r="K33" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>38.1</v>
+        <v>100.9</v>
       </c>
       <c r="O33" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33" t="n">
         <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>8.4</v>
+        <v>9</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>212.3</v>
+        <v>214.64</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3687,10 +3948,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>121.78</v>
+        <v>121</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3698,67 +3959,70 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>12.62</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BM33" t="n">
-        <v>35.64</v>
+        <v>34.42</v>
       </c>
       <c r="BN33" t="n">
-        <v>10274.1</v>
+        <v>10401.8</v>
       </c>
       <c r="BO33" t="n">
-        <v>2925.4</v>
+        <v>2042.8</v>
       </c>
       <c r="BP33" t="n">
-        <v>3588</v>
+        <v>3553.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B34" t="n">
-        <v>146.5</v>
+        <v>142.1</v>
       </c>
       <c r="C34" t="n">
-        <v>66.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="D34" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E34" t="n">
         <v>29.8</v>
       </c>
       <c r="F34" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K34" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="O34" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>9</v>
+        <v>12.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>6</v>
       </c>
       <c r="AF34" t="n">
-        <v>214.64</v>
+        <v>218.66</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.23</v>
+        <v>4.02</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3767,10 +4031,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>121</v>
+        <v>124.39</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3779,33 +4043,33 @@
         <v>142</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BM34" t="n">
-        <v>34.42</v>
+        <v>34.27</v>
       </c>
       <c r="BN34" t="n">
-        <v>10401.8</v>
+        <v>2566.2</v>
       </c>
       <c r="BO34" t="n">
-        <v>2042.8</v>
+        <v>1843.4</v>
       </c>
       <c r="BP34" t="n">
-        <v>3553.1</v>
+        <v>3518.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B35" t="n">
-        <v>142.1</v>
+        <v>138</v>
       </c>
       <c r="C35" t="n">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="D35" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="E35" t="n">
         <v>29.8</v>
@@ -3814,25 +4078,34 @@
         <v>6.6</v>
       </c>
       <c r="K35" t="n">
-        <v>101.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.6</v>
+      </c>
       <c r="AF35" t="n">
-        <v>218.66</v>
+        <v>220</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3841,10 +4114,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>124.39</v>
+        <v>126.54</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3853,60 +4126,96 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BM35" t="n">
-        <v>34.27</v>
+        <v>35.63</v>
       </c>
       <c r="BN35" t="n">
-        <v>2566.2</v>
+        <v>422.9</v>
       </c>
       <c r="BO35" t="n">
-        <v>1843.4</v>
+        <v>926.5</v>
       </c>
       <c r="BP35" t="n">
-        <v>3518.4</v>
+        <v>3432.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B36" t="n">
-        <v>138</v>
+        <v>160.7</v>
       </c>
       <c r="C36" t="n">
-        <v>60.6</v>
+        <v>62</v>
       </c>
       <c r="D36" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="E36" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="F36" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>41.1</v>
       </c>
       <c r="K36" t="n">
-        <v>98.40000000000001</v>
+        <v>73.7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>37.4</v>
       </c>
       <c r="O36" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>24.4</v>
       </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>8.6</v>
       </c>
       <c r="AF36" t="n">
         <v>220</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.34</v>
+        <v>-0.75</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3918,7 +4227,7 @@
         <v>126.54</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3926,88 +4235,103 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>13.37</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="BM36" t="n">
-        <v>35.63</v>
+        <v>36.56</v>
       </c>
       <c r="BN36" t="n">
-        <v>422.9</v>
+        <v>554.1</v>
       </c>
       <c r="BO36" t="n">
-        <v>926.5</v>
+        <v>569.9</v>
       </c>
       <c r="BP36" t="n">
-        <v>3432.2</v>
+        <v>3436.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B37" t="n">
-        <v>160.7</v>
+        <v>164.5</v>
       </c>
       <c r="C37" t="n">
-        <v>62</v>
+        <v>66.5</v>
       </c>
       <c r="D37" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="E37" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="F37" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="H37" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I37" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="K37" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N37" t="n">
-        <v>37.4</v>
+        <v>34.7</v>
       </c>
       <c r="O37" t="n">
-        <v>41.4</v>
+        <v>40.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF37" t="n">
-        <v>220</v>
+        <v>219.23</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.75</v>
+        <v>-2.93</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4016,10 +4340,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>126.54</v>
+        <v>126.55</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4028,93 +4352,102 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>80.18000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AS37" t="n">
-        <v>13.37</v>
+        <v>13.77</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BM37" t="n">
-        <v>36.56</v>
+        <v>37.15</v>
       </c>
       <c r="BN37" t="n">
-        <v>554.1</v>
+        <v>6026.3</v>
       </c>
       <c r="BO37" t="n">
-        <v>569.9</v>
+        <v>593.2</v>
       </c>
       <c r="BP37" t="n">
-        <v>3436.9</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B38" t="n">
-        <v>164.5</v>
+        <v>162.4</v>
       </c>
       <c r="C38" t="n">
-        <v>66.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="E38" t="n">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F38" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="I38" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K38" t="n">
         <v>76.5</v>
       </c>
       <c r="M38" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="O38" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>14.2</v>
+        <v>16</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>219.23</v>
+        <v>216.29</v>
       </c>
       <c r="AG38" t="n">
-        <v>-2.93</v>
+        <v>0.62</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4123,10 +4456,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>126.55</v>
+        <v>126.45</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4135,72 +4468,72 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>75.90000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="AS38" t="n">
-        <v>13.77</v>
+        <v>12.96</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="BM38" t="n">
-        <v>37.15</v>
+        <v>32.3</v>
       </c>
       <c r="BN38" t="n">
-        <v>6026.3</v>
+        <v>12649</v>
       </c>
       <c r="BO38" t="n">
-        <v>593.2</v>
+        <v>1123.4</v>
       </c>
       <c r="BP38" t="n">
-        <v>3525.8</v>
+        <v>3281.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B39" t="n">
-        <v>162.4</v>
+        <v>157.5</v>
       </c>
       <c r="C39" t="n">
-        <v>67.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D39" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="E39" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H39" t="n">
         <v>26.1</v>
       </c>
       <c r="I39" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J39" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="K39" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="N39" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="O39" t="n">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q39" t="n">
         <v>24.2</v>
       </c>
       <c r="R39" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -4209,19 +4542,28 @@
         <v>24.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
         <v>16</v>
       </c>
       <c r="AA39" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>7.6</v>
       </c>
       <c r="AF39" t="n">
-        <v>216.29</v>
+        <v>216.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4230,10 +4572,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>126.45</v>
+        <v>124.66</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4242,93 +4584,75 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>75.38</v>
+        <v>76.8</v>
       </c>
       <c r="AS39" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BM39" t="n">
-        <v>32.3</v>
+        <v>30.61</v>
       </c>
       <c r="BN39" t="n">
-        <v>12649</v>
+        <v>15239.7</v>
       </c>
       <c r="BO39" t="n">
-        <v>1123.4</v>
+        <v>1447.3</v>
       </c>
       <c r="BP39" t="n">
-        <v>3281.4</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B40" t="n">
-        <v>157.5</v>
+        <v>135.7</v>
       </c>
       <c r="C40" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="D40" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E40" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="F40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J40" t="n">
-        <v>41.3</v>
+        <v>5.4</v>
       </c>
       <c r="K40" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>34.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
         <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>13.8</v>
+        <v>14</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>216.91</v>
+        <v>217.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>-0.72</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4337,10 +4661,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>124.66</v>
+        <v>125.93</v>
       </c>
       <c r="AL40" t="n">
-        <v>-1.79</v>
+        <v>1.27</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4348,67 +4672,70 @@
       <c r="AN40" t="n">
         <v>142</v>
       </c>
-      <c r="AP40" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BL40" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="BM40" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="BN40" t="n">
-        <v>15239.7</v>
+        <v>12907.2</v>
       </c>
       <c r="BO40" t="n">
-        <v>1447.3</v>
+        <v>1441.3</v>
       </c>
       <c r="BP40" t="n">
-        <v>3587.2</v>
+        <v>3544.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B41" t="n">
-        <v>135.7</v>
+        <v>130.4</v>
       </c>
       <c r="C41" t="n">
-        <v>62.2</v>
+        <v>58.6</v>
       </c>
       <c r="D41" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="E41" t="n">
-        <v>25.3</v>
+        <v>22.5</v>
       </c>
       <c r="F41" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="K41" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z41" t="n">
         <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7.9</v>
       </c>
       <c r="AF41" t="n">
-        <v>217.5</v>
+        <v>217.82</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4417,10 +4744,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>125.93</v>
+        <v>125.03</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.27</v>
+        <v>-0.9</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4429,60 +4756,96 @@
         <v>142</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="BM41" t="n">
-        <v>30.47</v>
+        <v>29.35</v>
       </c>
       <c r="BN41" t="n">
-        <v>12907.2</v>
+        <v>7367.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>1441.3</v>
+        <v>1684.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>3544.9</v>
+        <v>3545.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B42" t="n">
-        <v>130.4</v>
+        <v>151</v>
       </c>
       <c r="C42" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="D42" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E42" t="n">
-        <v>22.5</v>
+        <v>25.1</v>
       </c>
       <c r="F42" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J42" t="n">
+        <v>41.3</v>
       </c>
       <c r="K42" t="n">
-        <v>96.90000000000001</v>
+        <v>72.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N42" t="n">
+        <v>37.1</v>
       </c>
       <c r="O42" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA42" t="n">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>217.82</v>
+        <v>217.8</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4494,7 +4857,7 @@
         <v>125.03</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4502,88 +4865,103 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>15.04</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="BM42" t="n">
-        <v>29.35</v>
+        <v>29.43</v>
       </c>
       <c r="BN42" t="n">
-        <v>7367.2</v>
+        <v>5971.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>1684.4</v>
+        <v>1199.2</v>
       </c>
       <c r="BP42" t="n">
-        <v>3545.2</v>
+        <v>3351.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B43" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C43" t="n">
-        <v>59.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="E43" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="F43" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="I43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K43" t="n">
-        <v>72.5</v>
+        <v>73.2</v>
       </c>
       <c r="M43" t="n">
         <v>2.7</v>
       </c>
       <c r="N43" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O43" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="R43" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T43" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA43" t="n">
-        <v>12</v>
+        <v>11.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>9.9</v>
       </c>
       <c r="AF43" t="n">
-        <v>217.8</v>
+        <v>219.54</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4592,10 +4970,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>125.03</v>
+        <v>129.57</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4604,78 +4982,78 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>81.81</v>
+        <v>83.89</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.04</v>
+        <v>15.89</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="BM43" t="n">
-        <v>29.43</v>
+        <v>39.73</v>
       </c>
       <c r="BN43" t="n">
-        <v>5971.2</v>
+        <v>2846.5</v>
       </c>
       <c r="BO43" t="n">
-        <v>1199.2</v>
+        <v>800.7</v>
       </c>
       <c r="BP43" t="n">
-        <v>3351.7</v>
+        <v>3191.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B44" t="n">
-        <v>169</v>
+        <v>174.1</v>
       </c>
       <c r="C44" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="D44" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="E44" t="n">
-        <v>35.9</v>
+        <v>37.8</v>
       </c>
       <c r="F44" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="I44" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="K44" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>39.4</v>
+        <v>37.2</v>
       </c>
       <c r="O44" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>16</v>
       </c>
       <c r="T44" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y44" t="n">
         <v>10</v>
@@ -4684,13 +5062,22 @@
         <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF44" t="n">
-        <v>219.54</v>
+        <v>220.65</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4699,10 +5086,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>129.57</v>
+        <v>132.59</v>
       </c>
       <c r="AL44" t="n">
-        <v>4.54</v>
+        <v>3.02</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4711,93 +5098,102 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>83.89</v>
+        <v>83.73</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.89</v>
+        <v>15.63</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="BM44" t="n">
-        <v>39.73</v>
+        <v>43.63</v>
       </c>
       <c r="BN44" t="n">
-        <v>2846.5</v>
+        <v>423.4</v>
       </c>
       <c r="BO44" t="n">
-        <v>800.7</v>
+        <v>559.8</v>
       </c>
       <c r="BP44" t="n">
-        <v>3191.9</v>
+        <v>3084.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B45" t="n">
-        <v>174.1</v>
+        <v>169.5</v>
       </c>
       <c r="C45" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="D45" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="E45" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="F45" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H45" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="K45" t="n">
-        <v>72.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N45" t="n">
-        <v>37.2</v>
+        <v>35.9</v>
       </c>
       <c r="O45" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S45" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T45" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="n">
-        <v>14.1</v>
+        <v>14</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>7.2</v>
       </c>
       <c r="AF45" t="n">
-        <v>220.65</v>
+        <v>219.97</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4806,10 +5202,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>132.59</v>
+        <v>130.34</v>
       </c>
       <c r="AL45" t="n">
-        <v>3.02</v>
+        <v>-2.25</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4818,78 +5214,78 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>83.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.63</v>
+        <v>13.98</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BM45" t="n">
-        <v>43.63</v>
+        <v>42.19</v>
       </c>
       <c r="BN45" t="n">
-        <v>423.4</v>
+        <v>56.3</v>
       </c>
       <c r="BO45" t="n">
-        <v>559.8</v>
+        <v>612.6</v>
       </c>
       <c r="BP45" t="n">
-        <v>3084.2</v>
+        <v>3054.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B46" t="n">
-        <v>169.5</v>
+        <v>171.5</v>
       </c>
       <c r="C46" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="D46" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="E46" t="n">
-        <v>38.6</v>
+        <v>41.2</v>
       </c>
       <c r="F46" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H46" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="I46" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J46" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="K46" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M46" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>35.9</v>
+        <v>38</v>
       </c>
       <c r="O46" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="S46" t="n">
         <v>12</v>
       </c>
       <c r="T46" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y46" t="n">
         <v>13</v>
@@ -4898,13 +5294,22 @@
         <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>14</v>
+        <v>15.3</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.97</v>
+        <v>223.97</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4913,10 +5318,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>130.34</v>
+        <v>124.73</v>
       </c>
       <c r="AL46" t="n">
-        <v>-2.25</v>
+        <v>-5.61</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4925,93 +5330,75 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>84.84999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="AS46" t="n">
-        <v>13.98</v>
+        <v>14.85</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="BM46" t="n">
-        <v>42.19</v>
+        <v>47.76</v>
       </c>
       <c r="BN46" t="n">
-        <v>56.3</v>
+        <v>33.2</v>
       </c>
       <c r="BO46" t="n">
-        <v>612.6</v>
+        <v>1106.6</v>
       </c>
       <c r="BP46" t="n">
-        <v>3054.3</v>
+        <v>3210.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B47" t="n">
-        <v>171.5</v>
+        <v>152.8</v>
       </c>
       <c r="C47" t="n">
         <v>57.9</v>
       </c>
       <c r="D47" t="n">
-        <v>35.7</v>
+        <v>36.9</v>
       </c>
       <c r="E47" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="F47" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H47" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I47" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>41.6</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>38</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S47" t="n">
-        <v>12</v>
-      </c>
-      <c r="T47" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="Y47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z47" t="n">
         <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>15.3</v>
+        <v>16.5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>223.97</v>
+        <v>226.45</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5020,10 +5407,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>124.73</v>
+        <v>125.89</v>
       </c>
       <c r="AL47" t="n">
-        <v>-5.61</v>
+        <v>1.16</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5031,67 +5418,70 @@
       <c r="AN47" t="n">
         <v>142</v>
       </c>
-      <c r="AP47" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>14.85</v>
-      </c>
       <c r="BL47" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BM47" t="n">
-        <v>47.76</v>
+        <v>47.09</v>
       </c>
       <c r="BN47" t="n">
-        <v>33.2</v>
+        <v>22.8</v>
       </c>
       <c r="BO47" t="n">
-        <v>1106.6</v>
+        <v>1116</v>
       </c>
       <c r="BP47" t="n">
-        <v>3210.2</v>
+        <v>3380.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B48" t="n">
-        <v>152.8</v>
+        <v>143.6</v>
       </c>
       <c r="C48" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="D48" t="n">
-        <v>36.9</v>
+        <v>33.9</v>
       </c>
       <c r="E48" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K48" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O48" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z48" t="n">
         <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>16.5</v>
+        <v>16</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>226.45</v>
+        <v>228.57</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5100,10 +5490,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>125.89</v>
+        <v>128.43</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.16</v>
+        <v>2.54</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5112,60 +5502,96 @@
         <v>142</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BM48" t="n">
-        <v>47.09</v>
+        <v>45.96</v>
       </c>
       <c r="BN48" t="n">
-        <v>22.8</v>
+        <v>30.9</v>
       </c>
       <c r="BO48" t="n">
-        <v>1116</v>
+        <v>582.3</v>
       </c>
       <c r="BP48" t="n">
-        <v>3380.9</v>
+        <v>3256.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B49" t="n">
-        <v>143.6</v>
+        <v>161.8</v>
       </c>
       <c r="C49" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="D49" t="n">
-        <v>33.9</v>
+        <v>31.9</v>
       </c>
       <c r="E49" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="F49" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>40.6</v>
       </c>
       <c r="K49" t="n">
-        <v>93.5</v>
+        <v>75.3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N49" t="n">
+        <v>36</v>
       </c>
       <c r="O49" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>11</v>
+      </c>
+      <c r="T49" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>16</v>
+        <v>15.7</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>228.57</v>
+        <v>228.53</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.11</v>
+        <v>-0.42</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5177,7 +5603,7 @@
         <v>128.43</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5185,88 +5611,103 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
+      <c r="AP49" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>15.64</v>
+      </c>
       <c r="BL49" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BM49" t="n">
-        <v>45.96</v>
+        <v>42.04</v>
       </c>
       <c r="BN49" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="BO49" t="n">
-        <v>582.3</v>
+        <v>369.2</v>
       </c>
       <c r="BP49" t="n">
-        <v>3256.4</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B50" t="n">
-        <v>161.8</v>
+        <v>176.9</v>
       </c>
       <c r="C50" t="n">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="D50" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="E50" t="n">
-        <v>38.1</v>
+        <v>42.8</v>
       </c>
       <c r="F50" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H50" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I50" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="K50" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
       <c r="O50" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="R50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>12</v>
+      </c>
+      <c r="T50" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1</v>
       </c>
-      <c r="S50" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>15.7</v>
+      <c r="AC50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF50" t="n">
-        <v>228.53</v>
+        <v>228.12</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5275,10 +5716,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>128.43</v>
+        <v>130.82</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5287,93 +5728,102 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>85.77</v>
+        <v>78.98</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.64</v>
+        <v>14.72</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BM50" t="n">
-        <v>42.04</v>
+        <v>47.75</v>
       </c>
       <c r="BN50" t="n">
-        <v>39.6</v>
+        <v>83.7</v>
       </c>
       <c r="BO50" t="n">
-        <v>369.2</v>
+        <v>1136.8</v>
       </c>
       <c r="BP50" t="n">
-        <v>3102.8</v>
+        <v>3331.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B51" t="n">
-        <v>176.9</v>
+        <v>177.6</v>
       </c>
       <c r="C51" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D51" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="E51" t="n">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
       <c r="F51" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H51" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="I51" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="K51" t="n">
         <v>75.7</v>
       </c>
       <c r="M51" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N51" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="O51" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="R51" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T51" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA51" t="n">
-        <v>14.5</v>
+        <v>11.7</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF51" t="n">
-        <v>228.12</v>
+        <v>221.25</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5382,10 +5832,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>130.82</v>
+        <v>130.31</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.39</v>
+        <v>-0.51</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5394,93 +5844,102 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>78.98</v>
+        <v>79.09</v>
       </c>
       <c r="AS51" t="n">
-        <v>14.72</v>
+        <v>14.58</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BM51" t="n">
-        <v>47.75</v>
+        <v>46.97</v>
       </c>
       <c r="BN51" t="n">
-        <v>83.7</v>
+        <v>120.7</v>
       </c>
       <c r="BO51" t="n">
-        <v>1136.8</v>
+        <v>1228.7</v>
       </c>
       <c r="BP51" t="n">
-        <v>3331.2</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B52" t="n">
-        <v>177.6</v>
+        <v>173.6</v>
       </c>
       <c r="C52" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D52" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="E52" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="F52" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>40.9</v>
+        <v>42.2</v>
       </c>
       <c r="K52" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="M52" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="O52" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S52" t="n">
         <v>17</v>
       </c>
       <c r="T52" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z52" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF52" t="n">
-        <v>221.25</v>
+        <v>221.33</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.06</v>
+        <v>-2.42</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5489,10 +5948,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>130.31</v>
+        <v>127.53</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5501,93 +5960,102 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>79.09</v>
+        <v>83.27</v>
       </c>
       <c r="AS52" t="n">
-        <v>14.58</v>
+        <v>15.52</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BM52" t="n">
-        <v>46.97</v>
+        <v>44.04</v>
       </c>
       <c r="BN52" t="n">
-        <v>120.7</v>
+        <v>75.8</v>
       </c>
       <c r="BO52" t="n">
-        <v>1228.7</v>
+        <v>1187.4</v>
       </c>
       <c r="BP52" t="n">
-        <v>3169.7</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B53" t="n">
-        <v>173.6</v>
+        <v>167.5</v>
       </c>
       <c r="C53" t="n">
-        <v>67.2</v>
+        <v>64.5</v>
       </c>
       <c r="D53" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E53" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H53" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I53" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J53" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="K53" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N53" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="O53" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R53" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S53" t="n">
         <v>17</v>
       </c>
       <c r="T53" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA53" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF53" t="n">
-        <v>221.33</v>
+        <v>218.89</v>
       </c>
       <c r="AG53" t="n">
-        <v>-2.42</v>
+        <v>4.08</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5596,10 +6064,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>127.53</v>
+        <v>128.07</v>
       </c>
       <c r="AL53" t="n">
-        <v>-2.78</v>
+        <v>0.54</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5608,93 +6076,75 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>83.27</v>
+        <v>86.44</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.52</v>
+        <v>15.76</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BM53" t="n">
-        <v>44.04</v>
+        <v>42.16</v>
       </c>
       <c r="BN53" t="n">
-        <v>75.8</v>
+        <v>705.1</v>
       </c>
       <c r="BO53" t="n">
-        <v>1187.4</v>
+        <v>1122.7</v>
       </c>
       <c r="BP53" t="n">
-        <v>2818.5</v>
+        <v>2933.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B54" t="n">
-        <v>167.5</v>
+        <v>147.9</v>
       </c>
       <c r="C54" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D54" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="E54" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="F54" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H54" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J54" t="n">
-        <v>41.2</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N54" t="n">
-        <v>35.2</v>
+        <v>96</v>
       </c>
       <c r="O54" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>17</v>
-      </c>
-      <c r="T54" t="n">
-        <v>22.9</v>
+        <v>38.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z54" t="n">
         <v>17</v>
       </c>
       <c r="AA54" t="n">
-        <v>13.5</v>
+        <v>12</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>-1</v>
       </c>
       <c r="AF54" t="n">
-        <v>218.89</v>
+        <v>222.39</v>
       </c>
       <c r="AG54" t="n">
-        <v>4.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5703,10 +6153,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>128.07</v>
+        <v>128.28</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5714,67 +6164,70 @@
       <c r="AN54" t="n">
         <v>142</v>
       </c>
-      <c r="AP54" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>15.76</v>
-      </c>
       <c r="BL54" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BM54" t="n">
-        <v>42.16</v>
+        <v>40.4</v>
       </c>
       <c r="BN54" t="n">
-        <v>705.1</v>
+        <v>1138.8</v>
       </c>
       <c r="BO54" t="n">
-        <v>1122.7</v>
+        <v>491.3</v>
       </c>
       <c r="BP54" t="n">
-        <v>2933.3</v>
+        <v>2986.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B55" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
       <c r="C55" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>32.7</v>
+        <v>31.1</v>
       </c>
       <c r="E55" t="n">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="O55" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z55" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>12</v>
+        <v>11.5</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>-2.6</v>
       </c>
       <c r="AF55" t="n">
-        <v>222.39</v>
+        <v>221.63</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5783,10 +6236,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.28</v>
+        <v>129.31</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5795,60 +6248,60 @@
         <v>142</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="BM55" t="n">
-        <v>40.4</v>
+        <v>40.92</v>
       </c>
       <c r="BN55" t="n">
-        <v>1138.8</v>
+        <v>66.8</v>
       </c>
       <c r="BO55" t="n">
-        <v>491.3</v>
+        <v>745.5</v>
       </c>
       <c r="BP55" t="n">
-        <v>2986.4</v>
+        <v>2960.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B56" t="n">
-        <v>148.8</v>
+        <v>151.5</v>
       </c>
       <c r="C56" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="E56" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K56" t="n">
-        <v>98.2</v>
+        <v>100.1</v>
       </c>
       <c r="O56" t="n">
         <v>39.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>221.63</v>
+        <v>222.64</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5857,10 +6310,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>129.31</v>
+        <v>130.65</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5869,60 +6322,87 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="BM56" t="n">
-        <v>40.92</v>
+        <v>39.77</v>
       </c>
       <c r="BN56" t="n">
-        <v>66.8</v>
+        <v>63.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>745.5</v>
+        <v>757.1</v>
       </c>
       <c r="BP56" t="n">
-        <v>2960.5</v>
+        <v>3027.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B57" t="n">
-        <v>151.5</v>
+        <v>172</v>
       </c>
       <c r="C57" t="n">
-        <v>72.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D57" t="n">
-        <v>30.9</v>
+        <v>29.9</v>
       </c>
       <c r="E57" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="F57" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>11</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40.6</v>
       </c>
       <c r="K57" t="n">
-        <v>100.1</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>36.9</v>
       </c>
       <c r="O57" t="n">
-        <v>39.5</v>
+        <v>40.4</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>17</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA57" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AF57" t="n">
-        <v>222.64</v>
+        <v>222.6</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5934,7 +6414,7 @@
         <v>130.65</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5942,88 +6422,94 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>14.74</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="BM57" t="n">
-        <v>39.77</v>
+        <v>40.76</v>
       </c>
       <c r="BN57" t="n">
-        <v>63.8</v>
+        <v>252.8</v>
       </c>
       <c r="BO57" t="n">
-        <v>757.1</v>
+        <v>1156.4</v>
       </c>
       <c r="BP57" t="n">
-        <v>3027.1</v>
+        <v>3172.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B58" t="n">
-        <v>172</v>
+        <v>181.5</v>
       </c>
       <c r="C58" t="n">
-        <v>75.7</v>
+        <v>73.7</v>
       </c>
       <c r="D58" t="n">
-        <v>29.9</v>
+        <v>31.9</v>
       </c>
       <c r="E58" t="n">
-        <v>34.3</v>
+        <v>38</v>
       </c>
       <c r="F58" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="H58" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="K58" t="n">
-        <v>75.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>36.9</v>
+        <v>35.9</v>
       </c>
       <c r="O58" t="n">
-        <v>40.4</v>
+        <v>39.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
       <c r="S58" t="n">
+        <v>18</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z58" t="n">
         <v>17</v>
       </c>
-      <c r="T58" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>15</v>
-      </c>
       <c r="AA58" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>222.6</v>
+        <v>224.57</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.94</v>
+        <v>-2.05</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6032,10 +6518,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>130.65</v>
+        <v>131.48</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6044,69 +6530,69 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>84.98999999999999</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="AS58" t="n">
-        <v>14.74</v>
+        <v>14.47</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="BM58" t="n">
-        <v>40.76</v>
+        <v>43.17</v>
       </c>
       <c r="BN58" t="n">
-        <v>252.8</v>
+        <v>2456.2</v>
       </c>
       <c r="BO58" t="n">
-        <v>1156.4</v>
+        <v>1075.8</v>
       </c>
       <c r="BP58" t="n">
-        <v>3172.7</v>
+        <v>3051.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B59" t="n">
-        <v>181.5</v>
+        <v>176.9</v>
       </c>
       <c r="C59" t="n">
-        <v>73.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="E59" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F59" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="H59" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>41.1</v>
+        <v>42.5</v>
       </c>
       <c r="K59" t="n">
-        <v>74.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>35.9</v>
+        <v>34.6</v>
       </c>
       <c r="O59" t="n">
-        <v>39.2</v>
+        <v>37.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="R59" t="n">
         <v>1</v>
@@ -6115,22 +6601,22 @@
         <v>18</v>
       </c>
       <c r="T59" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="Y59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>9.6</v>
+        <v>12.8</v>
       </c>
       <c r="AF59" t="n">
-        <v>224.57</v>
+        <v>222.52</v>
       </c>
       <c r="AG59" t="n">
-        <v>-2.05</v>
+        <v>-1.2</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6139,10 +6625,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>131.48</v>
+        <v>126.17</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.83</v>
+        <v>-5.31</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6151,93 +6637,93 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>84.06999999999999</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="AS59" t="n">
-        <v>14.47</v>
+        <v>14.28</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="BM59" t="n">
-        <v>43.17</v>
+        <v>41.78</v>
       </c>
       <c r="BN59" t="n">
-        <v>2456.2</v>
+        <v>4128.6</v>
       </c>
       <c r="BO59" t="n">
-        <v>1075.8</v>
+        <v>1204.7</v>
       </c>
       <c r="BP59" t="n">
-        <v>3051.6</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B60" t="n">
-        <v>176.9</v>
+        <v>173</v>
       </c>
       <c r="C60" t="n">
-        <v>75.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="D60" t="n">
-        <v>31.2</v>
+        <v>31.9</v>
       </c>
       <c r="E60" t="n">
-        <v>33</v>
+        <v>32.1</v>
       </c>
       <c r="F60" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H60" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="I60" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J60" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="K60" t="n">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
       <c r="O60" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="S60" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T60" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="Y60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA60" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="AF60" t="n">
-        <v>222.52</v>
+        <v>221.32</v>
       </c>
       <c r="AG60" t="n">
-        <v>-1.2</v>
+        <v>-1.79</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6246,10 +6732,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>126.17</v>
+        <v>123.51</v>
       </c>
       <c r="AL60" t="n">
-        <v>-5.31</v>
+        <v>-2.66</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6258,61 +6744,55 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>82.01000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="AS60" t="n">
-        <v>14.28</v>
+        <v>14.36</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="BM60" t="n">
-        <v>41.78</v>
+        <v>38.65</v>
       </c>
       <c r="BN60" t="n">
-        <v>4128.6</v>
+        <v>6526.2</v>
       </c>
       <c r="BO60" t="n">
-        <v>1204.7</v>
+        <v>1242.5</v>
       </c>
       <c r="BP60" t="n">
-        <v>3187</v>
+        <v>2960.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B61" t="n">
-        <v>146.2</v>
+        <v>149.8</v>
       </c>
       <c r="C61" t="n">
-        <v>69.3</v>
+        <v>75.5</v>
       </c>
       <c r="D61" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="E61" t="n">
-        <v>31.3</v>
+        <v>29</v>
       </c>
       <c r="F61" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA61" t="n">
         <v>11.5</v>
       </c>
-      <c r="AF61" t="n">
-        <v>219.56</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>-1.79</v>
-      </c>
       <c r="AH61" t="n">
         <v>215</v>
       </c>
@@ -6320,10 +6800,10 @@
         <v>235</v>
       </c>
       <c r="AK61" t="n">
-        <v>121.5</v>
+        <v>122.48</v>
       </c>
       <c r="AL61" t="n">
-        <v>-4.67</v>
+        <v>-1.03</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
@@ -6332,48 +6812,36 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>6526.2</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>1242.5</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>2960.5</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B62" t="n">
-        <v>149.8</v>
+        <v>146.2</v>
       </c>
       <c r="C62" t="n">
-        <v>75.5</v>
+        <v>71.2</v>
       </c>
       <c r="D62" t="n">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="E62" t="n">
-        <v>29</v>
+        <v>29.7</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="Y62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z62" t="n">
         <v>15</v>
       </c>
       <c r="AA62" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6388,7 +6856,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,79 +628,70 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B2" t="n">
-        <v>145.9</v>
+        <v>143.6</v>
       </c>
       <c r="C2" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="D2" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="E2" t="n">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="H2" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="I2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="K2" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N2" t="n">
-        <v>27.7</v>
+        <v>34.1</v>
       </c>
       <c r="O2" t="n">
-        <v>29.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>6.2</v>
+        <v>16.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>213</v>
+        <v>210.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2.75</v>
+        <v>4.37</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -709,7 +700,7 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>134.2</v>
+        <v>128.79</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -718,19 +709,19 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>13.07</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BM2" t="n">
-        <v>47.06</v>
+        <v>42.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>443.9</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -741,46 +732,46 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B3" t="n">
-        <v>143.6</v>
+        <v>139.1</v>
       </c>
       <c r="C3" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="D3" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="E3" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="F3" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H3" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="K3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N3" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="O3" t="n">
-        <v>36.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="R3" t="n">
         <v>0.6</v>
@@ -789,31 +780,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>6.6</v>
+        <v>17.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>210.3</v>
+        <v>214.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -822,10 +804,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>128.79</v>
+        <v>126.33</v>
       </c>
       <c r="AL3" t="n">
-        <v>-5.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -834,19 +816,19 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>78.36</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AS3" t="n">
         <v>13.07</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BM3" t="n">
-        <v>42.7</v>
+        <v>39.27</v>
       </c>
       <c r="BN3" t="n">
-        <v>443.9</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
@@ -857,79 +839,43 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B4" t="n">
-        <v>139.1</v>
+        <v>119.5</v>
       </c>
       <c r="C4" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="D4" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="E4" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J4" t="n">
-        <v>36.9</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="O4" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>19.8</v>
+        <v>28.5</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.3</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>214.63</v>
+        <v>213.96</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.35</v>
+        <v>-5.01</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -937,35 +883,23 @@
       <c r="AI4" t="n">
         <v>235</v>
       </c>
-      <c r="AK4" t="n">
-        <v>126.33</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-2.46</v>
-      </c>
       <c r="AM4" t="n">
         <v>110</v>
       </c>
       <c r="AN4" t="n">
         <v>142</v>
       </c>
-      <c r="AP4" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>13.07</v>
-      </c>
       <c r="BL4" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BM4" t="n">
-        <v>39.27</v>
+        <v>41.19</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BP4" t="n">
         <v>0</v>
@@ -973,52 +907,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B5" t="n">
-        <v>119.5</v>
+        <v>112.6</v>
       </c>
       <c r="C5" t="n">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="D5" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="E5" t="n">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>85.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>28.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>6.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>213.96</v>
+        <v>212.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1033,69 +958,87 @@
         <v>142</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="BM5" t="n">
-        <v>41.19</v>
+        <v>35.94</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B6" t="n">
-        <v>112.6</v>
+        <v>137.4</v>
       </c>
       <c r="C6" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3</v>
+        <v>32.8</v>
       </c>
       <c r="E6" t="n">
-        <v>30.1</v>
+        <v>27.7</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.6</v>
       </c>
       <c r="K6" t="n">
-        <v>80.59999999999999</v>
+        <v>69.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>34</v>
       </c>
       <c r="O6" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>212.08</v>
+        <v>212.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.88</v>
+        <v>-0.12</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1103,17 +1046,29 @@
       <c r="AI6" t="n">
         <v>235</v>
       </c>
+      <c r="AK6" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.31</v>
+      </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>12.45</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BM6" t="n">
-        <v>35.94</v>
+        <v>29.44</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -1122,84 +1077,75 @@
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>803</v>
+        <v>2614.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B7" t="n">
-        <v>137.4</v>
+        <v>156.2</v>
       </c>
       <c r="C7" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="E7" t="n">
-        <v>27.7</v>
+        <v>34.7</v>
       </c>
       <c r="F7" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I7" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="K7" t="n">
-        <v>69.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>27.8</v>
       </c>
       <c r="O7" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.1</v>
+        <v>11.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>212.1</v>
+        <v>211.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.12</v>
+        <v>-3.2</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1208,10 +1154,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>128.64</v>
+        <v>129.95</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1220,16 +1166,16 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>75.88</v>
+        <v>74.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BM7" t="n">
-        <v>29.44</v>
+        <v>38.57</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
@@ -1238,30 +1184,30 @@
         <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>2614.1</v>
+        <v>3080.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B8" t="n">
-        <v>156.2</v>
+        <v>151.4</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D8" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="E8" t="n">
-        <v>34.7</v>
+        <v>29.1</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="H8" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="I8" t="n">
         <v>9.800000000000001</v>
@@ -1270,52 +1216,43 @@
         <v>38.6</v>
       </c>
       <c r="K8" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="O8" t="n">
-        <v>31.4</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>6.1</v>
+        <v>15.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>211.95</v>
+        <v>208.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1324,10 +1261,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>129.95</v>
+        <v>122.63</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.31</v>
+        <v>-7.32</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1336,102 +1273,93 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>74.8</v>
+        <v>72.87</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.33</v>
+        <v>14.41</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BM8" t="n">
-        <v>38.57</v>
+        <v>35.38</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1290.5</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>3080.7</v>
+        <v>3224.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B9" t="n">
-        <v>151.4</v>
+        <v>143.4</v>
       </c>
       <c r="C9" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D9" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N9" t="n">
         <v>35.2</v>
       </c>
-      <c r="E9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J9" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>34.2</v>
-      </c>
       <c r="O9" t="n">
-        <v>38.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>8.300000000000001</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>208.67</v>
+        <v>208.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1440,10 +1368,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>122.63</v>
+        <v>120.64</v>
       </c>
       <c r="AL9" t="n">
-        <v>-7.32</v>
+        <v>-1.99</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1452,102 +1380,60 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>72.87</v>
+        <v>72.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.41</v>
+        <v>14.19</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BM9" t="n">
-        <v>35.38</v>
+        <v>33.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1290.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>3224.5</v>
+        <v>3077.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B10" t="n">
-        <v>143.4</v>
+        <v>126.5</v>
       </c>
       <c r="C10" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="D10" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="E10" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>21</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
         <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>7.3</v>
+        <v>15.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>208.07</v>
+        <v>205.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1556,10 +1442,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>120.64</v>
+        <v>126.26</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.99</v>
+        <v>5.62</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1567,70 +1453,55 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>14.19</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BM10" t="n">
-        <v>33.67</v>
+        <v>34.74</v>
       </c>
       <c r="BN10" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>3077.5</v>
+        <v>3215.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B11" t="n">
-        <v>126.5</v>
+        <v>117</v>
       </c>
       <c r="C11" t="n">
-        <v>42.3</v>
+        <v>40.6</v>
       </c>
       <c r="D11" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="F11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AF11" t="n">
-        <v>205.66</v>
+        <v>215.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.7</v>
+        <v>9.42</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1639,10 +1510,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>126.26</v>
+        <v>137.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.62</v>
+        <v>10.99</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1651,10 +1522,10 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BM11" t="n">
-        <v>34.74</v>
+        <v>28.2</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -1663,51 +1534,42 @@
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>3215.1</v>
+        <v>2951.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B12" t="n">
-        <v>117</v>
+        <v>123.4</v>
       </c>
       <c r="C12" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="D12" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="E12" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="F12" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.4</v>
+        <v>15.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>215.07</v>
+        <v>218.94</v>
       </c>
       <c r="AG12" t="n">
-        <v>9.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1716,10 +1578,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>137.25</v>
+        <v>138.94</v>
       </c>
       <c r="AL12" t="n">
-        <v>10.99</v>
+        <v>1.69</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1728,10 +1590,10 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BM12" t="n">
-        <v>28.2</v>
+        <v>34.9</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -1740,51 +1602,75 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>2951.2</v>
+        <v>2928.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B13" t="n">
-        <v>123.4</v>
+        <v>139.9</v>
       </c>
       <c r="C13" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="D13" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="F13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>22.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
         <v>18</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>11.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>218.94</v>
+        <v>216.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>5.78</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1796,7 +1682,7 @@
         <v>138.94</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1804,11 +1690,17 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>17.47</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BM13" t="n">
-        <v>34.9</v>
+        <v>35.06</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -1817,51 +1709,51 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>2928.3</v>
+        <v>2891.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B14" t="n">
-        <v>139.9</v>
+        <v>150.3</v>
       </c>
       <c r="C14" t="n">
-        <v>49.3</v>
+        <v>44.1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E14" t="n">
-        <v>30.3</v>
+        <v>35.2</v>
       </c>
       <c r="F14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I14" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="M14" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="N14" t="n">
-        <v>31.8</v>
+        <v>36</v>
       </c>
       <c r="O14" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="R14" t="n">
         <v>3.5</v>
@@ -1870,31 +1762,22 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6.8</v>
+        <v>16.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>216.4</v>
+        <v>224.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.78</v>
+        <v>-1.69</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1903,10 +1786,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>138.94</v>
+        <v>137.96</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1915,16 +1798,16 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>82.64</v>
+        <v>80.97</v>
       </c>
       <c r="AS14" t="n">
-        <v>17.47</v>
+        <v>15.56</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BM14" t="n">
-        <v>35.06</v>
+        <v>37.45</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -1933,84 +1816,75 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>2891.3</v>
+        <v>2948.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B15" t="n">
-        <v>150.3</v>
+        <v>147.9</v>
       </c>
       <c r="C15" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E15" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H15" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J15" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="K15" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N15" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="O15" t="n">
-        <v>41.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA15" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>7</v>
+        <v>20.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>224.66</v>
+        <v>223.02</v>
       </c>
       <c r="AG15" t="n">
-        <v>-1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2019,10 +1893,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>137.96</v>
+        <v>137.77</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2031,102 +1905,93 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>80.97</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="BM15" t="n">
-        <v>37.45</v>
+        <v>38.99</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>2948.4</v>
+        <v>3132.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B16" t="n">
-        <v>147.9</v>
+        <v>140.8</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="D16" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="E16" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="F16" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="H16" t="n">
         <v>25.4</v>
       </c>
       <c r="I16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J16" t="n">
-        <v>35.8</v>
+        <v>38.4</v>
       </c>
       <c r="K16" t="n">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="N16" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="O16" t="n">
-        <v>39.4</v>
+        <v>36.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>7.5</v>
+        <v>22.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>223.02</v>
+        <v>225.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.55</v>
+        <v>6.89</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2135,10 +2000,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>137.77</v>
+        <v>137.06</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2147,102 +2012,93 @@
         <v>142</v>
       </c>
       <c r="AP16" t="n">
-        <v>85.15000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="AS16" t="n">
-        <v>15.85</v>
+        <v>17.56</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="BM16" t="n">
-        <v>38.99</v>
+        <v>38.26</v>
       </c>
       <c r="BN16" t="n">
-        <v>32.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="BO16" t="n">
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>3132.5</v>
+        <v>3220.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B17" t="n">
-        <v>140.8</v>
+        <v>145.7</v>
       </c>
       <c r="C17" t="n">
-        <v>36.9</v>
+        <v>45.9</v>
       </c>
       <c r="D17" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="E17" t="n">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="F17" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="H17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I17" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J17" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O17" t="n">
         <v>38.4</v>
       </c>
-      <c r="K17" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>36.8</v>
-      </c>
       <c r="Q17" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.9</v>
+        <v>13.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>225.57</v>
+        <v>232.44</v>
       </c>
       <c r="AG17" t="n">
-        <v>6.89</v>
+        <v>0.32</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2251,10 +2107,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>137.06</v>
+        <v>136.23</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2263,102 +2119,66 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>88.22</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BM17" t="n">
-        <v>38.26</v>
+        <v>36.16</v>
       </c>
       <c r="BN17" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO17" t="n">
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3220.9</v>
+        <v>3053.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B18" t="n">
-        <v>145.7</v>
+        <v>136.5</v>
       </c>
       <c r="C18" t="n">
-        <v>45.9</v>
+        <v>52.8</v>
       </c>
       <c r="D18" t="n">
         <v>34.5</v>
       </c>
       <c r="E18" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="F18" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H18" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38.7</v>
+        <v>9.6</v>
       </c>
       <c r="K18" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N18" t="n">
-        <v>35.7</v>
+        <v>97.2</v>
       </c>
       <c r="O18" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20.6</v>
+        <v>36.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="AF18" t="n">
-        <v>232.44</v>
+        <v>228.64</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.32</v>
+        <v>-4.15</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2367,10 +2187,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>136.23</v>
+        <v>134.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.83</v>
+        <v>-1.56</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2378,17 +2198,11 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BM18" t="n">
-        <v>36.16</v>
+        <v>35.28</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -2397,57 +2211,48 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>3053.9</v>
+        <v>2989.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B19" t="n">
-        <v>136.5</v>
+        <v>135.2</v>
       </c>
       <c r="C19" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="E19" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
         <v>9.6</v>
       </c>
       <c r="K19" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
         <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>228.64</v>
+        <v>225.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>-4.15</v>
+        <v>-3.48</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2456,10 +2261,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>134.67</v>
+        <v>128.27</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.56</v>
+        <v>-6.4</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2468,69 +2273,87 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BM19" t="n">
-        <v>35.28</v>
+        <v>34.73</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>530.9</v>
       </c>
       <c r="BP19" t="n">
-        <v>2989.1</v>
+        <v>2772.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B20" t="n">
-        <v>135.2</v>
+        <v>154.3</v>
       </c>
       <c r="C20" t="n">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="D20" t="n">
-        <v>33.4</v>
+        <v>32.3</v>
       </c>
       <c r="E20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.7</v>
       </c>
       <c r="K20" t="n">
-        <v>97.59999999999999</v>
+        <v>74.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>33</v>
       </c>
       <c r="O20" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>23.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4</v>
+        <v>10.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>225.16</v>
+        <v>225.13</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.48</v>
+        <v>-1.28</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2542,7 +2365,7 @@
         <v>128.27</v>
       </c>
       <c r="AL20" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2550,97 +2373,94 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
+      <c r="AP20" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>13.55</v>
+      </c>
       <c r="BL20" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BM20" t="n">
-        <v>34.73</v>
+        <v>32.03</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>530.9</v>
+        <v>164</v>
       </c>
       <c r="BP20" t="n">
-        <v>2772.3</v>
+        <v>2906.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B21" t="n">
-        <v>154.3</v>
+        <v>152.8</v>
       </c>
       <c r="C21" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="D21" t="n">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="F21" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H21" t="n">
         <v>25.1</v>
       </c>
       <c r="I21" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="J21" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="K21" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="O21" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>6.8</v>
+        <v>12.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>225.13</v>
+        <v>223.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>-1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2649,10 +2469,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>128.27</v>
+        <v>125.44</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2661,72 +2481,72 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>79.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BM21" t="n">
-        <v>32.03</v>
+        <v>29.94</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="BP21" t="n">
-        <v>2906.5</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B22" t="n">
-        <v>152.8</v>
+        <v>152</v>
       </c>
       <c r="C22" t="n">
-        <v>60.4</v>
+        <v>57.9</v>
       </c>
       <c r="D22" t="n">
         <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H22" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="I22" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="O22" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q22" t="n">
         <v>23.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2735,28 +2555,19 @@
         <v>23.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>7.7</v>
+        <v>15.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>223.85</v>
+        <v>222.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2765,10 +2576,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>125.44</v>
+        <v>124.13</v>
       </c>
       <c r="AL22" t="n">
-        <v>-2.83</v>
+        <v>-1.31</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2777,69 +2588,69 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>77.90000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="AS22" t="n">
-        <v>13.16</v>
+        <v>13.94</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="BM22" t="n">
-        <v>29.94</v>
+        <v>30.3</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>6604.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>455</v>
+        <v>946</v>
       </c>
       <c r="BP22" t="n">
-        <v>3341</v>
+        <v>3260.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B23" t="n">
-        <v>152</v>
+        <v>156.1</v>
       </c>
       <c r="C23" t="n">
-        <v>57.9</v>
+        <v>60.7</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E23" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="F23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="I23" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J23" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="K23" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="O23" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
@@ -2848,31 +2659,22 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y23" t="n">
         <v>9</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>222.91</v>
+        <v>222.98</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2881,10 +2683,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>124.13</v>
+        <v>125.24</v>
       </c>
       <c r="AL23" t="n">
-        <v>-1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2893,102 +2695,93 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>79.44</v>
+        <v>79.06</v>
       </c>
       <c r="AS23" t="n">
-        <v>13.94</v>
+        <v>14.03</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="BM23" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="BN23" t="n">
-        <v>6604.6</v>
+        <v>0</v>
       </c>
       <c r="BO23" t="n">
-        <v>946</v>
+        <v>1027.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>3260.9</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B24" t="n">
-        <v>156.1</v>
+        <v>156.3</v>
       </c>
       <c r="C24" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="D24" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="E24" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="F24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I24" t="n">
         <v>9.4</v>
       </c>
       <c r="J24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O24" t="n">
         <v>39.5</v>
       </c>
-      <c r="K24" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>41.4</v>
-      </c>
       <c r="Q24" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>5.9</v>
+        <v>12.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.71</v>
+        <v>-0.2</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2997,10 +2790,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>125.24</v>
+        <v>125.58</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.11</v>
+        <v>0.34</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -3009,102 +2802,66 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>79.06</v>
+        <v>79.02</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.03</v>
+        <v>13.34</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="BM24" t="n">
-        <v>30.8</v>
+        <v>32.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>6212.1</v>
       </c>
       <c r="BO24" t="n">
-        <v>1027.3</v>
+        <v>1410.7</v>
       </c>
       <c r="BP24" t="n">
-        <v>3503</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B25" t="n">
-        <v>156.3</v>
+        <v>132.9</v>
       </c>
       <c r="C25" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D25" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="E25" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="F25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Y25" t="n">
         <v>8</v>
       </c>
-      <c r="H25" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N25" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>10</v>
-      </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>221.26</v>
+        <v>221.88</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3113,10 +2870,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>125.58</v>
+        <v>123.06</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3124,76 +2881,61 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>79.02</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>13.34</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BM25" t="n">
-        <v>32.04</v>
+        <v>30.26</v>
       </c>
       <c r="BN25" t="n">
-        <v>6212.1</v>
+        <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>1410.7</v>
+        <v>677.9</v>
       </c>
       <c r="BP25" t="n">
-        <v>3322</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B26" t="n">
-        <v>132.9</v>
+        <v>133.2</v>
       </c>
       <c r="C26" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="D26" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E26" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="K26" t="n">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O26" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>221.88</v>
+        <v>223.58</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3202,10 +2944,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>123.06</v>
+        <v>125.11</v>
       </c>
       <c r="AL26" t="n">
-        <v>-2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3214,69 +2956,87 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BM26" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>677.9</v>
+        <v>1209</v>
       </c>
       <c r="BP26" t="n">
-        <v>676.6</v>
+        <v>357.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B27" t="n">
-        <v>133.2</v>
+        <v>156.7</v>
       </c>
       <c r="C27" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F27" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>40</v>
       </c>
       <c r="K27" t="n">
-        <v>96.7</v>
+        <v>75</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36.7</v>
       </c>
       <c r="O27" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
+        <v>11.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>223.58</v>
+        <v>223.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.7</v>
+        <v>0.11</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3288,7 +3048,7 @@
         <v>125.11</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3296,97 +3056,94 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
+      <c r="AP27" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>14</v>
+      </c>
       <c r="BL27" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BM27" t="n">
-        <v>30.36</v>
+        <v>30.74</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>1209</v>
+        <v>1207.3</v>
       </c>
       <c r="BP27" t="n">
-        <v>357.9</v>
+        <v>1838.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B28" t="n">
-        <v>156.7</v>
+        <v>169.4</v>
       </c>
       <c r="C28" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="E28" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F28" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="K28" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="O28" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="T28" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>5.7</v>
+        <v>10.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>223.6</v>
+        <v>223.66</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.11</v>
+        <v>-3.09</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3395,10 +3152,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>125.11</v>
+        <v>129.53</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3407,102 +3164,93 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>83.37</v>
+        <v>81.22</v>
       </c>
       <c r="AS28" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BM28" t="n">
-        <v>30.74</v>
+        <v>33.76</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>1207.3</v>
+        <v>1003.3</v>
       </c>
       <c r="BP28" t="n">
-        <v>1838.3</v>
+        <v>3599.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B29" t="n">
-        <v>169.4</v>
+        <v>163.7</v>
       </c>
       <c r="C29" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="E29" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H29" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="I29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="K29" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="O29" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="T29" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>9.1</v>
+        <v>12.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>223.66</v>
+        <v>220.58</v>
       </c>
       <c r="AG29" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3511,10 +3259,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>129.53</v>
+        <v>125</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.42</v>
+        <v>-4.53</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3523,102 +3271,93 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>81.22</v>
+        <v>81.27</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BM29" t="n">
-        <v>33.76</v>
+        <v>34.44</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>1003.3</v>
+        <v>1174.9</v>
       </c>
       <c r="BP29" t="n">
-        <v>3599.2</v>
+        <v>3385.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B30" t="n">
-        <v>163.7</v>
+        <v>167.7</v>
       </c>
       <c r="C30" t="n">
-        <v>65.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D30" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E30" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q30" t="n">
         <v>23.